--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -4098,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D999"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4680,970 +4680,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
@@ -6167,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6766,7 +5802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6941,31 +5977,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
@@ -7014,7 +6025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -7108,8 +6119,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7167,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8006,7 +7015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8375,7 +7384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,20 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Song Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09 Block Party" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04 Lincolnwood" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06 Fat Shallot" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07 Chicago Union" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08 Fat Shallot" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09 Block Party" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10 Fat Shallot" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11 Double Clutch" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06 Fat Shallot" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06 American Legion" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09 Block Party" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01 Goat Village" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04 Spring Cha Ching" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05 Lincolnwood" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20250503 lincolnwood" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20250521 post 42" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gigs" sheetId="18" state="visible" r:id="rId18"/>
@@ -40,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +76,26 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF4FB3A8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +120,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -165,6 +188,36 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,12 +583,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -553,13 +606,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>KINGS OF EWING — SONG TRACKER</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Song</t>
@@ -572,1706 +625,1999 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>Decade</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>Never Played Live</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023-09 Block Party</t>
-        </is>
-      </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2024-04 Lincolnwood</t>
+          <t>2023-09-09
+Block Party</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2024-06 Fat Shallot</t>
+          <t>2024-04-27
+Lincolnwood</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2024-07 Chicago Union</t>
+          <t>2024-06-08
+Fat Shallot</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024-08 Fat Shallot</t>
+          <t>2024-07-13
+Chicago Union</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2024-09 Block Party</t>
+          <t>2024-08-10
+Fat Shallot</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2024-10 Fat Shallot</t>
+          <t>2024-09-07
+Block Party</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2025-11 Double Clutch</t>
+          <t>2024-10-09
+Fat Shallot</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2025-06 Fat Shallot</t>
+          <t>2025-11-16
+Double Clutch</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>2025-06 American Legion</t>
+          <t>2025-06-07
+Fat Shallot</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>2025-09 Block Party</t>
+          <t>2025-06-25
+American Legion</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>2026-01 Goat Village</t>
+          <t>2025-09-06
+Block Party</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2026-04 Spring Cha Ching</t>
+          <t>2026-01-24
+Goat Village</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>2026-05 Lincolnwood</t>
+          <t>2026-04-22
+Spring Cha Ching</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-02
+Lincolnwood</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>*Encore</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Rockin In The Free World</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Angel From Montgomery</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>20251016 Double Clutch</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr"/>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Angel From Montgomery</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Come Together</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Don't Let Me Down</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Don't Look Back In Anger</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr"/>
+      <c r="P11" s="8" t="inlineStr"/>
+      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="R11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Follow Your Arrow</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Matt / Miles</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr"/>
+      <c r="P13" s="8" t="inlineStr"/>
+      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="R13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>For What It's Worth</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>From The Start</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Come Together</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr"/>
+      <c r="R17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Head Over Heels</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Crossroads</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Dedicated Follower Of Fashion</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>I've Got A Feeling</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr"/>
+      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="R21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Don'T Let Me Down</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Miles, Miles / Matt, Miles/Matt</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Don'T Look Back In Anger</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Little By Little</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Down By The River</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>End Of The World</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Follow Your Arrow</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Matt, Matt / Miles</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>For What It'S Worth</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
-      <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="5" t="inlineStr"/>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Found Out About You</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>From The Start</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="8" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Head Over Heels</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Heroes</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>I'Ve Got A Feeling</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Miles/Nate</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="8" t="inlineStr"/>
-      <c r="P24" s="8" t="inlineStr"/>
-      <c r="Q24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Just What I Needed</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Matt, Nate</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="8" t="inlineStr"/>
       <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
+      <c r="N26" s="8" t="inlineStr"/>
+      <c r="O26" s="8" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q26" s="8" t="inlineStr"/>
+      <c r="R26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Kings Of Ewing</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Octopus's Garden</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Lincolnwood Spring Fling</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Little By Little</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="inlineStr"/>
-      <c r="Q30" s="8" t="inlineStr"/>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Little Goat Set List</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="R31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Message In A Bottle</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="R33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Rockin' In The Free World</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr"/>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Midnight Rider</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="R35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>No One To Depend On</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr"/>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Octopus'S Garden</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Miles, Miles / Matt, Miles/Matt</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr"/>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P36" s="8" t="inlineStr"/>
-      <c r="Q36" s="8" t="inlineStr"/>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
       <c r="P37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2282,706 +2628,528 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Riders On The Storm</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Teach Your Children</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr"/>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="inlineStr"/>
-      <c r="Q38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Rockin' In The Free World</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr"/>
+      <c r="R39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>That's What I Love</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Vodoo Child</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Voodoo Child</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Seven Nation Army</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>War Pigs</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="22" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
+      <c r="P45" s="8" t="inlineStr"/>
+      <c r="Q45" s="8" t="inlineStr"/>
+      <c r="R45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
-      <c r="O40" s="8" t="inlineStr"/>
-      <c r="P40" s="8" t="inlineStr"/>
-      <c r="Q40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Drew, Matt</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Starlight</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr"/>
-      <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Sympathy For The Devil</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Teach Your Children</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Who's That Lady</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Instrumental</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P47" s="8" t="inlineStr"/>
+      <c r="Q47" s="8" t="inlineStr"/>
+      <c r="R47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr"/>
-      <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
-      <c r="O44" s="8" t="inlineStr"/>
-      <c r="P44" s="8" t="inlineStr"/>
-      <c r="Q44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>That'S What I Love</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>The Seeker</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr"/>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr"/>
-      <c r="Q46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Vodoo Child</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Voodoo Child</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr"/>
-      <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="8" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P48" s="8" t="inlineStr"/>
-      <c r="Q48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>War Pigs</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr"/>
-      <c r="D50" s="8" t="inlineStr"/>
-      <c r="E50" s="8" t="inlineStr"/>
-      <c r="F50" s="8" t="inlineStr"/>
-      <c r="G50" s="8" t="inlineStr"/>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="inlineStr"/>
-      <c r="K50" s="8" t="inlineStr"/>
-      <c r="L50" s="8" t="inlineStr"/>
-      <c r="M50" s="8" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
-      <c r="O50" s="8" t="inlineStr"/>
-      <c r="P50" s="8" t="inlineStr"/>
-      <c r="Q50" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Drew, Matt, V</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Who'S That Lady</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Instrumental</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr"/>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="8" t="inlineStr"/>
-      <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr"/>
-      <c r="M52" s="8" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O52" s="8" t="inlineStr"/>
-      <c r="P52" s="8" t="inlineStr"/>
-      <c r="Q52" s="8" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>Won'T Back Down</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1"/>
@@ -2998,20 +3166,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3176,7 +3341,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
@@ -3312,7 +3476,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -3571,7 +3734,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="n">
         <v>14</v>
@@ -3782,7 +3944,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="n">
         <v>28</v>
@@ -3798,17 +3959,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="n">
         <v>21</v>
@@ -3866,7 +4016,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="n">
         <v>1</v>
@@ -4062,7 +4211,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="n">
         <v>15</v>
@@ -4402,7 +4550,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -6025,10 +6172,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="B2:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
@@ -6361,8 +6507,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -7200,7 +7344,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="n">
         <v>1</v>
@@ -7599,7 +7742,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="n">
         <v>14</v>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -22,8 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20250503 lincolnwood" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20250521 post 42" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gigs" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="future songs" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="old songs" sheetId="20" state="visible" r:id="rId20"/>
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -218,6 +218,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -583,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -603,6 +605,8 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -715,6 +719,18 @@
         <is>
           <t>2026-05-02
 Lincolnwood</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03
+Lincolnwood</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-21
+Post 42</t>
         </is>
       </c>
     </row>
@@ -757,6 +773,8 @@
       <c r="P3" s="8" t="inlineStr"/>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="23" t="inlineStr"/>
+      <c r="T3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -801,6 +819,8 @@
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="24" t="inlineStr"/>
+      <c r="T4" s="24" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -857,6 +877,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -901,6 +927,8 @@
       </c>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="24" t="inlineStr"/>
+      <c r="T6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -945,6 +973,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S7" s="23" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1009,6 +1039,12 @@
       </c>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T8" s="24" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1097,6 +1133,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1133,6 +1175,8 @@
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="24" t="inlineStr"/>
+      <c r="T10" s="24" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1201,6 +1245,8 @@
       <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
+      <c r="S11" s="23" t="inlineStr"/>
+      <c r="T11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1249,6 +1295,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S12" s="24" t="inlineStr"/>
+      <c r="T12" s="24" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1289,6 +1337,8 @@
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
+      <c r="S13" s="23" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1325,6 +1375,8 @@
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="24" t="inlineStr"/>
+      <c r="T14" s="24" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1397,6 +1449,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1457,6 +1515,8 @@
       </c>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="24" t="inlineStr"/>
+      <c r="T16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1493,6 +1553,8 @@
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
+      <c r="S17" s="23" t="inlineStr"/>
+      <c r="T17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1549,6 +1611,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S18" s="24" t="inlineStr"/>
+      <c r="T18" s="24" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1593,6 +1657,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S19" s="23" t="inlineStr"/>
+      <c r="T19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1657,6 +1723,8 @@
       </c>
       <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="24" t="inlineStr"/>
+      <c r="T20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1693,6 +1761,8 @@
       <c r="P21" s="8" t="inlineStr"/>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
+      <c r="S21" s="23" t="inlineStr"/>
+      <c r="T21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -1777,6 +1847,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1837,6 +1913,12 @@
       </c>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T23" s="23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1897,6 +1979,8 @@
       </c>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="24" t="inlineStr"/>
+      <c r="T24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -1969,6 +2053,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S25" s="23" t="inlineStr"/>
+      <c r="T25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2005,6 +2091,8 @@
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
+      <c r="S26" s="24" t="inlineStr"/>
+      <c r="T26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -2049,6 +2137,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S27" s="23" t="inlineStr"/>
+      <c r="T27" s="23" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -2121,6 +2211,12 @@
       </c>
       <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T28" s="24" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2201,6 +2297,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T29" s="23" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -2241,6 +2343,8 @@
       <c r="P30" s="5" t="inlineStr"/>
       <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="24" t="inlineStr"/>
+      <c r="T30" s="24" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -2297,6 +2401,8 @@
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
+      <c r="S31" s="23" t="inlineStr"/>
+      <c r="T31" s="23" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2365,6 +2471,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -2429,6 +2541,8 @@
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
+      <c r="S33" s="23" t="inlineStr"/>
+      <c r="T33" s="23" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -2489,6 +2603,8 @@
       </c>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="24" t="inlineStr"/>
+      <c r="T34" s="24" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -2533,6 +2649,8 @@
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
+      <c r="S35" s="23" t="inlineStr"/>
+      <c r="T35" s="23" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2589,6 +2707,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T36" s="24" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -2633,6 +2757,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S37" s="23" t="inlineStr"/>
+      <c r="T37" s="23" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
@@ -2673,6 +2799,8 @@
       <c r="P38" s="5" t="inlineStr"/>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="24" t="inlineStr"/>
+      <c r="T38" s="24" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -2709,6 +2837,8 @@
       <c r="P39" s="8" t="inlineStr"/>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
+      <c r="S39" s="23" t="inlineStr"/>
+      <c r="T39" s="23" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2753,6 +2883,8 @@
       </c>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="24" t="inlineStr"/>
+      <c r="T40" s="24" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2801,6 +2933,12 @@
       </c>
       <c r="Q41" s="8" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T41" s="23" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2837,6 +2975,8 @@
       <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="24" t="inlineStr"/>
+      <c r="T42" s="24" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -2873,6 +3013,8 @@
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
+      <c r="S43" s="23" t="inlineStr"/>
+      <c r="T43" s="23" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2917,6 +3059,12 @@
       <c r="P44" s="5" t="inlineStr"/>
       <c r="Q44" s="5" t="inlineStr"/>
       <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T44" s="24" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -2953,6 +3101,8 @@
       <c r="P45" s="8" t="inlineStr"/>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
+      <c r="S45" s="23" t="inlineStr"/>
+      <c r="T45" s="23" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -3041,6 +3191,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T46" s="24" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -3077,6 +3233,8 @@
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
+      <c r="S47" s="23" t="inlineStr"/>
+      <c r="T47" s="23" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -3145,9 +3303,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="S48" s="24" t="inlineStr"/>
+      <c r="T48" s="24" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -773,7 +773,7 @@
       <c r="P3" s="8" t="inlineStr"/>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="23" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
@@ -819,7 +819,7 @@
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="24" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="24" t="inlineStr"/>
     </row>
     <row r="5">
@@ -927,7 +927,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="24" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
       <c r="T6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
@@ -973,7 +973,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="23" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1175,7 +1175,7 @@
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="24" t="inlineStr"/>
+      <c r="S10" s="8" t="inlineStr"/>
       <c r="T10" s="24" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1245,7 +1245,7 @@
       <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
-      <c r="S11" s="23" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1295,7 +1295,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="24" t="inlineStr"/>
+      <c r="S12" s="8" t="inlineStr"/>
       <c r="T12" s="24" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1337,7 +1337,7 @@
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
-      <c r="S13" s="23" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1375,7 +1375,7 @@
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="24" t="inlineStr"/>
+      <c r="S14" s="8" t="inlineStr"/>
       <c r="T14" s="24" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="24" t="inlineStr"/>
+      <c r="S16" s="8" t="inlineStr"/>
       <c r="T16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
-      <c r="S17" s="23" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1611,7 +1611,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="24" t="inlineStr"/>
+      <c r="S18" s="8" t="inlineStr"/>
       <c r="T18" s="24" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="23" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="24" t="inlineStr"/>
+      <c r="S20" s="8" t="inlineStr"/>
       <c r="T20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1761,7 +1761,7 @@
       <c r="P21" s="8" t="inlineStr"/>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
-      <c r="S21" s="23" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="24" t="inlineStr"/>
+      <c r="S24" s="8" t="inlineStr"/>
       <c r="T24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2053,7 +2053,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="23" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
-      <c r="S26" s="24" t="inlineStr"/>
+      <c r="S26" s="8" t="inlineStr"/>
       <c r="T26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2137,7 +2137,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="23" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="23" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2343,7 +2343,7 @@
       <c r="P30" s="5" t="inlineStr"/>
       <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="24" t="inlineStr"/>
+      <c r="S30" s="8" t="inlineStr"/>
       <c r="T30" s="24" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
-      <c r="S31" s="23" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="23" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
-      <c r="S33" s="23" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="23" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="24" t="inlineStr"/>
+      <c r="S34" s="8" t="inlineStr"/>
       <c r="T34" s="24" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2649,7 +2649,7 @@
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
-      <c r="S35" s="23" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="23" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2757,7 +2757,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="23" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="23" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2799,7 +2799,7 @@
       <c r="P38" s="5" t="inlineStr"/>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="24" t="inlineStr"/>
+      <c r="S38" s="8" t="inlineStr"/>
       <c r="T38" s="24" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2837,7 +2837,7 @@
       <c r="P39" s="8" t="inlineStr"/>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
-      <c r="S39" s="23" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="23" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="24" t="inlineStr"/>
+      <c r="S40" s="8" t="inlineStr"/>
       <c r="T40" s="24" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2975,7 +2975,7 @@
       <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="24" t="inlineStr"/>
+      <c r="S42" s="8" t="inlineStr"/>
       <c r="T42" s="24" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
-      <c r="S43" s="23" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="23" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3101,7 +3101,7 @@
       <c r="P45" s="8" t="inlineStr"/>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
-      <c r="S45" s="23" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="23" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3233,7 +3233,7 @@
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
-      <c r="S47" s="23" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="23" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3303,14 +3303,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="24" t="inlineStr"/>
+      <c r="S48" s="8" t="inlineStr"/>
       <c r="T48" s="24" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1"/>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -10,22 +10,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Song Tracker" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gig Tracker" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Songs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Gigs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-14 Fat Shallot" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-24 Ridgeville Parks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +93,18 @@
       <b val="1"/>
       <color rgb="FFCC0000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE8DFC0"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -151,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,6 +238,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3328,6 +3355,974 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>20251016 Double Clutch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lead vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>message in a bottle</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>don't let me down</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>come together</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>smooth operator</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>teach your children</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pink pony club</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>the seeker</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>guess again</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>no one to depend on</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>end of the world</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>midnight rider</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>whipping post</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lead vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>don't let me down</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>miles / matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Angel from Montgomery</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>won't back down</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>fortunate son</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>No one to depend on</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Just what i needed</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>riders on the storm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>whipping post</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Who's That Lady</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Instrumental</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId7"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lead vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>don't let me down</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>miles / matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>down by the river</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>That's What I love</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MIles/Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Angel from Montgomery</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MIles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Your Arrow </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Matt / Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>won't back down</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>midnight rider</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>fortunate son</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>No one to depend on</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>found out about you</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Just what i needed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>laid</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>dedicated follower of fashion</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Bohemian like you</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>riders on the storm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Kings of Ewing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Come Together </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>heroes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>whipping post</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>rockin in the free world</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId19"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3653,7 +4648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3666,7 +4661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3917,7 +4912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4124,7 +5119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4568,7 +5563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4936,7 +5931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5150,7 +6145,500 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>KINGS OF EWING — GIG LOG</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t># Songs</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Venue Contact</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Event Contact</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Pay</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Block Party</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="29" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Lincolnwood</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="30" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Fat Shallot</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Chicago Union</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>J.A. Cohen (Jeff) — jacohenmusic@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>~1 hr set starting ~1 hr before game time. Now at ETHS Lazier Field (moved from NU due to Red Stars conflicts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fat Shallot</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Block Party</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="30" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Fat Shallot</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Lincolnwood</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="30" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Post 42</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Fat Shallot</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>American Legion</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="29" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Block Party</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="30" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Double Clutch (Bundled Blessings Fundraiser)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Nick Murray — nmurray@doubleclutchbrewing.com</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Krys Juleen — krys@faithatfirst.com (First United Methodist Church)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Goat Village</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>goatvillage777@gmail.com</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>They requested flyer in 2 sizes: 1080x1350 and 1080x1920. Asked to be added as cohosts on Facebook event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Spring Cha Ching</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="29" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Lincolnwood</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="30" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Mack's Bike &amp; Goods</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Kelly Mack — kelly@macksbikeandgoods.com</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr"/>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Cancelled due to weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ridgeville Parks District</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Natalie Sallee — programs@ridgeville.org — (847) 869-5640 / (847) 257-6912</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Agreement coming in a few weeks per Jan 21 email. 6:00 PM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Fat Shallot (Covenant Nursery Dining for Dollars)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Kim Stanton — kims@covenantnurseryschool.org — 847-675-2993</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>5:30-7:30 PM. Covenant Nursery School fundraiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5524,7 +7012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5773,7 +7261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5966,357 +7454,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>KINGS OF EWING — GIG LOG</t>
-        </is>
-      </c>
-      <c r="B1" s="24" t="n"/>
-      <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
-      <c r="E1" s="24" t="n"/>
-      <c r="F1" s="24" t="n"/>
-      <c r="G1" s="24" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t># Songs</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Pay</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Block Party</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Lincolnwood</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Fat Shallot</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Chicago Union</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Fat Shallot</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Block Party</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Fat Shallot</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Lincolnwood</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Post 42</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Fat Shallot</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>American Legion</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Block Party</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Double Clutch</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Goat Village</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Spring Cha Ching</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Lincolnwood</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6386,277 +7523,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="n">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lincolnwood Spring Fling</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>KINGS OF EWING — POTENTIAL GIGS</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Date Reached Out</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Proposed Date</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Downtown Evanston</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Andy Vick — avick@downtownevanston.org — 847-866-6319</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr"/>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Puts music line-up together in January — follow up Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Stippler Block Party</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Nicole Stippler — nicole@stippler.com — 773-627-6954</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Saw us at Lincolnwood Spring Fling. Last minute inquiry for block party closer. Asked about rates and availability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 — Fat Shallot — Covenant Nursery Dining for Dollars — 5:30-7:30 PM</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>opener</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>seven nation army</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>skye</t>
-        </is>
-      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Skye</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>head over heals</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Head Over Heals</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>just like heaven</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>guess again</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>message in a bottle</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>crossroads</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>starlight</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>end of the world</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6677,7 +7984,356 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 — Ridgeville Parks District — 6:00 PM</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="n">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lincolnwood Spring Fling</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>opener</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>seven nation army</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>skye</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>don't let me down</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pink pony club</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>head over heals</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>just like heaven</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>guess again</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>message in a bottle</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>crossroads</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>laid</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>no one to depend on</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>fortunate son</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>smooth operator</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>bohemian like you</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>starlight</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>end of the world</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>won't back down</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>whipping post</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6868,7 +8524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7482,972 +9138,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>20251016 Double Clutch</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>message in a bottle</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>come together</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>teach your children</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>the seeker</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>guess again</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>end of the world</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Angel from Montgomery</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Just what i needed</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Who's That Lady</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Instrumental</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId7"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>That's What I love</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MIles/Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Angel from Montgomery</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MIles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow Your Arrow </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Matt / Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Seeker</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Just what i needed</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Bohemian like you</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Kings of Ewing</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Come Together </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId19"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -11,24 +11,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gig Tracker" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Songs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Gigs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-14 Fat Shallot" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-24 Ridgeville Parks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-16 Fat Shallot" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-14 Fat Shallot" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-24 Ridgeville Parks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -166,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -250,6 +251,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2145,7 +2155,7 @@
       <c r="T26" s="26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
@@ -2455,7 +2465,7 @@
       <c r="T31" s="25" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
@@ -2703,7 +2713,7 @@
       <c r="T35" s="25" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
@@ -3335,15 +3345,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3355,236 +3366,589 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>20251016 Double Clutch</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-01-24 — Goat Village</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>message in a bottle</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Don't Let Me Down</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>After Song Ends Drew Will Start Riff For Next Song</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Found out About You</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles Will Tune Guitar Down Then Start Next Song</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>come together</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jack Will Switch To Acoustic Guitar And Start Next Song</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Jack Will Start Next Song</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>teach your children</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Little By Little</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack Will Back To Bass, Once Done, Jim Will Start Next Song</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>End of the World</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Jim Will Count Into Next Song And Start With Jack</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>the seeker</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Matt To Start Opening Riff For Next Song When Ready</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>guess again</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Head over Heels</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles Starts The Next Song With An Acoustic Riff</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>From the Start</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Jim Will Count In For Drew And Miles To Start Riff Of Next Song</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>What I Love</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Jack Starts Bass Riff For Next Song When Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>No One to Depend On</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Jim Starts Drum Beat Before Jack Joins</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Jim And Jack Count In And Start Together</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>end of the world</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Jack Chromatic Walkup To B To Start Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Miles Starts Next Song With Solo Acoustic Intro With Two "I Won'T Back Down"S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Jack Starts Bass Riff For Next Song When Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Set Ends</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Solo Guitar in A</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Band Will Take Get Back To Their Instruments While Drew Improvises And Drew Will Start Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Let Ending Chord Ring Out And Jim Counts In Start Of Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Matt Starts With Solo Piano Part</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Matt And Jim Start Together For Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Drew Starts Intro On Guitar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Kings of Ewing</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Miles Plays Audio Sample To Start Song Then Jack And Drums Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Riders on the Storm</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Drew Starts Intro On Guitar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Hold On D At End Then Gym Counts Us Into Start Of Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Jack Switches To Guitar And Starts Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Ded. Follower</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Jack Switches Back To Bass And Starts With Jim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Come Together</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Jim Counts Band In For Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>Message in a Bottle</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Drew Starts Intro On Guitar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Jim Counts Band In For Next Song</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Rockin in the World</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Miles Starts Solo Acoustic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Drew Starts If Time Is Permitting</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Voodoo Child</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Set Ends</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3596,233 +3960,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-11-16 — Double Clutch (Bundled Blessings Fundraiser)</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Come Together</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Teach Your Children</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Angel from Montgomery</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Just what i needed</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="14">
+      <c r="A14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Who's That Lady</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Instrumental</t>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
@@ -3830,11 +4193,13 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3846,472 +4211,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-09-06 — Ewing Block Party</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Drew</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>That's What I love</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Drew</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Angel From Montgomery</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MIles/Matt</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Angel from Montgomery</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MIles</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow Your Arrow </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Matt / Miles</t>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Seeker</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Drew</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Just what i needed</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Bohemian like you</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Kings of Ewing</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Come Together </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>21</v>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Who'S That Lady</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Instrumental</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4323,326 +4477,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-06-25 — American Legion</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>miles/matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>just like heaven</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>that's what i love</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>That'S What I Love</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>follow arrow</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Miles/Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Angel From Montgomery</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>guess again</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>the seeker</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Follow Your Arrow</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Matt / Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no one to depend on </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>just what i needed</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>follower of fashion</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>rider on the storm</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>kings of ewing</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>*encore</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Come Together</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4654,9 +4964,357 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-06-07 — Fat Shallot</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles/Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>That'S What I Love</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Follow Arrow</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Rider On The Storm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>*encore</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4667,243 +5325,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>walk on</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>immediate transition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>immediate transition</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>just like heavan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>band intro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>right into fotrunate son</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>just what i needed</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>right into dlmd</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>the seeker</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>encore</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>rocking in the free world0</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>miles</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-05-21 — Post 42</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
         </is>
       </c>
     </row>
@@ -4918,202 +5370,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2025-05-03 — Lincolnwood PTA Spring Fling</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Don't let me Down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Just Like Heavan</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>No one to Depend On</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Down by the River</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Kings of Ewing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Just What I Needed</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Dedicated Follower of Fashion</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>encore</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Rocking In The Free World0</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5125,439 +5638,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-10-09 — Fat Shallot (Covenant Nursery Dining for Dollars)</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>wont back down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>octopuss's garden</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kings of ewing </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ohio </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>sympathy for the devil</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>nate</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just what i needed </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>nate</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>i've got a feeling</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>miles/nate</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>don't look back in anger</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>seven national army</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just like heaven </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>vodoo child</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5569,363 +5860,450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-09-07 — Ewing Block Party</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>wont back down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wont Back Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Octopuss'S Garden</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kings of ewing </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ohio </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>sympathy for the devil</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>nate</t>
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just what i needed </t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>nate</t>
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A16" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Nate</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>seven national army</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Nate</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>jack</t>
+      <c r="A18" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>I'Ve Got A Feeling</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Miles/Nate</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Don'T Look Back In Anger</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just like heaven </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="A20" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>8</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="A21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="A22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Seven National Army</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Vodoo Child</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5937,209 +6315,374 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bass</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-08-10 — Fat Shallot</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just like heaven </t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wont Back Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ohio </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heroes </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>matt</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Seven National Army</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6151,7 +6694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6214,7 +6757,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2023-09-09</t>
         </is>
@@ -6233,7 +6776,7 @@
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>2024-04-27</t>
         </is>
@@ -6252,7 +6795,7 @@
       <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
@@ -6275,7 +6818,7 @@
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>2024-07-13</t>
         </is>
@@ -6302,7 +6845,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>2024-08-10</t>
         </is>
@@ -6325,7 +6868,7 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
@@ -6344,7 +6887,7 @@
       <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>2024-10-09</t>
         </is>
@@ -6367,7 +6910,7 @@
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
@@ -6386,7 +6929,7 @@
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
@@ -6403,7 +6946,7 @@
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
@@ -6426,7 +6969,7 @@
       <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>2025-06-25</t>
         </is>
@@ -6445,7 +6988,7 @@
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
@@ -6464,7 +7007,7 @@
       <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
@@ -6491,7 +7034,7 @@
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
@@ -6516,7 +7059,7 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -6535,7 +7078,7 @@
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
@@ -6579,7 +7122,7 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
@@ -6604,7 +7147,7 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -6632,8 +7175,57 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Fat Shallot (Greg's 40th Birthday)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>info@thefatshallot.com / Grace — catering@thefatshallot.com</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Jenny Sprenzel — Jenny.Sprenzel@rushortho.com</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>7:00-9:00 PM. Private birthday party.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6644,369 +7236,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bass</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-07-13 — Chicago Union (NU Soccer)</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>wont back down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>No one to depend on</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kings of ewing </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just like heaven </t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ohio </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>jack</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7018,244 +7459,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SET LIST ORDER</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-06-08 — Fat Shallot</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>wont back down</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wont Back Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">just like heaven </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>seven nation army</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>riders on the storm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>heroes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>midnight rider</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>rockin in the free world</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miles</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>So windy. Need solution for keeping stands up right</t>
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>need to check vocals against loudest songs</t>
+      <c r="A16" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>could have used longer xlr to pa</t>
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>spread pa out wider to limit feedback</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>put rhodes mics back farther to get better sound</t>
+      <c r="A18" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7267,192 +7760,433 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SET LIST ORDER</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>lead vocal</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/playlist/1UwXYOrt3AZvxw8wzesIbj?si=FqTTMOvSTvq3v4QzhxXD4w</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2024-04-27 — Lincolnwood PTA Spring Fling</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't le me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles / matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>found out about you</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wont Back Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>octupus's gardgen</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>down by the river</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>dedicated follower of fashion</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>for what it's worth</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heroes </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Rockin In The Free World</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>So Windy. Need Solution For Keeping Stands Up Right</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2023-09-09 — Ewing Block Party</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Don'T Le Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Octupus'S Gardgen</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>For What It'S Worth</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7650,7 +8384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7662,12 +8396,11 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>2026-05-14 — Fat Shallot — Covenant Nursery Dining for Dollars — 5:30-7:30 PM</t>
+          <t>2026-05-16 — Fat Shallot (Greg's 40th Birthday) — 7:00-9:00 PM</t>
         </is>
       </c>
       <c r="B1" s="24" t="n"/>
       <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7685,301 +8418,8 @@
           <t>Lead Vocal</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>opener</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Seven Nation Army</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Skye</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Don'T Let Me Down</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Head Over Heals</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Message In A Bottle</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Crossroads</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>No One To Depend On</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Starlight</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>End Of The World</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Won'T Back Down</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7990,7 +8430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8002,12 +8442,11 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 — Ridgeville Parks District — 6:00 PM</t>
+          <t>2026-05-14 — Fat Shallot (Covenant Nursery Dining for Dollars) — 5:30-7:30 PM</t>
         </is>
       </c>
       <c r="B1" s="24" t="n"/>
       <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -8025,13 +8464,264 @@
           <t>Lead Vocal</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Head Over Heals</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Little By Little</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8042,293 +8732,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="n">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lincolnwood Spring Fling</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>opener</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>seven nation army</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>skye</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>head over heals</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>just like heaven</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>guess again</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>message in a bottle</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>crossroads</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>fortunate son</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>smooth operator</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>bohemian like you</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>starlight</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>end of the world</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>won't back down</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>v</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 — Ridgeville Parks District — 6:00 PM</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8339,186 +8778,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>song</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>singer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-02 — Lincolnwood PTA Spring Fling</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>opener</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Skye</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>don't let me down</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pink pony club</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>head over heals</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Head Over Heals</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>just like heaven</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>crossroads</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>laid</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>no one to depend on</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>starlight</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">end of the world </t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>whipping post</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>drew</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Won'T Back Down</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8530,611 +9097,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Little Goat Set List</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>2026-04-22 — American Legion (D65 Spring Cha Ching)</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lead Singer</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Transition Note for next song</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Set 1</t>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lead Vocal</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Don't Let Me Down</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>After song ends Drew will start riff for next song</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Found out About You</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Head Over Heals</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Miles will tune guitar down then start next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Jack will switch to Acoustic Guitar and start next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jack will start next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Little By Little</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jack will back to bass, once done, Jim will start next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>End of the World</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jim will count into next song and start with Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Matt to start opening riff for next song when ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Head over Heels</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Drew</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Miles starts the next song with an acoustic riff</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>From the Start</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jim will count in for Drew and Miles to start riff of next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>What I Love</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jack starts bass riff for next song when ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>No One to Depend On</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jim starts drum beat before Jack joins</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Jim and Jack count in and start together</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Jack chromatic walkup to B to start next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Starlight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Miles starts next song with solo acoustic intro with two "I won't back down"s</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Won't Back Down</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Jack starts bass riff for next song when ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Set ends</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Solo Guitar in A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Band will take get back to their instruments while Drew improvises and Drew will start next song</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Set 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The Seeker</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Let ending chord ring out and Jim counts in start of next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Crossroads</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Matt starts with solo piano part</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Matt and Jim start together for next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Drew starts intro on Guitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Kings of Ewing</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Miles plays audio sample to start song then Jack and drums start</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Riders on the Storm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Drew starts intro on Guitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Midnight Rider</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Hold on D at end then gym counts us into start of next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Heroes</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jack switches to guitar and starts song</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Ded. Follower</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jack switches back to bass and starts with Jim</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Come Together</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jim counts band in for next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Message in a Bottle</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Drew starts intro on Guitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Just What I Needed</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jim counts band in for next song</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Rockin in the World</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Miles starts solo acoustic</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Drew starts if time is permitting</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Voodoo Child</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Set Ends</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -11,26 +11,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gig Tracker" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Songs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potential Gigs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-24 Ridgeville Parks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-21 Chicago Union" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-16 Fat Shallot" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-14 Fat Shallot" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-24 Ridgeville Parks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06-21 Chicago Union" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-16 Fat Shallot" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-14 Fat Shallot" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-02 Lincolnwood" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04-22 Spring Cha Ching" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01-24 Goat Village" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11-16 Double Clutch" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09-06 Block Party" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-25 American Legion" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-07 Fat Shallot" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-21 Post 42" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-05-03 Lincolnwood" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-10-09 Fat Shallot" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-09-07 Block Party" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-08-10 Fat Shallot" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-07-13 Chicago Union" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-06-08 Fat Shallot" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-04-27 Lincolnwood" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023-09-09 Block Party" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -342,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -604,6 +605,33 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -973,13 +1001,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1004,9 +1032,6 @@
           <t>KINGS OF EWING — SONG TRACKER</t>
         </is>
       </c>
-      <c r="B1" s="72" t="n"/>
-      <c r="C1" s="72" t="n"/>
-      <c r="D1" s="72" t="n"/>
       <c r="E1" s="72" t="n"/>
       <c r="F1" s="72" t="n"/>
       <c r="G1" s="72" t="n"/>
@@ -1022,120 +1047,138 @@
       <c r="Q1" s="72" t="n"/>
       <c r="R1" s="72" t="n"/>
       <c r="S1" s="72" t="n"/>
-      <c r="T1" s="73" t="n"/>
+      <c r="T1" s="72" t="n"/>
+      <c r="U1" s="72" t="n"/>
+      <c r="V1" s="72" t="n"/>
+      <c r="W1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="99" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C2" s="99" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D2" s="104" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>Lead Vocal(s)</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="F2" s="98" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="D2" s="89" t="inlineStr">
+      <c r="G2" s="98" t="inlineStr">
         <is>
           <t>Never Played Live</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
+      <c r="H2" s="98" t="inlineStr">
         <is>
           <t>2026-05-02
 Lincolnwood</t>
         </is>
       </c>
-      <c r="F2" s="89" t="inlineStr">
+      <c r="I2" s="98" t="inlineStr">
         <is>
           <t>2026-04-22
 Spring Cha Ching</t>
         </is>
       </c>
-      <c r="G2" s="89" t="inlineStr">
+      <c r="J2" s="98" t="inlineStr">
         <is>
           <t>2026-01-24
 Goat Village</t>
         </is>
       </c>
-      <c r="H2" s="89" t="inlineStr">
+      <c r="K2" s="98" t="inlineStr">
         <is>
           <t>2025-11-16
 Double Clutch</t>
         </is>
       </c>
-      <c r="I2" s="89" t="inlineStr">
+      <c r="L2" s="98" t="inlineStr">
         <is>
           <t>2025-09-06
 Block Party</t>
         </is>
       </c>
-      <c r="J2" s="89" t="inlineStr">
+      <c r="M2" s="98" t="inlineStr">
         <is>
           <t>2025-06-25
 American Legion</t>
         </is>
       </c>
-      <c r="K2" s="89" t="inlineStr">
+      <c r="N2" s="98" t="inlineStr">
         <is>
           <t>2025-06-07
 Fat Shallot</t>
         </is>
       </c>
-      <c r="L2" s="89" t="inlineStr">
+      <c r="O2" s="98" t="inlineStr">
         <is>
           <t>2025-05-21
 Post 42</t>
         </is>
       </c>
-      <c r="M2" s="89" t="inlineStr">
+      <c r="P2" s="98" t="inlineStr">
         <is>
           <t>2025-05-03
 Lincolnwood</t>
         </is>
       </c>
-      <c r="N2" s="89" t="inlineStr">
+      <c r="Q2" s="98" t="inlineStr">
         <is>
           <t>2024-10-09
 Fat Shallot</t>
         </is>
       </c>
-      <c r="O2" s="89" t="inlineStr">
+      <c r="R2" s="98" t="inlineStr">
         <is>
           <t>2024-09-07
 Block Party</t>
         </is>
       </c>
-      <c r="P2" s="89" t="inlineStr">
+      <c r="S2" s="98" t="inlineStr">
         <is>
           <t>2024-08-10
 Fat Shallot</t>
         </is>
       </c>
-      <c r="Q2" s="89" t="inlineStr">
+      <c r="T2" s="98" t="inlineStr">
         <is>
           <t>2024-07-13
 Chicago Union</t>
         </is>
       </c>
-      <c r="R2" s="89" t="inlineStr">
+      <c r="U2" s="98" t="inlineStr">
         <is>
           <t>2024-06-08
 Fat Shallot</t>
         </is>
       </c>
-      <c r="S2" s="89" t="inlineStr">
+      <c r="V2" s="98" t="inlineStr">
         <is>
           <t>2024-04-27
 Lincolnwood</t>
         </is>
       </c>
-      <c r="T2" s="89" t="inlineStr">
+      <c r="W2" s="98" t="inlineStr">
         <is>
           <t>2023-09-09
 Block Party</t>
@@ -1143,46 +1186,49 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="97" t="inlineStr">
         <is>
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="100" t="inlineStr"/>
+      <c r="C3" s="100" t="inlineStr"/>
+      <c r="D3" s="105" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="F3" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D3" s="92" t="inlineStr"/>
-      <c r="E3" s="92" t="n"/>
-      <c r="F3" s="92" t="n"/>
-      <c r="G3" s="92" t="n"/>
-      <c r="H3" s="92" t="n"/>
-      <c r="I3" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J3" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K3" s="92" t="n"/>
-      <c r="L3" s="92" t="n"/>
-      <c r="M3" s="92" t="n"/>
-      <c r="N3" s="92" t="n"/>
-      <c r="O3" s="92" t="n"/>
-      <c r="P3" s="92" t="n"/>
-      <c r="Q3" s="92" t="n"/>
-      <c r="R3" s="92" t="n"/>
-      <c r="S3" s="92" t="n"/>
-      <c r="T3" s="92" t="n"/>
+      <c r="G3" s="97" t="inlineStr"/>
+      <c r="H3" s="97" t="n"/>
+      <c r="I3" s="97" t="n"/>
+      <c r="J3" s="97" t="n"/>
+      <c r="K3" s="97" t="n"/>
+      <c r="L3" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M3" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N3" s="97" t="n"/>
+      <c r="O3" s="97" t="n"/>
+      <c r="P3" s="97" t="n"/>
+      <c r="Q3" s="97" t="n"/>
+      <c r="R3" s="97" t="n"/>
+      <c r="S3" s="97" t="n"/>
+      <c r="T3" s="97" t="n"/>
+      <c r="U3" s="97" t="n"/>
+      <c r="V3" s="97" t="n"/>
+      <c r="W3" s="97" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="94" t="inlineStr">
@@ -1190,107 +1236,121 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C4" s="102" t="inlineStr"/>
+      <c r="D4" s="106" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="F4" s="94" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="D4" s="94" t="inlineStr"/>
-      <c r="E4" s="94" t="n"/>
-      <c r="F4" s="94" t="n"/>
-      <c r="G4" s="94" t="n"/>
+      <c r="G4" s="94" t="inlineStr"/>
       <c r="H4" s="94" t="n"/>
       <c r="I4" s="94" t="n"/>
-      <c r="J4" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J4" s="94" t="n"/>
       <c r="K4" s="94" t="n"/>
       <c r="L4" s="94" t="n"/>
-      <c r="M4" s="94" t="n"/>
+      <c r="M4" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N4" s="94" t="n"/>
-      <c r="O4" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P4" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O4" s="94" t="n"/>
+      <c r="P4" s="94" t="n"/>
       <c r="Q4" s="94" t="n"/>
-      <c r="R4" s="94" t="n"/>
-      <c r="S4" s="94" t="n"/>
+      <c r="R4" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T4" s="94" t="n"/>
+      <c r="U4" s="94" t="n"/>
+      <c r="V4" s="94" t="n"/>
+      <c r="W4" s="94" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="inlineStr">
+      <c r="A5" s="97" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
+      <c r="B5" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C5" s="100" t="inlineStr"/>
+      <c r="D5" s="105" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="F5" s="97" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="D5" s="92" t="inlineStr"/>
-      <c r="E5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F5" s="92" t="n"/>
-      <c r="G5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H5" s="92" t="n"/>
-      <c r="I5" s="92" t="n"/>
-      <c r="J5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K5" s="92" t="n"/>
-      <c r="L5" s="92" t="n"/>
-      <c r="M5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N5" s="92" t="n"/>
-      <c r="O5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="92" t="n"/>
-      <c r="R5" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="92" t="n"/>
-      <c r="T5" s="92" t="n"/>
+      <c r="G5" s="97" t="inlineStr"/>
+      <c r="H5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I5" s="97" t="n"/>
+      <c r="J5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="97" t="n"/>
+      <c r="L5" s="97" t="n"/>
+      <c r="M5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N5" s="97" t="n"/>
+      <c r="O5" s="97" t="n"/>
+      <c r="P5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="97" t="n"/>
+      <c r="R5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T5" s="97" t="n"/>
+      <c r="U5" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="97" t="n"/>
+      <c r="W5" s="97" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="94" t="inlineStr">
@@ -1298,38 +1358,42 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C6" s="102" t="inlineStr"/>
+      <c r="D6" s="106" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="F6" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D6" s="94" t="inlineStr"/>
-      <c r="E6" s="94" t="n"/>
-      <c r="F6" s="94" t="n"/>
-      <c r="G6" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H6" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G6" s="94" t="inlineStr"/>
+      <c r="H6" s="94" t="n"/>
       <c r="I6" s="94" t="n"/>
       <c r="J6" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K6" s="94" t="n"/>
+      <c r="K6" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L6" s="94" t="n"/>
-      <c r="M6" s="94" t="n"/>
+      <c r="M6" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N6" s="94" t="n"/>
       <c r="O6" s="94" t="n"/>
       <c r="P6" s="94" t="n"/>
@@ -1337,77 +1401,87 @@
       <c r="R6" s="94" t="n"/>
       <c r="S6" s="94" t="n"/>
       <c r="T6" s="94" t="n"/>
+      <c r="U6" s="94" t="n"/>
+      <c r="V6" s="94" t="n"/>
+      <c r="W6" s="94" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="97" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C7" s="100" t="inlineStr"/>
+      <c r="D7" s="105" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="F7" s="97" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D7" s="92" t="inlineStr"/>
-      <c r="E7" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G7" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H7" s="92" t="n"/>
-      <c r="I7" s="92" t="n"/>
-      <c r="J7" s="92" t="n"/>
-      <c r="K7" s="92" t="n"/>
-      <c r="L7" s="92" t="n"/>
-      <c r="M7" s="92" t="n"/>
-      <c r="N7" s="92" t="n"/>
-      <c r="O7" s="92" t="n"/>
-      <c r="P7" s="92" t="n"/>
-      <c r="Q7" s="92" t="n"/>
-      <c r="R7" s="92" t="n"/>
-      <c r="S7" s="92" t="n"/>
-      <c r="T7" s="92" t="n"/>
+      <c r="G7" s="97" t="inlineStr"/>
+      <c r="H7" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="97" t="n"/>
+      <c r="L7" s="97" t="n"/>
+      <c r="M7" s="97" t="n"/>
+      <c r="N7" s="97" t="n"/>
+      <c r="O7" s="97" t="n"/>
+      <c r="P7" s="97" t="n"/>
+      <c r="Q7" s="97" t="n"/>
+      <c r="R7" s="97" t="n"/>
+      <c r="S7" s="97" t="n"/>
+      <c r="T7" s="97" t="n"/>
+      <c r="U7" s="97" t="n"/>
+      <c r="V7" s="97" t="n"/>
+      <c r="W7" s="97" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="95" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C8" s="102" t="inlineStr"/>
+      <c r="D8" s="106" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="F8" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D8" s="94" t="inlineStr"/>
-      <c r="E8" s="94" t="n"/>
-      <c r="F8" s="94" t="n"/>
-      <c r="G8" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G8" s="94" t="inlineStr"/>
       <c r="H8" s="94" t="n"/>
       <c r="I8" s="94" t="n"/>
       <c r="J8" s="94" t="inlineStr">
@@ -1415,11 +1489,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K8" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K8" s="94" t="n"/>
       <c r="L8" s="94" t="n"/>
       <c r="M8" s="94" t="inlineStr">
         <is>
@@ -1431,143 +1501,161 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O8" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O8" s="94" t="n"/>
       <c r="P8" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="94" t="n"/>
+      <c r="Q8" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R8" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="94" t="n"/>
-      <c r="T8" s="94" t="inlineStr">
+      <c r="S8" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T8" s="94" t="n"/>
+      <c r="U8" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="94" t="n"/>
+      <c r="W8" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="97" t="inlineStr">
         <is>
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C9" s="100" t="inlineStr"/>
+      <c r="D9" s="105" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="F9" s="97" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D9" s="92" t="inlineStr"/>
-      <c r="E9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L9" s="92" t="n"/>
-      <c r="M9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T9" s="92" t="inlineStr">
+      <c r="G9" s="97" t="inlineStr"/>
+      <c r="H9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O9" s="97" t="n"/>
+      <c r="P9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W9" s="97" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="95" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="102" t="inlineStr"/>
+      <c r="C10" s="102" t="inlineStr"/>
+      <c r="D10" s="106" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="F10" s="94" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="D10" s="94" t="inlineStr"/>
-      <c r="E10" s="94" t="n"/>
-      <c r="F10" s="94" t="n"/>
-      <c r="G10" s="94" t="n"/>
+      <c r="G10" s="94" t="inlineStr"/>
       <c r="H10" s="94" t="n"/>
       <c r="I10" s="94" t="n"/>
       <c r="J10" s="94" t="n"/>
@@ -1575,127 +1663,137 @@
       <c r="L10" s="94" t="n"/>
       <c r="M10" s="94" t="n"/>
       <c r="N10" s="94" t="n"/>
-      <c r="O10" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O10" s="94" t="n"/>
       <c r="P10" s="94" t="n"/>
       <c r="Q10" s="94" t="n"/>
-      <c r="R10" s="94" t="n"/>
+      <c r="R10" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S10" s="94" t="n"/>
       <c r="T10" s="94" t="n"/>
+      <c r="U10" s="94" t="n"/>
+      <c r="V10" s="94" t="n"/>
+      <c r="W10" s="94" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="inlineStr"/>
+      <c r="D11" s="105" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="F11" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D11" s="92" t="inlineStr"/>
-      <c r="E11" s="92" t="n"/>
-      <c r="F11" s="92" t="n"/>
-      <c r="G11" s="92" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="92" t="n"/>
-      <c r="J11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L11" s="92" t="n"/>
-      <c r="M11" s="92" t="n"/>
-      <c r="N11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T11" s="92" t="inlineStr">
+      <c r="G11" s="97" t="inlineStr"/>
+      <c r="H11" s="97" t="n"/>
+      <c r="I11" s="97" t="n"/>
+      <c r="J11" s="97" t="n"/>
+      <c r="K11" s="97" t="n"/>
+      <c r="L11" s="97" t="n"/>
+      <c r="M11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O11" s="97" t="n"/>
+      <c r="P11" s="97" t="n"/>
+      <c r="Q11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W11" s="97" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="95" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="102" t="inlineStr"/>
+      <c r="C12" s="102" t="inlineStr"/>
+      <c r="D12" s="106" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="F12" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D12" s="94" t="inlineStr"/>
-      <c r="E12" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F12" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G12" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G12" s="94" t="inlineStr"/>
       <c r="H12" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I12" s="94" t="n"/>
-      <c r="J12" s="94" t="n"/>
-      <c r="K12" s="94" t="n"/>
+      <c r="I12" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J12" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K12" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L12" s="94" t="n"/>
       <c r="M12" s="94" t="n"/>
       <c r="N12" s="94" t="n"/>
@@ -1705,69 +1803,75 @@
       <c r="R12" s="94" t="n"/>
       <c r="S12" s="94" t="n"/>
       <c r="T12" s="94" t="n"/>
+      <c r="U12" s="94" t="n"/>
+      <c r="V12" s="94" t="n"/>
+      <c r="W12" s="94" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="97" t="inlineStr">
         <is>
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="100" t="inlineStr"/>
+      <c r="C13" s="100" t="inlineStr"/>
+      <c r="D13" s="105" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="F13" s="97" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="D13" s="92" t="inlineStr"/>
-      <c r="E13" s="92" t="n"/>
-      <c r="F13" s="92" t="n"/>
-      <c r="G13" s="92" t="n"/>
-      <c r="H13" s="92" t="n"/>
-      <c r="I13" s="92" t="n"/>
-      <c r="J13" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K13" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L13" s="92" t="n"/>
-      <c r="M13" s="92" t="n"/>
-      <c r="N13" s="92" t="n"/>
-      <c r="O13" s="92" t="n"/>
-      <c r="P13" s="92" t="n"/>
-      <c r="Q13" s="92" t="n"/>
-      <c r="R13" s="92" t="n"/>
-      <c r="S13" s="92" t="n"/>
-      <c r="T13" s="92" t="n"/>
+      <c r="G13" s="97" t="inlineStr"/>
+      <c r="H13" s="97" t="n"/>
+      <c r="I13" s="97" t="n"/>
+      <c r="J13" s="97" t="n"/>
+      <c r="K13" s="97" t="n"/>
+      <c r="L13" s="97" t="n"/>
+      <c r="M13" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N13" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O13" s="97" t="n"/>
+      <c r="P13" s="97" t="n"/>
+      <c r="Q13" s="97" t="n"/>
+      <c r="R13" s="97" t="n"/>
+      <c r="S13" s="97" t="n"/>
+      <c r="T13" s="97" t="n"/>
+      <c r="U13" s="97" t="n"/>
+      <c r="V13" s="97" t="n"/>
+      <c r="W13" s="97" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="95" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="102" t="inlineStr"/>
+      <c r="C14" s="102" t="inlineStr"/>
+      <c r="D14" s="106" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="F14" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D14" s="94" t="inlineStr"/>
-      <c r="E14" s="94" t="n"/>
-      <c r="F14" s="94" t="n"/>
-      <c r="G14" s="94" t="n"/>
+      <c r="G14" s="94" t="inlineStr"/>
       <c r="H14" s="94" t="n"/>
       <c r="I14" s="94" t="n"/>
       <c r="J14" s="94" t="n"/>
@@ -1780,89 +1884,99 @@
       <c r="Q14" s="94" t="n"/>
       <c r="R14" s="94" t="n"/>
       <c r="S14" s="94" t="n"/>
-      <c r="T14" s="94" t="inlineStr">
+      <c r="T14" s="94" t="n"/>
+      <c r="U14" s="94" t="n"/>
+      <c r="V14" s="94" t="n"/>
+      <c r="W14" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C15" s="100" t="inlineStr"/>
+      <c r="D15" s="105" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="F15" s="97" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D15" s="92" t="inlineStr"/>
-      <c r="E15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="92" t="n"/>
-      <c r="G15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H15" s="92" t="n"/>
-      <c r="I15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L15" s="92" t="n"/>
-      <c r="M15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N15" s="92" t="n"/>
-      <c r="O15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T15" s="92" t="n"/>
+      <c r="G15" s="97" t="inlineStr"/>
+      <c r="H15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K15" s="97" t="n"/>
+      <c r="L15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O15" s="97" t="n"/>
+      <c r="P15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="97" t="n"/>
+      <c r="R15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W15" s="97" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="94" t="inlineStr">
@@ -1870,24 +1984,24 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C16" s="102" t="inlineStr"/>
+      <c r="D16" s="106" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="F16" s="94" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="D16" s="94" t="inlineStr"/>
-      <c r="E16" s="94" t="n"/>
-      <c r="F16" s="94" t="n"/>
-      <c r="G16" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G16" s="94" t="inlineStr"/>
       <c r="H16" s="94" t="n"/>
       <c r="I16" s="94" t="n"/>
       <c r="J16" s="94" t="inlineStr">
@@ -1897,111 +2011,113 @@
       </c>
       <c r="K16" s="94" t="n"/>
       <c r="L16" s="94" t="n"/>
-      <c r="M16" s="94" t="n"/>
+      <c r="M16" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N16" s="94" t="n"/>
-      <c r="O16" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P16" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O16" s="94" t="n"/>
+      <c r="P16" s="94" t="n"/>
+      <c r="Q16" s="94" t="n"/>
       <c r="R16" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="94" t="n"/>
+      <c r="S16" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T16" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U16" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="94" t="n"/>
+      <c r="W16" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="inlineStr">
+      <c r="A17" s="97" t="inlineStr">
         <is>
           <t>From The Start</t>
         </is>
       </c>
-      <c r="B17" s="92" t="inlineStr">
+      <c r="B17" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C17" s="100" t="inlineStr"/>
+      <c r="D17" s="105" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="F17" s="97" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="D17" s="92" t="inlineStr"/>
-      <c r="E17" s="92" t="n"/>
-      <c r="F17" s="92" t="n"/>
-      <c r="G17" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H17" s="92" t="n"/>
-      <c r="I17" s="92" t="n"/>
-      <c r="J17" s="92" t="n"/>
-      <c r="K17" s="92" t="n"/>
-      <c r="L17" s="92" t="n"/>
-      <c r="M17" s="92" t="n"/>
-      <c r="N17" s="92" t="n"/>
-      <c r="O17" s="92" t="n"/>
-      <c r="P17" s="92" t="n"/>
-      <c r="Q17" s="92" t="n"/>
-      <c r="R17" s="92" t="n"/>
-      <c r="S17" s="92" t="n"/>
-      <c r="T17" s="92" t="n"/>
+      <c r="G17" s="97" t="inlineStr"/>
+      <c r="H17" s="97" t="n"/>
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K17" s="97" t="n"/>
+      <c r="L17" s="97" t="n"/>
+      <c r="M17" s="97" t="n"/>
+      <c r="N17" s="97" t="n"/>
+      <c r="O17" s="97" t="n"/>
+      <c r="P17" s="97" t="n"/>
+      <c r="Q17" s="97" t="n"/>
+      <c r="R17" s="97" t="n"/>
+      <c r="S17" s="97" t="n"/>
+      <c r="T17" s="97" t="n"/>
+      <c r="U17" s="97" t="n"/>
+      <c r="V17" s="97" t="n"/>
+      <c r="W17" s="97" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="95" t="inlineStr">
+      <c r="A18" s="94" t="inlineStr">
         <is>
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B18" s="102" t="inlineStr"/>
+      <c r="C18" s="102" t="inlineStr"/>
+      <c r="D18" s="106" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="F18" s="94" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="D18" s="94" t="inlineStr"/>
-      <c r="E18" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="94" t="n"/>
-      <c r="G18" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G18" s="94" t="inlineStr"/>
       <c r="H18" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I18" s="94" t="n"/>
       <c r="J18" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2012,86 +2128,108 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L18" s="94" t="n"/>
-      <c r="M18" s="94" t="n"/>
-      <c r="N18" s="94" t="n"/>
+      <c r="L18" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M18" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N18" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O18" s="94" t="n"/>
       <c r="P18" s="94" t="n"/>
       <c r="Q18" s="94" t="n"/>
       <c r="R18" s="94" t="n"/>
       <c r="S18" s="94" t="n"/>
       <c r="T18" s="94" t="n"/>
+      <c r="U18" s="94" t="n"/>
+      <c r="V18" s="94" t="n"/>
+      <c r="W18" s="94" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="93" t="inlineStr">
+      <c r="A19" s="97" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C19" s="100" t="inlineStr"/>
+      <c r="D19" s="105" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="F19" s="97" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D19" s="92" t="inlineStr"/>
-      <c r="E19" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F19" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G19" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H19" s="92" t="n"/>
-      <c r="I19" s="92" t="n"/>
-      <c r="J19" s="92" t="n"/>
-      <c r="K19" s="92" t="n"/>
-      <c r="L19" s="92" t="n"/>
-      <c r="M19" s="92" t="n"/>
-      <c r="N19" s="92" t="n"/>
-      <c r="O19" s="92" t="n"/>
-      <c r="P19" s="92" t="n"/>
-      <c r="Q19" s="92" t="n"/>
-      <c r="R19" s="92" t="n"/>
-      <c r="S19" s="92" t="n"/>
-      <c r="T19" s="92" t="n"/>
+      <c r="G19" s="97" t="inlineStr"/>
+      <c r="H19" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J19" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K19" s="97" t="n"/>
+      <c r="L19" s="97" t="n"/>
+      <c r="M19" s="97" t="n"/>
+      <c r="N19" s="97" t="n"/>
+      <c r="O19" s="97" t="n"/>
+      <c r="P19" s="97" t="n"/>
+      <c r="Q19" s="97" t="n"/>
+      <c r="R19" s="97" t="n"/>
+      <c r="S19" s="97" t="n"/>
+      <c r="T19" s="97" t="n"/>
+      <c r="U19" s="97" t="n"/>
+      <c r="V19" s="97" t="n"/>
+      <c r="W19" s="97" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="95" t="inlineStr">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B20" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C20" s="102" t="inlineStr"/>
+      <c r="D20" s="106" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="F20" s="94" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D20" s="94" t="inlineStr"/>
-      <c r="E20" s="94" t="n"/>
-      <c r="F20" s="94" t="n"/>
-      <c r="G20" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G20" s="94" t="inlineStr"/>
       <c r="H20" s="94" t="n"/>
       <c r="I20" s="94" t="n"/>
       <c r="J20" s="94" t="inlineStr">
@@ -2099,30 +2237,26 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K20" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K20" s="94" t="n"/>
       <c r="L20" s="94" t="n"/>
-      <c r="M20" s="94" t="n"/>
-      <c r="N20" s="94" t="n"/>
-      <c r="O20" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P20" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="94" t="n"/>
+      <c r="M20" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N20" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O20" s="94" t="n"/>
+      <c r="P20" s="94" t="n"/>
+      <c r="Q20" s="94" t="n"/>
+      <c r="R20" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S20" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2133,78 +2267,88 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="U20" s="94" t="n"/>
+      <c r="V20" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="97" t="inlineStr">
         <is>
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
+      <c r="B21" s="100" t="inlineStr"/>
+      <c r="C21" s="100" t="inlineStr"/>
+      <c r="D21" s="105" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="F21" s="97" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D21" s="92" t="inlineStr"/>
-      <c r="E21" s="92" t="n"/>
-      <c r="F21" s="92" t="n"/>
-      <c r="G21" s="92" t="n"/>
-      <c r="H21" s="92" t="n"/>
-      <c r="I21" s="92" t="n"/>
-      <c r="J21" s="92" t="n"/>
-      <c r="K21" s="92" t="n"/>
-      <c r="L21" s="92" t="n"/>
-      <c r="M21" s="92" t="n"/>
-      <c r="N21" s="92" t="n"/>
-      <c r="O21" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P21" s="92" t="n"/>
-      <c r="Q21" s="92" t="n"/>
-      <c r="R21" s="92" t="n"/>
-      <c r="S21" s="92" t="n"/>
-      <c r="T21" s="92" t="n"/>
+      <c r="G21" s="97" t="inlineStr"/>
+      <c r="H21" s="97" t="n"/>
+      <c r="I21" s="97" t="n"/>
+      <c r="J21" s="97" t="n"/>
+      <c r="K21" s="97" t="n"/>
+      <c r="L21" s="97" t="n"/>
+      <c r="M21" s="97" t="n"/>
+      <c r="N21" s="97" t="n"/>
+      <c r="O21" s="97" t="n"/>
+      <c r="P21" s="97" t="n"/>
+      <c r="Q21" s="97" t="n"/>
+      <c r="R21" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="97" t="n"/>
+      <c r="T21" s="97" t="n"/>
+      <c r="U21" s="97" t="n"/>
+      <c r="V21" s="97" t="n"/>
+      <c r="W21" s="97" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="95" t="inlineStr">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C22" s="102" t="inlineStr"/>
+      <c r="D22" s="106" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="F22" s="94" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D22" s="94" t="inlineStr"/>
-      <c r="E22" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F22" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G22" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H22" s="94" t="n"/>
+      <c r="G22" s="94" t="inlineStr"/>
+      <c r="H22" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I22" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2215,12 +2359,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K22" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L22" s="94" t="n"/>
+      <c r="K22" s="94" t="n"/>
+      <c r="L22" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M22" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2231,11 +2375,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O22" s="94" t="n"/>
       <c r="P22" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2261,72 +2401,90 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="U22" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="93" t="inlineStr">
+      <c r="A23" s="97" t="inlineStr">
         <is>
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="92" t="inlineStr">
+      <c r="B23" s="100" t="inlineStr"/>
+      <c r="C23" s="100" t="inlineStr"/>
+      <c r="D23" s="105" t="inlineStr"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C23" s="92" t="inlineStr">
+      <c r="F23" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D23" s="92" t="inlineStr"/>
-      <c r="E23" s="92" t="n"/>
-      <c r="F23" s="92" t="n"/>
-      <c r="G23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H23" s="92" t="n"/>
-      <c r="I23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L23" s="92" t="n"/>
-      <c r="M23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P23" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" s="92" t="n"/>
-      <c r="R23" s="92" t="n"/>
-      <c r="S23" s="92" t="n"/>
-      <c r="T23" s="92" t="n"/>
+      <c r="G23" s="97" t="inlineStr"/>
+      <c r="H23" s="97" t="n"/>
+      <c r="I23" s="97" t="n"/>
+      <c r="J23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K23" s="97" t="n"/>
+      <c r="L23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O23" s="97" t="n"/>
+      <c r="P23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T23" s="97" t="n"/>
+      <c r="U23" s="97" t="n"/>
+      <c r="V23" s="97" t="n"/>
+      <c r="W23" s="97" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="94" t="inlineStr">
@@ -2334,24 +2492,24 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C24" s="102" t="inlineStr"/>
+      <c r="D24" s="106" t="inlineStr"/>
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="F24" s="94" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D24" s="94" t="inlineStr"/>
-      <c r="E24" s="94" t="n"/>
-      <c r="F24" s="94" t="n"/>
-      <c r="G24" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G24" s="94" t="inlineStr"/>
       <c r="H24" s="94" t="n"/>
       <c r="I24" s="94" t="n"/>
       <c r="J24" s="94" t="inlineStr">
@@ -2359,110 +2517,124 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K24" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K24" s="94" t="n"/>
       <c r="L24" s="94" t="n"/>
-      <c r="M24" s="94" t="n"/>
+      <c r="M24" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N24" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O24" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P24" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="94" t="n"/>
+      <c r="O24" s="94" t="n"/>
+      <c r="P24" s="94" t="n"/>
+      <c r="Q24" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R24" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="94" t="n"/>
+      <c r="S24" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T24" s="94" t="n"/>
+      <c r="U24" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="94" t="n"/>
+      <c r="W24" s="94" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="93" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="B25" s="92" t="inlineStr">
+      <c r="B25" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C25" s="100" t="inlineStr"/>
+      <c r="D25" s="105" t="inlineStr"/>
+      <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C25" s="92" t="inlineStr">
+      <c r="F25" s="97" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="D25" s="92" t="inlineStr"/>
-      <c r="E25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H25" s="92" t="n"/>
-      <c r="I25" s="92" t="n"/>
-      <c r="J25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L25" s="92" t="n"/>
-      <c r="M25" s="92" t="n"/>
-      <c r="N25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="92" t="n"/>
-      <c r="T25" s="92" t="n"/>
+      <c r="G25" s="97" t="inlineStr"/>
+      <c r="H25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K25" s="97" t="n"/>
+      <c r="L25" s="97" t="n"/>
+      <c r="M25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O25" s="97" t="n"/>
+      <c r="P25" s="97" t="n"/>
+      <c r="Q25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="97" t="n"/>
+      <c r="W25" s="97" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="94" t="inlineStr">
@@ -2470,27 +2642,31 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C26" s="102" t="inlineStr"/>
+      <c r="D26" s="106" t="inlineStr"/>
+      <c r="E26" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="F26" s="94" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="D26" s="94" t="inlineStr"/>
-      <c r="E26" s="94" t="n"/>
-      <c r="F26" s="94" t="n"/>
-      <c r="G26" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G26" s="94" t="inlineStr"/>
       <c r="H26" s="94" t="n"/>
       <c r="I26" s="94" t="n"/>
-      <c r="J26" s="94" t="n"/>
+      <c r="J26" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K26" s="94" t="n"/>
       <c r="L26" s="94" t="n"/>
       <c r="M26" s="94" t="n"/>
@@ -2501,52 +2677,62 @@
       <c r="R26" s="94" t="n"/>
       <c r="S26" s="94" t="n"/>
       <c r="T26" s="94" t="n"/>
+      <c r="U26" s="94" t="n"/>
+      <c r="V26" s="94" t="n"/>
+      <c r="W26" s="94" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="93" t="inlineStr">
+      <c r="A27" s="97" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="B27" s="92" t="inlineStr">
+      <c r="B27" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="100" t="inlineStr"/>
+      <c r="D27" s="105" t="inlineStr"/>
+      <c r="E27" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C27" s="92" t="inlineStr">
+      <c r="F27" s="97" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D27" s="92" t="inlineStr"/>
-      <c r="E27" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F27" s="92" t="n"/>
-      <c r="G27" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I27" s="92" t="n"/>
-      <c r="J27" s="92" t="n"/>
-      <c r="K27" s="92" t="n"/>
-      <c r="L27" s="92" t="n"/>
-      <c r="M27" s="92" t="n"/>
-      <c r="N27" s="92" t="n"/>
-      <c r="O27" s="92" t="n"/>
-      <c r="P27" s="92" t="n"/>
-      <c r="Q27" s="92" t="n"/>
-      <c r="R27" s="92" t="n"/>
-      <c r="S27" s="92" t="n"/>
-      <c r="T27" s="92" t="n"/>
+      <c r="G27" s="97" t="inlineStr"/>
+      <c r="H27" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I27" s="97" t="n"/>
+      <c r="J27" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K27" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L27" s="97" t="n"/>
+      <c r="M27" s="97" t="n"/>
+      <c r="N27" s="97" t="n"/>
+      <c r="O27" s="97" t="n"/>
+      <c r="P27" s="97" t="n"/>
+      <c r="Q27" s="97" t="n"/>
+      <c r="R27" s="97" t="n"/>
+      <c r="S27" s="97" t="n"/>
+      <c r="T27" s="97" t="n"/>
+      <c r="U27" s="97" t="n"/>
+      <c r="V27" s="97" t="n"/>
+      <c r="W27" s="97" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="94" t="inlineStr">
@@ -2554,29 +2740,25 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="B28" s="94" t="inlineStr">
+      <c r="B28" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C28" s="102" t="inlineStr"/>
+      <c r="D28" s="106" t="inlineStr"/>
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="F28" s="94" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D28" s="94" t="inlineStr"/>
-      <c r="E28" s="94" t="n"/>
-      <c r="F28" s="94" t="n"/>
-      <c r="G28" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H28" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G28" s="94" t="inlineStr"/>
+      <c r="H28" s="94" t="n"/>
       <c r="I28" s="94" t="n"/>
       <c r="J28" s="94" t="inlineStr">
         <is>
@@ -2599,11 +2781,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O28" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O28" s="94" t="n"/>
       <c r="P28" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2624,114 +2802,140 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T28" s="94" t="n"/>
+      <c r="T28" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="94" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="92" t="inlineStr">
+      <c r="A29" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="B29" s="92" t="inlineStr">
+      <c r="B29" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C29" s="100" t="inlineStr"/>
+      <c r="D29" s="105" t="inlineStr"/>
+      <c r="E29" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C29" s="92" t="inlineStr">
+      <c r="F29" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D29" s="92" t="inlineStr"/>
-      <c r="E29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L29" s="92" t="n"/>
-      <c r="M29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="92" t="n"/>
-      <c r="T29" s="92" t="n"/>
+      <c r="G29" s="97" t="inlineStr"/>
+      <c r="H29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O29" s="97" t="n"/>
+      <c r="P29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="97" t="n"/>
+      <c r="W29" s="97" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="95" t="inlineStr">
+      <c r="A30" s="94" t="inlineStr">
         <is>
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B30" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C30" s="102" t="inlineStr"/>
+      <c r="D30" s="106" t="inlineStr"/>
+      <c r="E30" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="F30" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D30" s="94" t="inlineStr"/>
-      <c r="E30" s="94" t="n"/>
-      <c r="F30" s="94" t="n"/>
-      <c r="G30" s="94" t="n"/>
+      <c r="G30" s="94" t="inlineStr"/>
       <c r="H30" s="94" t="n"/>
       <c r="I30" s="94" t="n"/>
       <c r="J30" s="94" t="n"/>
@@ -2739,111 +2943,113 @@
       <c r="L30" s="94" t="n"/>
       <c r="M30" s="94" t="n"/>
       <c r="N30" s="94" t="n"/>
-      <c r="O30" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O30" s="94" t="n"/>
       <c r="P30" s="94" t="n"/>
       <c r="Q30" s="94" t="n"/>
-      <c r="R30" s="94" t="n"/>
+      <c r="R30" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S30" s="94" t="n"/>
-      <c r="T30" s="94" t="inlineStr">
+      <c r="T30" s="94" t="n"/>
+      <c r="U30" s="94" t="n"/>
+      <c r="V30" s="94" t="n"/>
+      <c r="W30" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="92" t="inlineStr">
+      <c r="A31" s="97" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B31" s="92" t="inlineStr">
+      <c r="B31" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C31" s="100" t="inlineStr"/>
+      <c r="D31" s="105" t="inlineStr"/>
+      <c r="E31" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="C31" s="92" t="inlineStr">
+      <c r="F31" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D31" s="92" t="inlineStr"/>
-      <c r="E31" s="92" t="n"/>
-      <c r="F31" s="92" t="n"/>
-      <c r="G31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H31" s="92" t="n"/>
-      <c r="I31" s="92" t="n"/>
-      <c r="J31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K31" s="92" t="n"/>
-      <c r="L31" s="92" t="n"/>
-      <c r="M31" s="92" t="n"/>
-      <c r="N31" s="92" t="n"/>
-      <c r="O31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="92" t="n"/>
-      <c r="T31" s="92" t="n"/>
+      <c r="G31" s="97" t="inlineStr"/>
+      <c r="H31" s="97" t="n"/>
+      <c r="I31" s="97" t="n"/>
+      <c r="J31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K31" s="97" t="n"/>
+      <c r="L31" s="97" t="n"/>
+      <c r="M31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N31" s="97" t="n"/>
+      <c r="O31" s="97" t="n"/>
+      <c r="P31" s="97" t="n"/>
+      <c r="Q31" s="97" t="n"/>
+      <c r="R31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="97" t="n"/>
+      <c r="W31" s="97" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="95" t="inlineStr">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C32" s="102" t="inlineStr"/>
+      <c r="D32" s="106" t="inlineStr"/>
+      <c r="E32" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="F32" s="94" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="D32" s="94" t="inlineStr"/>
-      <c r="E32" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F32" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G32" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G32" s="94" t="inlineStr"/>
       <c r="H32" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2864,7 +3070,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L32" s="94" t="n"/>
+      <c r="L32" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M32" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2875,107 +3085,125 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O32" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P32" s="94" t="n"/>
-      <c r="Q32" s="94" t="n"/>
-      <c r="R32" s="94" t="n"/>
+      <c r="O32" s="94" t="n"/>
+      <c r="P32" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S32" s="94" t="n"/>
       <c r="T32" s="94" t="n"/>
+      <c r="U32" s="94" t="n"/>
+      <c r="V32" s="94" t="n"/>
+      <c r="W32" s="94" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="93" t="inlineStr">
+      <c r="A33" s="97" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="B33" s="92" t="inlineStr">
+      <c r="B33" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C33" s="100" t="inlineStr"/>
+      <c r="D33" s="105" t="inlineStr"/>
+      <c r="E33" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C33" s="92" t="inlineStr">
+      <c r="F33" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D33" s="92" t="inlineStr"/>
-      <c r="E33" s="92" t="n"/>
-      <c r="F33" s="92" t="n"/>
-      <c r="G33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H33" s="92" t="n"/>
-      <c r="I33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L33" s="92" t="n"/>
-      <c r="M33" s="92" t="n"/>
-      <c r="N33" s="92" t="n"/>
-      <c r="O33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="92" t="n"/>
-      <c r="R33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T33" s="92" t="n"/>
+      <c r="G33" s="97" t="inlineStr"/>
+      <c r="H33" s="97" t="n"/>
+      <c r="I33" s="97" t="n"/>
+      <c r="J33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K33" s="97" t="n"/>
+      <c r="L33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O33" s="97" t="n"/>
+      <c r="P33" s="97" t="n"/>
+      <c r="Q33" s="97" t="n"/>
+      <c r="R33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T33" s="97" t="n"/>
+      <c r="U33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="97" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="95" t="inlineStr">
+      <c r="A34" s="94" t="inlineStr">
         <is>
           <t>Rockin' In The Free World</t>
         </is>
       </c>
-      <c r="B34" s="94" t="inlineStr">
+      <c r="B34" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C34" s="102" t="inlineStr"/>
+      <c r="D34" s="106" t="inlineStr"/>
+      <c r="E34" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C34" s="94" t="inlineStr">
+      <c r="F34" s="94" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D34" s="94" t="inlineStr"/>
-      <c r="E34" s="94" t="n"/>
-      <c r="F34" s="94" t="n"/>
-      <c r="G34" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G34" s="94" t="inlineStr"/>
       <c r="H34" s="94" t="n"/>
       <c r="I34" s="94" t="n"/>
       <c r="J34" s="94" t="inlineStr">
@@ -2983,24 +3211,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K34" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K34" s="94" t="n"/>
       <c r="L34" s="94" t="n"/>
-      <c r="M34" s="94" t="n"/>
-      <c r="N34" s="94" t="n"/>
-      <c r="O34" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P34" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M34" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N34" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O34" s="94" t="n"/>
+      <c r="P34" s="94" t="n"/>
       <c r="Q34" s="94" t="n"/>
       <c r="R34" s="94" t="inlineStr">
         <is>
@@ -3013,91 +3237,101 @@
         </is>
       </c>
       <c r="T34" s="94" t="n"/>
+      <c r="U34" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="94" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="93" t="inlineStr">
+      <c r="A35" s="97" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="B35" s="92" t="inlineStr">
+      <c r="B35" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C35" s="100" t="inlineStr"/>
+      <c r="D35" s="105" t="inlineStr"/>
+      <c r="E35" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C35" s="92" t="inlineStr">
+      <c r="F35" s="97" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="D35" s="92" t="inlineStr"/>
-      <c r="E35" s="92" t="n"/>
-      <c r="F35" s="92" t="n"/>
-      <c r="G35" s="92" t="n"/>
-      <c r="H35" s="92" t="n"/>
-      <c r="I35" s="92" t="n"/>
-      <c r="J35" s="92" t="n"/>
-      <c r="K35" s="92" t="n"/>
-      <c r="L35" s="92" t="n"/>
-      <c r="M35" s="92" t="n"/>
-      <c r="N35" s="92" t="n"/>
-      <c r="O35" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P35" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="92" t="n"/>
-      <c r="R35" s="92" t="n"/>
-      <c r="S35" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T35" s="92" t="n"/>
+      <c r="G35" s="97" t="inlineStr"/>
+      <c r="H35" s="97" t="n"/>
+      <c r="I35" s="97" t="n"/>
+      <c r="J35" s="97" t="n"/>
+      <c r="K35" s="97" t="n"/>
+      <c r="L35" s="97" t="n"/>
+      <c r="M35" s="97" t="n"/>
+      <c r="N35" s="97" t="n"/>
+      <c r="O35" s="97" t="n"/>
+      <c r="P35" s="97" t="n"/>
+      <c r="Q35" s="97" t="n"/>
+      <c r="R35" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T35" s="97" t="n"/>
+      <c r="U35" s="97" t="n"/>
+      <c r="V35" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="97" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="95" t="inlineStr">
+      <c r="A36" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="B36" s="94" t="inlineStr">
+      <c r="B36" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C36" s="102" t="inlineStr"/>
+      <c r="D36" s="106" t="inlineStr"/>
+      <c r="E36" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C36" s="94" t="inlineStr">
+      <c r="F36" s="94" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D36" s="94" t="inlineStr"/>
-      <c r="E36" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F36" s="94" t="n"/>
-      <c r="G36" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G36" s="94" t="inlineStr"/>
       <c r="H36" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I36" s="94" t="n"/>
       <c r="J36" s="94" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3108,86 +3342,112 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L36" s="94" t="n"/>
+      <c r="L36" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M36" s="94" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" s="94" t="n"/>
+      <c r="N36" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O36" s="94" t="n"/>
-      <c r="P36" s="94" t="n"/>
+      <c r="P36" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q36" s="94" t="n"/>
       <c r="R36" s="94" t="n"/>
       <c r="S36" s="94" t="n"/>
       <c r="T36" s="94" t="n"/>
+      <c r="U36" s="94" t="n"/>
+      <c r="V36" s="94" t="n"/>
+      <c r="W36" s="94" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="92" t="inlineStr">
+      <c r="A37" s="97" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="B37" s="92" t="inlineStr">
+      <c r="B37" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C37" s="100" t="inlineStr"/>
+      <c r="D37" s="105" t="inlineStr"/>
+      <c r="E37" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C37" s="92" t="inlineStr">
+      <c r="F37" s="97" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="D37" s="92" t="inlineStr"/>
-      <c r="E37" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F37" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G37" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H37" s="92" t="n"/>
-      <c r="I37" s="92" t="n"/>
-      <c r="J37" s="92" t="n"/>
-      <c r="K37" s="92" t="n"/>
-      <c r="L37" s="92" t="n"/>
-      <c r="M37" s="92" t="n"/>
-      <c r="N37" s="92" t="n"/>
-      <c r="O37" s="92" t="n"/>
-      <c r="P37" s="92" t="n"/>
-      <c r="Q37" s="92" t="n"/>
-      <c r="R37" s="92" t="n"/>
-      <c r="S37" s="92" t="n"/>
-      <c r="T37" s="92" t="n"/>
+      <c r="G37" s="97" t="inlineStr"/>
+      <c r="H37" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J37" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K37" s="97" t="n"/>
+      <c r="L37" s="97" t="n"/>
+      <c r="M37" s="97" t="n"/>
+      <c r="N37" s="97" t="n"/>
+      <c r="O37" s="97" t="n"/>
+      <c r="P37" s="97" t="n"/>
+      <c r="Q37" s="97" t="n"/>
+      <c r="R37" s="97" t="n"/>
+      <c r="S37" s="97" t="n"/>
+      <c r="T37" s="97" t="n"/>
+      <c r="U37" s="97" t="n"/>
+      <c r="V37" s="97" t="n"/>
+      <c r="W37" s="97" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="95" t="inlineStr">
+      <c r="A38" s="94" t="inlineStr">
         <is>
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="B38" s="94" t="inlineStr">
+      <c r="B38" s="101" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C38" s="102" t="inlineStr"/>
+      <c r="D38" s="106" t="inlineStr"/>
+      <c r="E38" s="94" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="C38" s="94" t="inlineStr">
+      <c r="F38" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D38" s="94" t="inlineStr"/>
-      <c r="E38" s="94" t="n"/>
-      <c r="F38" s="94" t="n"/>
-      <c r="G38" s="94" t="n"/>
+      <c r="G38" s="94" t="inlineStr"/>
       <c r="H38" s="94" t="n"/>
       <c r="I38" s="94" t="n"/>
       <c r="J38" s="94" t="n"/>
@@ -3195,83 +3455,89 @@
       <c r="L38" s="94" t="n"/>
       <c r="M38" s="94" t="n"/>
       <c r="N38" s="94" t="n"/>
-      <c r="O38" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P38" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O38" s="94" t="n"/>
+      <c r="P38" s="94" t="n"/>
       <c r="Q38" s="94" t="n"/>
-      <c r="R38" s="94" t="n"/>
-      <c r="S38" s="94" t="n"/>
+      <c r="R38" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T38" s="94" t="n"/>
+      <c r="U38" s="94" t="n"/>
+      <c r="V38" s="94" t="n"/>
+      <c r="W38" s="94" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="93" t="inlineStr">
+      <c r="A39" s="97" t="inlineStr">
         <is>
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="B39" s="92" t="inlineStr">
+      <c r="B39" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C39" s="100" t="inlineStr"/>
+      <c r="D39" s="105" t="inlineStr"/>
+      <c r="E39" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C39" s="92" t="inlineStr">
+      <c r="F39" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D39" s="92" t="inlineStr"/>
-      <c r="E39" s="92" t="n"/>
-      <c r="F39" s="92" t="n"/>
-      <c r="G39" s="92" t="n"/>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I39" s="92" t="n"/>
-      <c r="J39" s="92" t="n"/>
-      <c r="K39" s="92" t="n"/>
-      <c r="L39" s="92" t="n"/>
-      <c r="M39" s="92" t="n"/>
-      <c r="N39" s="92" t="n"/>
-      <c r="O39" s="92" t="n"/>
-      <c r="P39" s="92" t="n"/>
-      <c r="Q39" s="92" t="n"/>
-      <c r="R39" s="92" t="n"/>
-      <c r="S39" s="92" t="n"/>
-      <c r="T39" s="92" t="n"/>
+      <c r="G39" s="97" t="inlineStr"/>
+      <c r="H39" s="97" t="n"/>
+      <c r="I39" s="97" t="n"/>
+      <c r="J39" s="97" t="n"/>
+      <c r="K39" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L39" s="97" t="n"/>
+      <c r="M39" s="97" t="n"/>
+      <c r="N39" s="97" t="n"/>
+      <c r="O39" s="97" t="n"/>
+      <c r="P39" s="97" t="n"/>
+      <c r="Q39" s="97" t="n"/>
+      <c r="R39" s="97" t="n"/>
+      <c r="S39" s="97" t="n"/>
+      <c r="T39" s="97" t="n"/>
+      <c r="U39" s="97" t="n"/>
+      <c r="V39" s="97" t="n"/>
+      <c r="W39" s="97" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="95" t="inlineStr">
+      <c r="A40" s="94" t="inlineStr">
         <is>
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B40" s="94" t="inlineStr">
+      <c r="B40" s="102" t="inlineStr"/>
+      <c r="C40" s="102" t="inlineStr"/>
+      <c r="D40" s="106" t="inlineStr"/>
+      <c r="E40" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C40" s="94" t="inlineStr">
+      <c r="F40" s="94" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="D40" s="94" t="inlineStr"/>
-      <c r="E40" s="94" t="n"/>
-      <c r="F40" s="94" t="n"/>
-      <c r="G40" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G40" s="94" t="inlineStr"/>
       <c r="H40" s="94" t="n"/>
       <c r="I40" s="94" t="n"/>
       <c r="J40" s="94" t="inlineStr">
@@ -3279,74 +3545,84 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K40" s="94" t="n"/>
       <c r="L40" s="94" t="n"/>
-      <c r="M40" s="94" t="n"/>
-      <c r="N40" s="94" t="n"/>
+      <c r="M40" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N40" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O40" s="94" t="n"/>
       <c r="P40" s="94" t="n"/>
       <c r="Q40" s="94" t="n"/>
       <c r="R40" s="94" t="n"/>
       <c r="S40" s="94" t="n"/>
       <c r="T40" s="94" t="n"/>
+      <c r="U40" s="94" t="n"/>
+      <c r="V40" s="94" t="n"/>
+      <c r="W40" s="94" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="92" t="inlineStr">
+      <c r="A41" s="97" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B41" s="92" t="inlineStr">
+      <c r="B41" s="100" t="inlineStr"/>
+      <c r="C41" s="100" t="inlineStr"/>
+      <c r="D41" s="105" t="inlineStr"/>
+      <c r="E41" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C41" s="92" t="inlineStr">
+      <c r="F41" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D41" s="92" t="inlineStr"/>
-      <c r="E41" s="92" t="n"/>
-      <c r="F41" s="92" t="n"/>
-      <c r="G41" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H41" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I41" s="92" t="n"/>
-      <c r="J41" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K41" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L41" s="92" t="n"/>
-      <c r="M41" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N41" s="92" t="n"/>
-      <c r="O41" s="92" t="n"/>
-      <c r="P41" s="92" t="n"/>
-      <c r="Q41" s="92" t="n"/>
-      <c r="R41" s="92" t="n"/>
-      <c r="S41" s="92" t="n"/>
-      <c r="T41" s="92" t="n"/>
+      <c r="G41" s="97" t="inlineStr"/>
+      <c r="H41" s="97" t="n"/>
+      <c r="I41" s="97" t="n"/>
+      <c r="J41" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K41" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L41" s="97" t="n"/>
+      <c r="M41" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N41" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O41" s="97" t="n"/>
+      <c r="P41" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="97" t="n"/>
+      <c r="R41" s="97" t="n"/>
+      <c r="S41" s="97" t="n"/>
+      <c r="T41" s="97" t="n"/>
+      <c r="U41" s="97" t="n"/>
+      <c r="V41" s="97" t="n"/>
+      <c r="W41" s="97" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="94" t="inlineStr">
@@ -3354,27 +3630,27 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
+      <c r="B42" s="102" t="inlineStr"/>
+      <c r="C42" s="102" t="inlineStr"/>
+      <c r="D42" s="106" t="inlineStr"/>
+      <c r="E42" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C42" s="94" t="inlineStr">
+      <c r="F42" s="94" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="D42" s="94" t="inlineStr"/>
-      <c r="E42" s="94" t="n"/>
-      <c r="F42" s="94" t="n"/>
-      <c r="G42" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G42" s="94" t="inlineStr"/>
       <c r="H42" s="94" t="n"/>
       <c r="I42" s="94" t="n"/>
-      <c r="J42" s="94" t="n"/>
+      <c r="J42" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K42" s="94" t="n"/>
       <c r="L42" s="94" t="n"/>
       <c r="M42" s="94" t="n"/>
@@ -3385,81 +3661,87 @@
       <c r="R42" s="94" t="n"/>
       <c r="S42" s="94" t="n"/>
       <c r="T42" s="94" t="n"/>
+      <c r="U42" s="94" t="n"/>
+      <c r="V42" s="94" t="n"/>
+      <c r="W42" s="94" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="93" t="inlineStr">
+      <c r="A43" s="97" t="inlineStr">
         <is>
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B43" s="92" t="inlineStr">
+      <c r="B43" s="100" t="inlineStr"/>
+      <c r="C43" s="100" t="inlineStr"/>
+      <c r="D43" s="105" t="inlineStr"/>
+      <c r="E43" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C43" s="92" t="inlineStr">
+      <c r="F43" s="97" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="D43" s="92" t="inlineStr"/>
-      <c r="E43" s="92" t="n"/>
-      <c r="F43" s="92" t="n"/>
-      <c r="G43" s="92" t="n"/>
-      <c r="H43" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I43" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J43" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K43" s="92" t="n"/>
-      <c r="L43" s="92" t="n"/>
-      <c r="M43" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N43" s="92" t="n"/>
-      <c r="O43" s="92" t="n"/>
-      <c r="P43" s="92" t="n"/>
-      <c r="Q43" s="92" t="n"/>
-      <c r="R43" s="92" t="n"/>
-      <c r="S43" s="92" t="n"/>
-      <c r="T43" s="92" t="n"/>
+      <c r="G43" s="97" t="inlineStr"/>
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="97" t="n"/>
+      <c r="J43" s="97" t="n"/>
+      <c r="K43" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L43" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M43" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N43" s="97" t="n"/>
+      <c r="O43" s="97" t="n"/>
+      <c r="P43" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="97" t="n"/>
+      <c r="R43" s="97" t="n"/>
+      <c r="S43" s="97" t="n"/>
+      <c r="T43" s="97" t="n"/>
+      <c r="U43" s="97" t="n"/>
+      <c r="V43" s="97" t="n"/>
+      <c r="W43" s="97" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="95" t="inlineStr">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B44" s="94" t="inlineStr">
+      <c r="B44" s="102" t="inlineStr"/>
+      <c r="C44" s="102" t="inlineStr"/>
+      <c r="D44" s="106" t="inlineStr"/>
+      <c r="E44" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C44" s="94" t="inlineStr">
+      <c r="F44" s="94" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D44" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E44" s="94" t="n"/>
-      <c r="F44" s="94" t="n"/>
-      <c r="G44" s="94" t="n"/>
+      <c r="G44" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H44" s="94" t="n"/>
       <c r="I44" s="94" t="n"/>
       <c r="J44" s="94" t="n"/>
@@ -3473,96 +3755,106 @@
       <c r="R44" s="94" t="n"/>
       <c r="S44" s="94" t="n"/>
       <c r="T44" s="94" t="n"/>
+      <c r="U44" s="94" t="n"/>
+      <c r="V44" s="94" t="n"/>
+      <c r="W44" s="94" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="92" t="inlineStr">
+      <c r="A45" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="B45" s="92" t="inlineStr">
+      <c r="B45" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C45" s="100" t="inlineStr"/>
+      <c r="D45" s="105" t="inlineStr"/>
+      <c r="E45" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="C45" s="92" t="inlineStr">
+      <c r="F45" s="97" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D45" s="92" t="inlineStr"/>
-      <c r="E45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L45" s="92" t="n"/>
-      <c r="M45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T45" s="92" t="inlineStr">
+      <c r="G45" s="97" t="inlineStr"/>
+      <c r="H45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O45" s="97" t="n"/>
+      <c r="P45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W45" s="97" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3574,29 +3866,29 @@
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
+      <c r="B46" s="102" t="inlineStr"/>
+      <c r="C46" s="102" t="inlineStr"/>
+      <c r="D46" s="106" t="inlineStr"/>
+      <c r="E46" s="94" t="inlineStr">
         <is>
           <t>Instrumental</t>
         </is>
       </c>
-      <c r="C46" s="94" t="inlineStr">
+      <c r="F46" s="94" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="D46" s="94" t="inlineStr"/>
-      <c r="E46" s="94" t="n"/>
-      <c r="F46" s="94" t="n"/>
-      <c r="G46" s="94" t="n"/>
+      <c r="G46" s="94" t="inlineStr"/>
       <c r="H46" s="94" t="n"/>
-      <c r="I46" s="94" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I46" s="94" t="n"/>
       <c r="J46" s="94" t="n"/>
       <c r="K46" s="94" t="n"/>
-      <c r="L46" s="94" t="n"/>
+      <c r="L46" s="94" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M46" s="94" t="n"/>
       <c r="N46" s="94" t="n"/>
       <c r="O46" s="94" t="n"/>
@@ -3605,72 +3897,82 @@
       <c r="R46" s="94" t="n"/>
       <c r="S46" s="94" t="n"/>
       <c r="T46" s="94" t="n"/>
+      <c r="U46" s="94" t="n"/>
+      <c r="V46" s="94" t="n"/>
+      <c r="W46" s="94" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="92" t="inlineStr">
+      <c r="A47" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="B47" s="92" t="inlineStr">
+      <c r="B47" s="103" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C47" s="100" t="inlineStr"/>
+      <c r="D47" s="105" t="inlineStr"/>
+      <c r="E47" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="C47" s="92" t="inlineStr">
+      <c r="F47" s="97" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="D47" s="92" t="inlineStr"/>
-      <c r="E47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F47" s="92" t="n"/>
-      <c r="G47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H47" s="92" t="n"/>
-      <c r="I47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K47" s="92" t="n"/>
-      <c r="L47" s="92" t="n"/>
-      <c r="M47" s="92" t="n"/>
-      <c r="N47" s="92" t="n"/>
-      <c r="O47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="92" t="n"/>
-      <c r="R47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="92" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T47" s="92" t="inlineStr">
+      <c r="G47" s="97" t="inlineStr"/>
+      <c r="H47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I47" s="97" t="n"/>
+      <c r="J47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K47" s="97" t="n"/>
+      <c r="L47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N47" s="97" t="n"/>
+      <c r="O47" s="97" t="n"/>
+      <c r="P47" s="97" t="n"/>
+      <c r="Q47" s="97" t="n"/>
+      <c r="R47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T47" s="97" t="n"/>
+      <c r="U47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="97" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W47" s="97" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3678,37 +3980,362 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-02 — Lincolnwood PTA Spring Fling</t>
+        </is>
+      </c>
+      <c r="B1" s="72" t="n"/>
+      <c r="C1" s="73" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="98" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="98" t="inlineStr">
+        <is>
+          <t>Vocals</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="97" t="inlineStr">
+        <is>
+          <t>opener</t>
+        </is>
+      </c>
+      <c r="B3" s="96" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="C3" s="97" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="95" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="97" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="96" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C5" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>Head Over Heels</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="97" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="96" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C7" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="97" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="97" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C13" s="97" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="97" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="95" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="97" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="97" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="95" t="inlineStr">
+        <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="97" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="96" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C19" s="97" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3732,32 +4359,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -3779,15 +4406,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -3809,15 +4436,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -3839,15 +4466,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -3869,15 +4496,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -3914,7 +4541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3938,32 +4565,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -3985,15 +4612,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4015,15 +4642,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4045,15 +4672,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4075,15 +4702,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>From the Start</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4105,15 +4732,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>No One to Depend On</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4135,15 +4762,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4165,15 +4792,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4195,15 +4822,15 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
+      <c r="A19" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4225,15 +4852,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="n">
+      <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4255,15 +4882,15 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="92" t="n">
+      <c r="A23" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Kings of Ewing</t>
         </is>
       </c>
-      <c r="C23" s="92" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4285,15 +4912,15 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="92" t="n">
+      <c r="A25" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="93" t="inlineStr">
+      <c r="B25" s="96" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C25" s="92" t="inlineStr">
+      <c r="C25" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4315,15 +4942,15 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="92" t="n">
+      <c r="A27" s="97" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="93" t="inlineStr">
+      <c r="B27" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C27" s="92" t="inlineStr">
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4345,15 +4972,15 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="92" t="n">
+      <c r="A29" s="97" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="93" t="inlineStr">
+      <c r="B29" s="96" t="inlineStr">
         <is>
           <t>Message in a Bottle</t>
         </is>
       </c>
-      <c r="C29" s="92" t="inlineStr">
+      <c r="C29" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4375,15 +5002,15 @@
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="92" t="n">
+      <c r="A31" s="97" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="93" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C31" s="92" t="inlineStr">
+      <c r="C31" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4405,15 +5032,15 @@
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="92" t="n">
+      <c r="A33" s="97" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="92" t="inlineStr">
+      <c r="B33" s="97" t="inlineStr">
         <is>
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C33" s="92" t="inlineStr">
+      <c r="C33" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4452,7 +5079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4476,32 +5103,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4523,15 +5150,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4553,15 +5180,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4583,15 +5210,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4613,15 +5240,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4643,15 +5270,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4673,15 +5300,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4703,7 +5330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4727,32 +5354,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4774,15 +5401,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4804,15 +5431,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4834,15 +5461,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4864,15 +5491,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4894,15 +5521,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4924,15 +5551,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4969,7 +5596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4993,32 +5620,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5040,15 +5667,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5070,15 +5697,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5100,15 +5727,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5130,15 +5757,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5160,15 +5787,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5190,15 +5817,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5220,15 +5847,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5250,15 +5877,15 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
+      <c r="A19" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5280,15 +5907,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="n">
+      <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -5310,15 +5937,15 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="92" t="n">
+      <c r="A23" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C23" s="92" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5340,15 +5967,15 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="92" t="n">
+      <c r="A25" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="93" t="inlineStr">
+      <c r="B25" s="96" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C25" s="92" t="inlineStr">
+      <c r="C25" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5370,15 +5997,15 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="92" t="n">
+      <c r="A27" s="97" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="92" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C27" s="92" t="inlineStr">
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5400,15 +6027,15 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="92" t="n">
+      <c r="A29" s="97" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="93" t="inlineStr">
+      <c r="B29" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C29" s="92" t="inlineStr">
+      <c r="C29" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5457,7 +6084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5481,32 +6108,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5528,15 +6155,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5558,15 +6185,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5588,15 +6215,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
@@ -5618,15 +6245,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5648,15 +6275,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5678,15 +6305,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5708,15 +6335,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -5738,15 +6365,15 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
+      <c r="A19" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="93" t="inlineStr">
+      <c r="B19" s="96" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5768,15 +6395,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="n">
+      <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5821,7 +6448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5845,17 +6472,17 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -5866,7 +6493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5890,32 +6517,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5937,15 +6564,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5967,15 +6594,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -5997,15 +6624,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6027,15 +6654,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -6057,15 +6684,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6087,15 +6714,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6136,7 +6763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6160,32 +6787,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -6207,15 +6834,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6237,15 +6864,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6267,15 +6894,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6297,15 +6924,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6327,15 +6954,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6358,479 +6985,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="87" t="inlineStr">
-        <is>
-          <t>2024-09-07 — Ewing Block Party</t>
-        </is>
-      </c>
-      <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>Song</t>
-        </is>
-      </c>
-      <c r="C2" s="89" t="inlineStr">
-        <is>
-          <t>Vocals</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="93" t="inlineStr">
-        <is>
-          <t>Don'T Let Me Down</t>
-        </is>
-      </c>
-      <c r="C3" s="92" t="inlineStr">
-        <is>
-          <t>Miles / Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="94" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="95" t="inlineStr">
-        <is>
-          <t>Won't Back Down</t>
-        </is>
-      </c>
-      <c r="C4" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>No One To Depend On</t>
-        </is>
-      </c>
-      <c r="C5" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Found Out About You</t>
-        </is>
-      </c>
-      <c r="C6" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="93" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="C7" s="92" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="94" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="95" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="C8" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="93" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="C9" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="94" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="93" t="inlineStr">
-        <is>
-          <t>Octopus's Garden</t>
-        </is>
-      </c>
-      <c r="C11" s="92" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="94" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="95" t="inlineStr">
-        <is>
-          <t>Down By The River</t>
-        </is>
-      </c>
-      <c r="C12" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="93" t="inlineStr">
-        <is>
-          <t>Kings Of Ewing</t>
-        </is>
-      </c>
-      <c r="C13" s="92" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="94" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="95" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="C14" s="94" t="inlineStr">
-        <is>
-          <t>Miles / Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="93" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="C15" s="92" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="94" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="95" t="inlineStr">
-        <is>
-          <t>Sympathy For The Devil</t>
-        </is>
-      </c>
-      <c r="C16" s="94" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="92" t="inlineStr">
-        <is>
-          <t>Just What I Needed</t>
-        </is>
-      </c>
-      <c r="C17" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="94" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="94" t="inlineStr">
-        <is>
-          <t>I'Ve Got A Feeling</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
-        <is>
-          <t>Miles / Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="92" t="inlineStr">
-        <is>
-          <t>Don'T Look Back In Anger</t>
-        </is>
-      </c>
-      <c r="C19" s="92" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="94" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="95" t="inlineStr">
-        <is>
-          <t>Riders On The Storm</t>
-        </is>
-      </c>
-      <c r="C20" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="93" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C21" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="94" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="95" t="inlineStr">
-        <is>
-          <t>Seven Nation Army</t>
-        </is>
-      </c>
-      <c r="C22" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="92" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="93" t="inlineStr">
-        <is>
-          <t>Dedicated Follower Of Fashion</t>
-        </is>
-      </c>
-      <c r="C23" s="92" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="94" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="95" t="inlineStr">
-        <is>
-          <t>Midnight Rider</t>
-        </is>
-      </c>
-      <c r="C24" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="92" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="93" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C25" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="94" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="95" t="inlineStr">
-        <is>
-          <t>Rockin' in the Free World</t>
-        </is>
-      </c>
-      <c r="C26" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="92" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="93" t="inlineStr">
-        <is>
-          <t>Heroes</t>
-        </is>
-      </c>
-      <c r="C27" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="94" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="94" t="inlineStr">
-        <is>
-          <t>Voodoo Child</t>
-        </is>
-      </c>
-      <c r="C28" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId22"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -6847,90 +7015,96 @@
       <c r="B1" s="72" t="n"/>
       <c r="C1" s="72" t="n"/>
       <c r="D1" s="72" t="n"/>
-      <c r="E1" s="72" t="n"/>
       <c r="F1" s="72" t="n"/>
       <c r="G1" s="72" t="n"/>
       <c r="H1" s="72" t="n"/>
       <c r="I1" s="72" t="n"/>
-      <c r="J1" s="73" t="n"/>
+      <c r="J1" s="72" t="n"/>
+      <c r="K1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D2" s="89" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t># Songs</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
+      <c r="E2" s="104" t="inlineStr">
+        <is>
+          <t>Gig Length</t>
+        </is>
+      </c>
+      <c r="F2" s="98" t="inlineStr">
         <is>
           <t>Venue Name</t>
         </is>
       </c>
-      <c r="F2" s="89" t="inlineStr">
+      <c r="G2" s="98" t="inlineStr">
         <is>
           <t>Venue Email</t>
         </is>
       </c>
-      <c r="G2" s="89" t="inlineStr">
+      <c r="H2" s="98" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="H2" s="89" t="inlineStr">
+      <c r="I2" s="98" t="inlineStr">
         <is>
           <t>Event Email</t>
         </is>
       </c>
-      <c r="I2" s="89" t="inlineStr">
+      <c r="J2" s="98" t="inlineStr">
         <is>
           <t>Pay</t>
         </is>
       </c>
-      <c r="J2" s="89" t="inlineStr">
+      <c r="K2" s="98" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="96" t="inlineStr">
         <is>
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Block Party</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Ewing Block Party</t>
         </is>
       </c>
-      <c r="D3" s="92" t="n">
+      <c r="D3" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="92" t="n"/>
-      <c r="F3" s="92" t="n"/>
-      <c r="G3" s="92" t="n"/>
-      <c r="H3" s="92" t="n"/>
-      <c r="I3" s="92" t="n"/>
-      <c r="J3" s="92" t="n"/>
+      <c r="E3" s="105" t="inlineStr"/>
+      <c r="F3" s="97" t="n"/>
+      <c r="G3" s="97" t="n"/>
+      <c r="H3" s="97" t="n"/>
+      <c r="I3" s="97" t="n"/>
+      <c r="J3" s="97" t="n"/>
+      <c r="K3" s="97" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="95" t="inlineStr">
@@ -6951,42 +7125,44 @@
       <c r="D4" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="94" t="n"/>
+      <c r="E4" s="106" t="inlineStr"/>
       <c r="F4" s="94" t="n"/>
       <c r="G4" s="94" t="n"/>
       <c r="H4" s="94" t="n"/>
       <c r="I4" s="94" t="n"/>
       <c r="J4" s="94" t="n"/>
+      <c r="K4" s="94" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="93" t="inlineStr">
+      <c r="A5" s="96" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="C5" s="92" t="n"/>
-      <c r="D5" s="92" t="n">
+      <c r="C5" s="97" t="n"/>
+      <c r="D5" s="97" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="92" t="inlineStr">
+      <c r="E5" s="105" t="inlineStr"/>
+      <c r="F5" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F5" s="92" t="inlineStr">
+      <c r="G5" s="97" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G5" s="92" t="n"/>
-      <c r="H5" s="92" t="n"/>
-      <c r="I5" s="92" t="n"/>
-      <c r="J5" s="92" t="n"/>
+      <c r="H5" s="97" t="n"/>
+      <c r="I5" s="97" t="n"/>
+      <c r="J5" s="97" t="n"/>
+      <c r="K5" s="97" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
@@ -7007,54 +7183,56 @@
       <c r="D6" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="94" t="inlineStr">
+      <c r="E6" s="106" t="inlineStr"/>
+      <c r="F6" s="94" t="inlineStr">
         <is>
           <t>J.A. Cohen (Jeff)</t>
         </is>
       </c>
-      <c r="F6" s="94" t="inlineStr">
+      <c r="G6" s="94" t="inlineStr">
         <is>
           <t>jacohenmusic@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="94" t="n"/>
       <c r="H6" s="94" t="n"/>
       <c r="I6" s="94" t="n"/>
-      <c r="J6" s="94" t="inlineStr">
+      <c r="J6" s="94" t="n"/>
+      <c r="K6" s="94" t="inlineStr">
         <is>
           <t>~1 hr set starting ~1 hr before game time. Now at ETHS Lazier Field.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="96" t="inlineStr">
         <is>
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="C7" s="92" t="n"/>
-      <c r="D7" s="92" t="n">
+      <c r="C7" s="97" t="n"/>
+      <c r="D7" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="E7" s="92" t="inlineStr">
+      <c r="E7" s="105" t="inlineStr"/>
+      <c r="F7" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F7" s="92" t="inlineStr">
+      <c r="G7" s="97" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G7" s="92" t="n"/>
-      <c r="H7" s="92" t="n"/>
-      <c r="I7" s="92" t="n"/>
-      <c r="J7" s="92" t="n"/>
+      <c r="H7" s="97" t="n"/>
+      <c r="I7" s="97" t="n"/>
+      <c r="J7" s="97" t="n"/>
+      <c r="K7" s="97" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="95" t="inlineStr">
@@ -7075,46 +7253,48 @@
       <c r="D8" s="94" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="94" t="n"/>
+      <c r="E8" s="106" t="inlineStr"/>
       <c r="F8" s="94" t="n"/>
       <c r="G8" s="94" t="n"/>
       <c r="H8" s="94" t="n"/>
       <c r="I8" s="94" t="n"/>
       <c r="J8" s="94" t="n"/>
+      <c r="K8" s="94" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="96" t="inlineStr">
         <is>
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Covenant Nursery Dining for Dollars</t>
         </is>
       </c>
-      <c r="D9" s="92" t="n">
+      <c r="D9" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="E9" s="92" t="inlineStr">
+      <c r="E9" s="105" t="inlineStr"/>
+      <c r="F9" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F9" s="92" t="inlineStr">
+      <c r="G9" s="97" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G9" s="92" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="92" t="n"/>
-      <c r="J9" s="92" t="n"/>
+      <c r="H9" s="97" t="n"/>
+      <c r="I9" s="97" t="n"/>
+      <c r="J9" s="97" t="n"/>
+      <c r="K9" s="97" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="95" t="inlineStr">
@@ -7135,32 +7315,34 @@
       <c r="D10" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="94" t="n"/>
+      <c r="E10" s="106" t="inlineStr"/>
       <c r="F10" s="94" t="n"/>
       <c r="G10" s="94" t="n"/>
       <c r="H10" s="94" t="n"/>
       <c r="I10" s="94" t="n"/>
       <c r="J10" s="94" t="n"/>
+      <c r="K10" s="94" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="96" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Post 42</t>
         </is>
       </c>
-      <c r="C11" s="92" t="n"/>
-      <c r="D11" s="92" t="n"/>
-      <c r="E11" s="92" t="n"/>
-      <c r="F11" s="92" t="n"/>
-      <c r="G11" s="92" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="92" t="n"/>
-      <c r="J11" s="92" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="97" t="n"/>
+      <c r="E11" s="105" t="inlineStr"/>
+      <c r="F11" s="97" t="n"/>
+      <c r="G11" s="97" t="n"/>
+      <c r="H11" s="97" t="n"/>
+      <c r="I11" s="97" t="n"/>
+      <c r="J11" s="97" t="n"/>
+      <c r="K11" s="97" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="95" t="inlineStr">
@@ -7177,42 +7359,44 @@
       <c r="D12" s="94" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="94" t="inlineStr">
+      <c r="E12" s="106" t="inlineStr"/>
+      <c r="F12" s="94" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F12" s="94" t="inlineStr">
+      <c r="G12" s="94" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G12" s="94" t="n"/>
       <c r="H12" s="94" t="n"/>
       <c r="I12" s="94" t="n"/>
       <c r="J12" s="94" t="n"/>
+      <c r="K12" s="94" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="93" t="inlineStr">
+      <c r="A13" s="96" t="inlineStr">
         <is>
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>American Legion</t>
         </is>
       </c>
-      <c r="C13" s="92" t="n"/>
-      <c r="D13" s="92" t="n">
+      <c r="C13" s="97" t="n"/>
+      <c r="D13" s="97" t="n">
         <v>28</v>
       </c>
-      <c r="E13" s="92" t="n"/>
-      <c r="F13" s="92" t="n"/>
-      <c r="G13" s="92" t="n"/>
-      <c r="H13" s="92" t="n"/>
-      <c r="I13" s="92" t="n"/>
-      <c r="J13" s="92" t="n"/>
+      <c r="E13" s="105" t="inlineStr"/>
+      <c r="F13" s="97" t="n"/>
+      <c r="G13" s="97" t="n"/>
+      <c r="H13" s="97" t="n"/>
+      <c r="I13" s="97" t="n"/>
+      <c r="J13" s="97" t="n"/>
+      <c r="K13" s="97" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="95" t="inlineStr">
@@ -7233,40 +7417,42 @@
       <c r="D14" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="E14" s="94" t="n"/>
+      <c r="E14" s="106" t="inlineStr"/>
       <c r="F14" s="94" t="n"/>
       <c r="G14" s="94" t="n"/>
       <c r="H14" s="94" t="n"/>
       <c r="I14" s="94" t="n"/>
       <c r="J14" s="94" t="n"/>
+      <c r="K14" s="94" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
         <is>
           <t>2025-10-18</t>
         </is>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Mack's Bike &amp; Goods</t>
         </is>
       </c>
-      <c r="C15" s="92" t="n"/>
-      <c r="D15" s="92" t="n"/>
-      <c r="E15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="97" t="n"/>
+      <c r="E15" s="105" t="inlineStr"/>
+      <c r="F15" s="97" t="inlineStr">
         <is>
           <t>Kelly Mack</t>
         </is>
       </c>
-      <c r="F15" s="92" t="inlineStr">
+      <c r="G15" s="97" t="inlineStr">
         <is>
           <t>kelly@macksbikeandgoods.com</t>
         </is>
       </c>
-      <c r="G15" s="92" t="n"/>
-      <c r="H15" s="92" t="n"/>
-      <c r="I15" s="92" t="n"/>
-      <c r="J15" s="92" t="inlineStr">
+      <c r="H15" s="97" t="n"/>
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="97" t="n"/>
+      <c r="K15" s="97" t="inlineStr">
         <is>
           <t>Cancelled due to weather</t>
         </is>
@@ -7291,58 +7477,60 @@
       <c r="D16" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="E16" s="94" t="inlineStr">
+      <c r="E16" s="106" t="inlineStr"/>
+      <c r="F16" s="94" t="inlineStr">
         <is>
           <t>Nick Murray</t>
         </is>
       </c>
-      <c r="F16" s="94" t="inlineStr">
+      <c r="G16" s="94" t="inlineStr">
         <is>
           <t>nmurray@doubleclutchbrewing.com</t>
         </is>
       </c>
-      <c r="G16" s="94" t="inlineStr">
+      <c r="H16" s="94" t="inlineStr">
         <is>
           <t>Krys Juleen</t>
         </is>
       </c>
-      <c r="H16" s="94" t="inlineStr">
+      <c r="I16" s="94" t="inlineStr">
         <is>
           <t>krys@faithatfirst.com</t>
         </is>
       </c>
-      <c r="I16" s="94" t="n"/>
       <c r="J16" s="94" t="n"/>
+      <c r="K16" s="94" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="93" t="inlineStr">
+      <c r="A17" s="96" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="B17" s="92" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Goat Village</t>
         </is>
       </c>
-      <c r="C17" s="92" t="n"/>
-      <c r="D17" s="92" t="n">
+      <c r="C17" s="97" t="n"/>
+      <c r="D17" s="97" t="n">
         <v>31</v>
       </c>
-      <c r="E17" s="92" t="inlineStr">
+      <c r="E17" s="105" t="inlineStr"/>
+      <c r="F17" s="97" t="inlineStr">
         <is>
           <t>Goat Village</t>
         </is>
       </c>
-      <c r="F17" s="92" t="inlineStr">
+      <c r="G17" s="97" t="inlineStr">
         <is>
           <t>goatvillage777@gmail.com</t>
         </is>
       </c>
-      <c r="G17" s="92" t="n"/>
-      <c r="H17" s="92" t="n"/>
-      <c r="I17" s="92" t="n"/>
-      <c r="J17" s="92" t="inlineStr">
+      <c r="H17" s="97" t="n"/>
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="97" t="n"/>
+      <c r="K17" s="97" t="inlineStr">
         <is>
           <t>Requested flyer: 1080x1350 and 1080x1920. Add as cohost on Facebook event.</t>
         </is>
@@ -7367,38 +7555,40 @@
       <c r="D18" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="E18" s="94" t="n"/>
+      <c r="E18" s="106" t="inlineStr"/>
       <c r="F18" s="94" t="n"/>
       <c r="G18" s="94" t="n"/>
       <c r="H18" s="94" t="n"/>
       <c r="I18" s="94" t="n"/>
       <c r="J18" s="94" t="n"/>
+      <c r="K18" s="94" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="93" t="inlineStr">
+      <c r="A19" s="96" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Lincolnwood</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Spring Fling</t>
         </is>
       </c>
-      <c r="D19" s="92" t="n">
+      <c r="D19" s="97" t="n">
         <v>16</v>
       </c>
-      <c r="E19" s="92" t="n"/>
-      <c r="F19" s="92" t="n"/>
-      <c r="G19" s="92" t="n"/>
-      <c r="H19" s="92" t="n"/>
-      <c r="I19" s="92" t="n"/>
-      <c r="J19" s="92" t="n"/>
+      <c r="E19" s="105" t="inlineStr"/>
+      <c r="F19" s="97" t="n"/>
+      <c r="G19" s="97" t="n"/>
+      <c r="H19" s="97" t="n"/>
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="97" t="n"/>
+      <c r="K19" s="97" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="95" t="inlineStr">
@@ -7417,72 +7607,74 @@
         </is>
       </c>
       <c r="D20" s="94" t="n"/>
-      <c r="E20" s="94" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr"/>
+      <c r="F20" s="94" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F20" s="94" t="inlineStr">
+      <c r="G20" s="94" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G20" s="94" t="inlineStr">
+      <c r="H20" s="94" t="inlineStr">
         <is>
           <t>Kim Stanton</t>
         </is>
       </c>
-      <c r="H20" s="94" t="inlineStr">
+      <c r="I20" s="94" t="inlineStr">
         <is>
           <t>kims@covenantnurseryschool.org</t>
         </is>
       </c>
-      <c r="I20" s="94" t="n"/>
-      <c r="J20" s="94" t="inlineStr">
+      <c r="J20" s="94" t="n"/>
+      <c r="K20" s="94" t="inlineStr">
         <is>
           <t>5:30-7:30 PM</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="93" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Greg's 40th Birthday</t>
         </is>
       </c>
-      <c r="D21" s="92" t="n"/>
-      <c r="E21" s="92" t="inlineStr">
+      <c r="D21" s="97" t="n"/>
+      <c r="E21" s="105" t="inlineStr"/>
+      <c r="F21" s="97" t="inlineStr">
         <is>
           <t>Fat Shallot</t>
         </is>
       </c>
-      <c r="F21" s="92" t="inlineStr">
+      <c r="G21" s="97" t="inlineStr">
         <is>
           <t>info@thefatshallot.com</t>
         </is>
       </c>
-      <c r="G21" s="92" t="inlineStr">
+      <c r="H21" s="97" t="inlineStr">
         <is>
           <t>Jenny Sprenzel</t>
         </is>
       </c>
-      <c r="H21" s="92" t="inlineStr">
+      <c r="I21" s="97" t="inlineStr">
         <is>
           <t>Jenny.Sprenzel@rushortho.com</t>
         </is>
       </c>
-      <c r="I21" s="92" t="n"/>
-      <c r="J21" s="92" t="inlineStr">
+      <c r="J21" s="97" t="n"/>
+      <c r="K21" s="97" t="inlineStr">
         <is>
           <t>7:00-9:00 PM</t>
         </is>
@@ -7501,20 +7693,21 @@
       </c>
       <c r="C22" s="94" t="n"/>
       <c r="D22" s="94" t="n"/>
-      <c r="E22" s="94" t="inlineStr">
+      <c r="E22" s="106" t="inlineStr"/>
+      <c r="F22" s="94" t="inlineStr">
         <is>
           <t>Natalie Sallee</t>
         </is>
       </c>
-      <c r="F22" s="94" t="inlineStr">
+      <c r="G22" s="94" t="inlineStr">
         <is>
           <t>programs@ridgeville.org</t>
         </is>
       </c>
-      <c r="G22" s="94" t="n"/>
       <c r="H22" s="94" t="n"/>
       <c r="I22" s="94" t="n"/>
-      <c r="J22" s="94" t="inlineStr">
+      <c r="J22" s="94" t="n"/>
+      <c r="K22" s="94" t="inlineStr">
         <is>
           <t>6:00 PM. Agreement coming.</t>
         </is>
@@ -7537,20 +7730,21 @@
         </is>
       </c>
       <c r="D23" s="97" t="inlineStr"/>
-      <c r="E23" s="97" t="inlineStr">
+      <c r="E23" s="105" t="inlineStr"/>
+      <c r="F23" s="97" t="inlineStr">
         <is>
           <t>J.A. Cohen (Jeff)</t>
         </is>
       </c>
-      <c r="F23" s="97" t="inlineStr">
+      <c r="G23" s="97" t="inlineStr">
         <is>
           <t>jacohenmusic@gmail.com</t>
         </is>
       </c>
-      <c r="G23" s="97" t="n"/>
       <c r="H23" s="97" t="n"/>
       <c r="I23" s="97" t="n"/>
-      <c r="J23" s="97" t="inlineStr">
+      <c r="J23" s="97" t="n"/>
+      <c r="K23" s="97" t="inlineStr">
         <is>
           <t>5:00 PM. ~1 hr set starting ~1 hr before game. ETHS Lazier Field.</t>
         </is>
@@ -7590,6 +7784,465 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>2024-09-07 — Ewing Block Party</t>
+        </is>
+      </c>
+      <c r="B1" s="72" t="n"/>
+      <c r="C1" s="73" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="98" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C2" s="98" t="inlineStr">
+        <is>
+          <t>Vocals</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="97" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="96" t="inlineStr">
+        <is>
+          <t>Don'T Let Me Down</t>
+        </is>
+      </c>
+      <c r="C3" s="97" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="95" t="inlineStr">
+        <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="96" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="C5" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="96" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="C7" s="97" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="94" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="97" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="94" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="97" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>Octopus's Garden</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="94" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="97" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="C13" s="97" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="94" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="97" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="94" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="95" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="97" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="97" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="94" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>I'Ve Got A Feeling</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>Miles / Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="97" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="97" t="inlineStr">
+        <is>
+          <t>Don'T Look Back In Anger</t>
+        </is>
+      </c>
+      <c r="C19" s="97" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="94" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="95" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="97" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="96" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="C21" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="94" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="C22" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="97" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="96" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="C23" s="97" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="94" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="95" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="C24" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="97" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="96" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="C25" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="94" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="95" t="inlineStr">
+        <is>
+          <t>Rockin' in the Free World</t>
+        </is>
+      </c>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="97" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="94" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="94" t="inlineStr">
+        <is>
+          <t>Voodoo Child</t>
+        </is>
+      </c>
+      <c r="C28" s="94" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId22"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7608,32 +8261,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -7655,15 +8308,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7685,15 +8338,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -7715,15 +8368,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7745,15 +8398,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -7775,15 +8428,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -7805,15 +8458,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7835,15 +8488,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7865,15 +8518,15 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
+      <c r="A19" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="93" t="inlineStr">
+      <c r="B19" s="96" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7895,15 +8548,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="92" t="n">
+      <c r="A21" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7925,15 +8578,15 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="92" t="n">
+      <c r="A23" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C23" s="92" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7966,7 +8619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7990,32 +8643,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8037,15 +8690,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8067,15 +8720,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8097,15 +8750,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8127,15 +8780,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8157,15 +8810,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8189,7 +8842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8213,32 +8866,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8260,15 +8913,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8290,15 +8943,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8320,15 +8973,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8350,15 +9003,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8380,15 +9033,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8410,15 +9063,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8440,15 +9093,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8492,7 +9145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8516,32 +9169,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8563,15 +9216,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8593,15 +9246,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8623,15 +9276,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8653,15 +9306,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8683,15 +9336,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8716,7 +9369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8740,32 +9393,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8787,15 +9440,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8817,15 +9470,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8847,15 +9500,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>For What It'S Worth</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8877,15 +9530,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8950,27 +9603,27 @@
       <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Artist</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Who Suggested</t>
         </is>
       </c>
-      <c r="D2" s="89" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9013,70 +9666,70 @@
       <c r="G1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D2" s="89" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>Date Reached Out</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>Proposed Date</t>
         </is>
       </c>
-      <c r="F2" s="89" t="inlineStr">
+      <c r="F2" s="98" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G2" s="89" t="inlineStr">
+      <c r="G2" s="98" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="97" t="inlineStr">
         <is>
           <t>Downtown Evanston</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Andy Vick</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>avick@downtownevanston.org</t>
         </is>
       </c>
-      <c r="D3" s="92" t="inlineStr">
+      <c r="D3" s="97" t="inlineStr">
         <is>
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="E3" s="92" t="n"/>
-      <c r="F3" s="92" t="inlineStr">
+      <c r="E3" s="97" t="n"/>
+      <c r="F3" s="97" t="inlineStr">
         <is>
           <t>Waiting</t>
         </is>
       </c>
-      <c r="G3" s="92" t="inlineStr">
+      <c r="G3" s="97" t="inlineStr">
         <is>
           <t>Puts music line-up together in January — follow up Jan 2026</t>
         </is>
@@ -9125,6 +9778,73 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>KINGS OF EWING — EXPENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="107" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="107" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D2" s="107" t="inlineStr">
+        <is>
+          <t>Paid By</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F2" s="107" t="inlineStr">
+        <is>
+          <t>Reimbursed</t>
+        </is>
+      </c>
+      <c r="G2" s="107" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9149,17 +9869,17 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9170,7 +9890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9213,7 +9933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9238,17 +9958,17 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9259,7 +9979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9284,32 +10004,32 @@
       <c r="C1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="89" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="89" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="n">
+      <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -9331,15 +10051,15 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
+      <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9361,15 +10081,15 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9391,15 +10111,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
+      <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9421,15 +10141,15 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9451,15 +10171,15 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9481,15 +10201,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9511,15 +10231,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
+      <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9559,323 +10279,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-02 — Lincolnwood PTA Spring Fling</t>
-        </is>
-      </c>
-      <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>Song</t>
-        </is>
-      </c>
-      <c r="C2" s="89" t="inlineStr">
-        <is>
-          <t>Vocals</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="92" t="inlineStr">
-        <is>
-          <t>opener</t>
-        </is>
-      </c>
-      <c r="B3" s="93" t="inlineStr">
-        <is>
-          <t>Seven Nation Army</t>
-        </is>
-      </c>
-      <c r="C3" s="92" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="95" t="inlineStr">
-        <is>
-          <t>Don'T Let Me Down</t>
-        </is>
-      </c>
-      <c r="C4" s="94" t="inlineStr">
-        <is>
-          <t>Miles / Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="92" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="C5" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="94" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Head Over Heels</t>
-        </is>
-      </c>
-      <c r="C6" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="92" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="93" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="C7" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="94" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="94" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="C8" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="92" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="93" t="inlineStr">
-        <is>
-          <t>Message In A Bottle</t>
-        </is>
-      </c>
-      <c r="C9" s="92" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="94" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Crossroads</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="92" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="93" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="C11" s="92" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="94" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="95" t="inlineStr">
-        <is>
-          <t>No One To Depend On</t>
-        </is>
-      </c>
-      <c r="C12" s="94" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="92" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="93" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="C13" s="92" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="94" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="95" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="C14" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="92" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="93" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="C15" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="94" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="95" t="inlineStr">
-        <is>
-          <t>Starlight</t>
-        </is>
-      </c>
-      <c r="C16" s="94" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="92" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="92" t="inlineStr">
-        <is>
-          <t>End Of The World</t>
-        </is>
-      </c>
-      <c r="C17" s="92" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="94" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="95" t="inlineStr">
-        <is>
-          <t>Won't Back Down</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="92" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="93" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="C19" s="92" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -343,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,6 +635,21 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1053,17 +1068,17 @@
       <c r="W1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" s="99" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C2" s="99" t="inlineStr">
+      <c r="B2" s="104" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C2" s="104" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -1073,112 +1088,112 @@
           <t>Duration</t>
         </is>
       </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Lead Vocal(s)</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
+      <c r="F2" s="107" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="G2" s="98" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Never Played Live</t>
         </is>
       </c>
-      <c r="H2" s="98" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>2026-05-02
 Lincolnwood</t>
         </is>
       </c>
-      <c r="I2" s="98" t="inlineStr">
+      <c r="I2" s="107" t="inlineStr">
         <is>
           <t>2026-04-22
 Spring Cha Ching</t>
         </is>
       </c>
-      <c r="J2" s="98" t="inlineStr">
+      <c r="J2" s="107" t="inlineStr">
         <is>
           <t>2026-01-24
 Goat Village</t>
         </is>
       </c>
-      <c r="K2" s="98" t="inlineStr">
+      <c r="K2" s="107" t="inlineStr">
         <is>
           <t>2025-11-16
 Double Clutch</t>
         </is>
       </c>
-      <c r="L2" s="98" t="inlineStr">
+      <c r="L2" s="107" t="inlineStr">
         <is>
           <t>2025-09-06
 Block Party</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="M2" s="107" t="inlineStr">
         <is>
           <t>2025-06-25
 American Legion</t>
         </is>
       </c>
-      <c r="N2" s="98" t="inlineStr">
+      <c r="N2" s="107" t="inlineStr">
         <is>
           <t>2025-06-07
 Fat Shallot</t>
         </is>
       </c>
-      <c r="O2" s="98" t="inlineStr">
+      <c r="O2" s="107" t="inlineStr">
         <is>
           <t>2025-05-21
 Post 42</t>
         </is>
       </c>
-      <c r="P2" s="98" t="inlineStr">
+      <c r="P2" s="107" t="inlineStr">
         <is>
           <t>2025-05-03
 Lincolnwood</t>
         </is>
       </c>
-      <c r="Q2" s="98" t="inlineStr">
+      <c r="Q2" s="107" t="inlineStr">
         <is>
           <t>2024-10-09
 Fat Shallot</t>
         </is>
       </c>
-      <c r="R2" s="98" t="inlineStr">
+      <c r="R2" s="107" t="inlineStr">
         <is>
           <t>2024-09-07
 Block Party</t>
         </is>
       </c>
-      <c r="S2" s="98" t="inlineStr">
+      <c r="S2" s="107" t="inlineStr">
         <is>
           <t>2024-08-10
 Fat Shallot</t>
         </is>
       </c>
-      <c r="T2" s="98" t="inlineStr">
+      <c r="T2" s="107" t="inlineStr">
         <is>
           <t>2024-07-13
 Chicago Union</t>
         </is>
       </c>
-      <c r="U2" s="98" t="inlineStr">
+      <c r="U2" s="107" t="inlineStr">
         <is>
           <t>2024-06-08
 Fat Shallot</t>
         </is>
       </c>
-      <c r="V2" s="98" t="inlineStr">
+      <c r="V2" s="107" t="inlineStr">
         <is>
           <t>2024-04-27
 Lincolnwood</t>
         </is>
       </c>
-      <c r="W2" s="98" t="inlineStr">
+      <c r="W2" s="107" t="inlineStr">
         <is>
           <t>2023-09-09
 Block Party</t>
@@ -1191,8 +1206,8 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="100" t="inlineStr"/>
-      <c r="C3" s="100" t="inlineStr"/>
+      <c r="B3" s="105" t="inlineStr"/>
+      <c r="C3" s="105" t="inlineStr"/>
       <c r="D3" s="105" t="inlineStr"/>
       <c r="E3" s="97" t="inlineStr">
         <is>
@@ -1241,7 +1256,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C4" s="102" t="inlineStr"/>
+      <c r="C4" s="106" t="inlineStr"/>
       <c r="D4" s="106" t="inlineStr"/>
       <c r="E4" s="94" t="inlineStr">
         <is>
@@ -1294,8 +1309,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C5" s="100" t="inlineStr"/>
-      <c r="D5" s="105" t="inlineStr"/>
+      <c r="C5" s="105" t="inlineStr"/>
+      <c r="D5" s="105" t="inlineStr">
+        <is>
+          <t>3:43</t>
+        </is>
+      </c>
       <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -1363,8 +1382,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C6" s="102" t="inlineStr"/>
-      <c r="D6" s="106" t="inlineStr"/>
+      <c r="C6" s="106" t="inlineStr"/>
+      <c r="D6" s="106" t="inlineStr">
+        <is>
+          <t>3:55</t>
+        </is>
+      </c>
       <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -1416,8 +1439,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C7" s="100" t="inlineStr"/>
-      <c r="D7" s="105" t="inlineStr"/>
+      <c r="C7" s="105" t="inlineStr"/>
+      <c r="D7" s="105" t="inlineStr">
+        <is>
+          <t>4:55</t>
+        </is>
+      </c>
       <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -1469,8 +1496,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C8" s="102" t="inlineStr"/>
-      <c r="D8" s="106" t="inlineStr"/>
+      <c r="C8" s="106" t="inlineStr"/>
+      <c r="D8" s="106" t="inlineStr">
+        <is>
+          <t>2:31</t>
+        </is>
+      </c>
       <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -1546,8 +1577,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C9" s="100" t="inlineStr"/>
-      <c r="D9" s="105" t="inlineStr"/>
+      <c r="C9" s="105" t="inlineStr"/>
+      <c r="D9" s="105" t="inlineStr">
+        <is>
+          <t>3:09</t>
+        </is>
+      </c>
       <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -1642,8 +1677,8 @@
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="102" t="inlineStr"/>
-      <c r="C10" s="102" t="inlineStr"/>
+      <c r="B10" s="106" t="inlineStr"/>
+      <c r="C10" s="106" t="inlineStr"/>
       <c r="D10" s="106" t="inlineStr"/>
       <c r="E10" s="94" t="inlineStr">
         <is>
@@ -1688,7 +1723,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr"/>
+      <c r="C11" s="105" t="inlineStr"/>
       <c r="D11" s="105" t="inlineStr"/>
       <c r="E11" s="97" t="inlineStr">
         <is>
@@ -1760,9 +1795,13 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="102" t="inlineStr"/>
-      <c r="C12" s="102" t="inlineStr"/>
-      <c r="D12" s="106" t="inlineStr"/>
+      <c r="B12" s="106" t="inlineStr"/>
+      <c r="C12" s="106" t="inlineStr"/>
+      <c r="D12" s="106" t="inlineStr">
+        <is>
+          <t>3:57</t>
+        </is>
+      </c>
       <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -1813,8 +1852,8 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="100" t="inlineStr"/>
-      <c r="C13" s="100" t="inlineStr"/>
+      <c r="B13" s="105" t="inlineStr"/>
+      <c r="C13" s="105" t="inlineStr"/>
       <c r="D13" s="105" t="inlineStr"/>
       <c r="E13" s="97" t="inlineStr">
         <is>
@@ -1858,8 +1897,8 @@
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="102" t="inlineStr"/>
-      <c r="C14" s="102" t="inlineStr"/>
+      <c r="B14" s="106" t="inlineStr"/>
+      <c r="C14" s="106" t="inlineStr"/>
       <c r="D14" s="106" t="inlineStr"/>
       <c r="E14" s="94" t="inlineStr">
         <is>
@@ -1904,8 +1943,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C15" s="100" t="inlineStr"/>
-      <c r="D15" s="105" t="inlineStr"/>
+      <c r="C15" s="105" t="inlineStr"/>
+      <c r="D15" s="105" t="inlineStr">
+        <is>
+          <t>4:01</t>
+        </is>
+      </c>
       <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -1989,8 +2032,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C16" s="102" t="inlineStr"/>
-      <c r="D16" s="106" t="inlineStr"/>
+      <c r="C16" s="106" t="inlineStr"/>
+      <c r="D16" s="106" t="inlineStr">
+        <is>
+          <t>3:35</t>
+        </is>
+      </c>
       <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -2058,8 +2105,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C17" s="100" t="inlineStr"/>
-      <c r="D17" s="105" t="inlineStr"/>
+      <c r="C17" s="105" t="inlineStr"/>
+      <c r="D17" s="105" t="inlineStr">
+        <is>
+          <t>2:47</t>
+        </is>
+      </c>
       <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -2098,8 +2149,8 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="102" t="inlineStr"/>
-      <c r="C18" s="102" t="inlineStr"/>
+      <c r="B18" s="106" t="inlineStr"/>
+      <c r="C18" s="106" t="inlineStr"/>
       <c r="D18" s="106" t="inlineStr"/>
       <c r="E18" s="94" t="inlineStr">
         <is>
@@ -2164,8 +2215,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C19" s="100" t="inlineStr"/>
-      <c r="D19" s="105" t="inlineStr"/>
+      <c r="C19" s="105" t="inlineStr"/>
+      <c r="D19" s="105" t="inlineStr">
+        <is>
+          <t>3:45</t>
+        </is>
+      </c>
       <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -2217,8 +2272,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C20" s="102" t="inlineStr"/>
-      <c r="D20" s="106" t="inlineStr"/>
+      <c r="C20" s="106" t="inlineStr"/>
+      <c r="D20" s="106" t="inlineStr">
+        <is>
+          <t>6:45</t>
+        </is>
+      </c>
       <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -2285,8 +2344,8 @@
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="100" t="inlineStr"/>
-      <c r="C21" s="100" t="inlineStr"/>
+      <c r="B21" s="105" t="inlineStr"/>
+      <c r="C21" s="105" t="inlineStr"/>
       <c r="D21" s="105" t="inlineStr"/>
       <c r="E21" s="97" t="inlineStr">
         <is>
@@ -2331,8 +2390,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C22" s="102" t="inlineStr"/>
-      <c r="D22" s="106" t="inlineStr"/>
+      <c r="C22" s="106" t="inlineStr"/>
+      <c r="D22" s="106" t="inlineStr">
+        <is>
+          <t>3:43</t>
+        </is>
+      </c>
       <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -2423,8 +2486,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="100" t="inlineStr"/>
-      <c r="C23" s="100" t="inlineStr"/>
+      <c r="B23" s="105" t="inlineStr"/>
+      <c r="C23" s="105" t="inlineStr"/>
       <c r="D23" s="105" t="inlineStr"/>
       <c r="E23" s="97" t="inlineStr">
         <is>
@@ -2497,8 +2560,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C24" s="102" t="inlineStr"/>
-      <c r="D24" s="106" t="inlineStr"/>
+      <c r="C24" s="106" t="inlineStr"/>
+      <c r="D24" s="106" t="inlineStr">
+        <is>
+          <t>5:33</t>
+        </is>
+      </c>
       <c r="E24" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -2566,8 +2633,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C25" s="100" t="inlineStr"/>
-      <c r="D25" s="105" t="inlineStr"/>
+      <c r="C25" s="105" t="inlineStr"/>
+      <c r="D25" s="105" t="inlineStr">
+        <is>
+          <t>2:51</t>
+        </is>
+      </c>
       <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -2647,8 +2718,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C26" s="102" t="inlineStr"/>
-      <c r="D26" s="106" t="inlineStr"/>
+      <c r="C26" s="106" t="inlineStr"/>
+      <c r="D26" s="106" t="inlineStr">
+        <is>
+          <t>4:23</t>
+        </is>
+      </c>
       <c r="E26" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -2692,8 +2767,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C27" s="100" t="inlineStr"/>
-      <c r="D27" s="105" t="inlineStr"/>
+      <c r="C27" s="105" t="inlineStr"/>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>4:07</t>
+        </is>
+      </c>
       <c r="E27" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -2745,8 +2824,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C28" s="102" t="inlineStr"/>
-      <c r="D28" s="106" t="inlineStr"/>
+      <c r="C28" s="106" t="inlineStr"/>
+      <c r="D28" s="106" t="inlineStr">
+        <is>
+          <t>2:57</t>
+        </is>
+      </c>
       <c r="E28" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -2830,8 +2913,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C29" s="100" t="inlineStr"/>
-      <c r="D29" s="105" t="inlineStr"/>
+      <c r="C29" s="105" t="inlineStr"/>
+      <c r="D29" s="105" t="inlineStr">
+        <is>
+          <t>5:11</t>
+        </is>
+      </c>
       <c r="E29" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -2923,7 +3010,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C30" s="102" t="inlineStr"/>
+      <c r="C30" s="106" t="inlineStr"/>
       <c r="D30" s="106" t="inlineStr"/>
       <c r="E30" s="94" t="inlineStr">
         <is>
@@ -2972,8 +3059,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C31" s="100" t="inlineStr"/>
-      <c r="D31" s="105" t="inlineStr"/>
+      <c r="C31" s="105" t="inlineStr"/>
+      <c r="D31" s="105" t="inlineStr">
+        <is>
+          <t>4:39</t>
+        </is>
+      </c>
       <c r="E31" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -3037,8 +3128,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C32" s="102" t="inlineStr"/>
-      <c r="D32" s="106" t="inlineStr"/>
+      <c r="C32" s="106" t="inlineStr"/>
+      <c r="D32" s="106" t="inlineStr">
+        <is>
+          <t>4:15</t>
+        </is>
+      </c>
       <c r="E32" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -3118,8 +3213,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C33" s="100" t="inlineStr"/>
-      <c r="D33" s="105" t="inlineStr"/>
+      <c r="C33" s="105" t="inlineStr"/>
+      <c r="D33" s="105" t="inlineStr">
+        <is>
+          <t>5:57</t>
+        </is>
+      </c>
       <c r="E33" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -3191,8 +3290,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C34" s="102" t="inlineStr"/>
-      <c r="D34" s="106" t="inlineStr"/>
+      <c r="C34" s="106" t="inlineStr"/>
+      <c r="D34" s="106" t="inlineStr">
+        <is>
+          <t>8:35</t>
+        </is>
+      </c>
       <c r="E34" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -3260,7 +3363,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C35" s="100" t="inlineStr"/>
+      <c r="C35" s="105" t="inlineStr"/>
       <c r="D35" s="105" t="inlineStr"/>
       <c r="E35" s="97" t="inlineStr">
         <is>
@@ -3313,8 +3416,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C36" s="102" t="inlineStr"/>
-      <c r="D36" s="106" t="inlineStr"/>
+      <c r="C36" s="106" t="inlineStr"/>
+      <c r="D36" s="106" t="inlineStr">
+        <is>
+          <t>4:51</t>
+        </is>
+      </c>
       <c r="E36" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3382,8 +3489,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C37" s="100" t="inlineStr"/>
-      <c r="D37" s="105" t="inlineStr"/>
+      <c r="C37" s="105" t="inlineStr"/>
+      <c r="D37" s="105" t="inlineStr">
+        <is>
+          <t>3:45</t>
+        </is>
+      </c>
       <c r="E37" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3435,7 +3546,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C38" s="102" t="inlineStr"/>
+      <c r="C38" s="106" t="inlineStr"/>
       <c r="D38" s="106" t="inlineStr"/>
       <c r="E38" s="94" t="inlineStr">
         <is>
@@ -3484,7 +3595,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C39" s="100" t="inlineStr"/>
+      <c r="C39" s="105" t="inlineStr"/>
       <c r="D39" s="105" t="inlineStr"/>
       <c r="E39" s="97" t="inlineStr">
         <is>
@@ -3524,9 +3635,13 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B40" s="102" t="inlineStr"/>
-      <c r="C40" s="102" t="inlineStr"/>
-      <c r="D40" s="106" t="inlineStr"/>
+      <c r="B40" s="106" t="inlineStr"/>
+      <c r="C40" s="106" t="inlineStr"/>
+      <c r="D40" s="106" t="inlineStr">
+        <is>
+          <t>4:59</t>
+        </is>
+      </c>
       <c r="E40" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3573,9 +3688,13 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B41" s="100" t="inlineStr"/>
-      <c r="C41" s="100" t="inlineStr"/>
-      <c r="D41" s="105" t="inlineStr"/>
+      <c r="B41" s="105" t="inlineStr"/>
+      <c r="C41" s="105" t="inlineStr"/>
+      <c r="D41" s="105" t="inlineStr">
+        <is>
+          <t>3:15</t>
+        </is>
+      </c>
       <c r="E41" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3630,8 +3749,8 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B42" s="102" t="inlineStr"/>
-      <c r="C42" s="102" t="inlineStr"/>
+      <c r="B42" s="106" t="inlineStr"/>
+      <c r="C42" s="106" t="inlineStr"/>
       <c r="D42" s="106" t="inlineStr"/>
       <c r="E42" s="94" t="inlineStr">
         <is>
@@ -3671,8 +3790,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B43" s="100" t="inlineStr"/>
-      <c r="C43" s="100" t="inlineStr"/>
+      <c r="B43" s="105" t="inlineStr"/>
+      <c r="C43" s="105" t="inlineStr"/>
       <c r="D43" s="105" t="inlineStr"/>
       <c r="E43" s="97" t="inlineStr">
         <is>
@@ -3724,8 +3843,8 @@
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B44" s="102" t="inlineStr"/>
-      <c r="C44" s="102" t="inlineStr"/>
+      <c r="B44" s="106" t="inlineStr"/>
+      <c r="C44" s="106" t="inlineStr"/>
       <c r="D44" s="106" t="inlineStr"/>
       <c r="E44" s="94" t="inlineStr">
         <is>
@@ -3770,8 +3889,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C45" s="100" t="inlineStr"/>
-      <c r="D45" s="105" t="inlineStr"/>
+      <c r="C45" s="105" t="inlineStr"/>
+      <c r="D45" s="105" t="inlineStr">
+        <is>
+          <t>4:47</t>
+        </is>
+      </c>
       <c r="E45" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3866,8 +3989,8 @@
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B46" s="102" t="inlineStr"/>
-      <c r="C46" s="102" t="inlineStr"/>
+      <c r="B46" s="106" t="inlineStr"/>
+      <c r="C46" s="106" t="inlineStr"/>
       <c r="D46" s="106" t="inlineStr"/>
       <c r="E46" s="94" t="inlineStr">
         <is>
@@ -3912,8 +4035,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C47" s="100" t="inlineStr"/>
-      <c r="D47" s="105" t="inlineStr"/>
+      <c r="C47" s="105" t="inlineStr"/>
+      <c r="D47" s="105" t="inlineStr">
+        <is>
+          <t>3:01</t>
+        </is>
+      </c>
       <c r="E47" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -4022,12 +4149,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4037,20 +4165,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -4062,12 +4200,18 @@
           <t>opener</t>
         </is>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4077,12 +4221,18 @@
       <c r="A4" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4092,12 +4242,18 @@
       <c r="A5" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4107,12 +4263,18 @@
       <c r="A6" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4122,12 +4284,18 @@
       <c r="A7" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4142,7 +4310,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr"/>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4152,12 +4322,18 @@
       <c r="A9" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4167,12 +4343,18 @@
       <c r="A10" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4182,12 +4364,18 @@
       <c r="A11" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4197,12 +4385,18 @@
       <c r="A12" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4212,12 +4406,18 @@
       <c r="A13" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4227,12 +4427,18 @@
       <c r="A14" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4242,12 +4448,18 @@
       <c r="A15" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4257,12 +4469,18 @@
       <c r="A16" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4277,7 +4495,9 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="110" t="inlineStr"/>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4287,12 +4507,18 @@
       <c r="A18" s="94" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4302,12 +4528,18 @@
       <c r="A19" s="97" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="96" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4315,21 +4547,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4341,12 +4573,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4356,20 +4589,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -4379,12 +4622,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4394,12 +4643,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4409,12 +4664,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4424,12 +4685,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4439,12 +4706,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4454,12 +4727,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4469,12 +4748,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4484,12 +4769,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4504,7 +4795,9 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr"/>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4514,12 +4807,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4527,15 +4826,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4547,12 +4846,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4562,20 +4862,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -4585,12 +4895,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4600,12 +4916,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4615,12 +4937,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -4630,12 +4958,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4645,12 +4979,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4665,7 +5005,9 @@
           <t>End of the World</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr"/>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4675,12 +5017,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4690,12 +5038,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4705,12 +5059,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>From the Start</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4725,7 +5085,9 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr"/>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4735,12 +5097,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>No One to Depend On</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4750,12 +5118,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4765,12 +5139,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4780,12 +5160,18 @@
       <c r="A16" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4795,12 +5181,18 @@
       <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4810,12 +5202,18 @@
       <c r="A18" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4830,7 +5228,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr"/>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4840,12 +5240,18 @@
       <c r="A20" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4855,12 +5261,18 @@
       <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4870,12 +5282,18 @@
       <c r="A22" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4885,12 +5303,18 @@
       <c r="A23" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>Kings of Ewing</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="inlineStr"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4900,12 +5324,18 @@
       <c r="A24" s="94" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="95" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D24" s="112" t="inlineStr"/>
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -4915,12 +5345,18 @@
       <c r="A25" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C25" s="97" t="inlineStr">
+      <c r="C25" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="inlineStr"/>
+      <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4930,12 +5366,18 @@
       <c r="A26" s="94" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="95" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D26" s="112" t="inlineStr"/>
+      <c r="E26" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4945,12 +5387,18 @@
       <c r="A27" s="97" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="96" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C27" s="97" t="inlineStr">
+      <c r="C27" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D27" s="110" t="inlineStr"/>
+      <c r="E27" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -4960,12 +5408,18 @@
       <c r="A28" s="94" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="95" t="inlineStr">
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D28" s="112" t="inlineStr"/>
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -4975,12 +5429,18 @@
       <c r="A29" s="97" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="96" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>Message in a Bottle</t>
         </is>
       </c>
-      <c r="C29" s="97" t="inlineStr">
+      <c r="C29" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="110" t="inlineStr"/>
+      <c r="E29" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -4995,7 +5455,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="112" t="inlineStr"/>
+      <c r="D30" s="112" t="inlineStr"/>
+      <c r="E30" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5005,12 +5467,18 @@
       <c r="A31" s="97" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="96" t="inlineStr">
+      <c r="B31" s="97" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C31" s="97" t="inlineStr">
+      <c r="C31" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D31" s="110" t="inlineStr"/>
+      <c r="E31" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5025,7 +5493,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="C32" s="112" t="inlineStr"/>
+      <c r="D32" s="112" t="inlineStr"/>
+      <c r="E32" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5040,7 +5510,9 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C33" s="97" t="inlineStr">
+      <c r="C33" s="110" t="inlineStr"/>
+      <c r="D33" s="110" t="inlineStr"/>
+      <c r="E33" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5049,31 +5521,31 @@
     <row r="34" ht="22" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5085,12 +5557,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5100,20 +5573,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -5123,12 +5606,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5138,12 +5627,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5153,12 +5648,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5168,12 +5669,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5183,12 +5690,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5198,12 +5711,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5218,7 +5737,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="110" t="inlineStr"/>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5233,7 +5754,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr"/>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5243,12 +5766,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5263,7 +5792,9 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr"/>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5278,7 +5809,9 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="110" t="inlineStr"/>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5288,12 +5821,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5303,12 +5842,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5316,15 +5861,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5336,12 +5881,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5351,20 +5897,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -5374,12 +5930,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5389,12 +5951,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5404,12 +5972,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5419,12 +5993,18 @@
       <c r="A6" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5439,7 +6019,9 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr"/>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5454,7 +6036,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr"/>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5464,12 +6048,18 @@
       <c r="A9" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5479,12 +6069,18 @@
       <c r="A10" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5494,12 +6090,18 @@
       <c r="A11" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5514,7 +6116,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr"/>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5524,12 +6128,18 @@
       <c r="A13" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5544,7 +6154,9 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="112" t="inlineStr"/>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5554,12 +6166,18 @@
       <c r="A15" s="97" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5574,7 +6192,9 @@
           <t>Who'S That Lady</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr"/>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Instrumental</t>
         </is>
@@ -5582,15 +6202,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5602,12 +6222,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5617,20 +6238,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -5640,12 +6271,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5655,12 +6292,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5670,12 +6313,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5685,12 +6334,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5700,12 +6355,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5720,7 +6381,9 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr"/>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5730,12 +6393,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -5750,7 +6419,9 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr"/>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5765,7 +6436,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr"/>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5780,7 +6453,9 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr"/>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
@@ -5790,12 +6465,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5805,12 +6486,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5825,7 +6512,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr"/>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5835,12 +6524,18 @@
       <c r="A16" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5850,12 +6545,18 @@
       <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5865,12 +6566,18 @@
       <c r="A18" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5885,7 +6592,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr"/>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5895,12 +6604,18 @@
       <c r="A20" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -5910,12 +6625,18 @@
       <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -5925,12 +6646,18 @@
       <c r="A22" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -5940,12 +6667,18 @@
       <c r="A23" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="inlineStr"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -5955,12 +6688,18 @@
       <c r="A24" s="94" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="95" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D24" s="112" t="inlineStr"/>
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5970,12 +6709,18 @@
       <c r="A25" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C25" s="97" t="inlineStr">
+      <c r="C25" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="inlineStr"/>
+      <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -5985,12 +6730,18 @@
       <c r="A26" s="94" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="95" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D26" s="112" t="inlineStr"/>
+      <c r="E26" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6005,7 +6756,9 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C27" s="97" t="inlineStr">
+      <c r="C27" s="110" t="inlineStr"/>
+      <c r="D27" s="110" t="inlineStr"/>
+      <c r="E27" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6015,12 +6768,18 @@
       <c r="A28" s="94" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="95" t="inlineStr">
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D28" s="112" t="inlineStr"/>
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6030,12 +6789,18 @@
       <c r="A29" s="97" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="96" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C29" s="97" t="inlineStr">
+      <c r="C29" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="110" t="inlineStr"/>
+      <c r="E29" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6045,12 +6810,18 @@
       <c r="A30" s="94" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="95" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D30" s="112" t="inlineStr"/>
+      <c r="E30" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6058,27 +6829,27 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6090,12 +6861,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6105,20 +6877,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -6128,12 +6910,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -6143,12 +6931,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6158,12 +6952,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6173,12 +6973,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6188,12 +6994,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6208,7 +7020,9 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr"/>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6223,7 +7037,9 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="110" t="inlineStr"/>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
@@ -6233,12 +7049,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6253,7 +7075,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr"/>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6268,7 +7092,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr"/>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6278,12 +7104,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6293,12 +7125,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6313,7 +7151,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr"/>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6323,12 +7163,18 @@
       <c r="A16" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6338,12 +7184,18 @@
       <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6353,12 +7205,18 @@
       <c r="A18" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6368,12 +7226,18 @@
       <c r="A19" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="96" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6383,12 +7247,18 @@
       <c r="A20" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6398,12 +7268,18 @@
       <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6415,12 +7291,18 @@
           <t>*encore</t>
         </is>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6428,21 +7310,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6454,12 +7336,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6469,20 +7352,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -6499,12 +7392,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6514,20 +7408,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -6542,7 +7446,9 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="110" t="inlineStr"/>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6552,12 +7458,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6567,12 +7479,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6582,12 +7500,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6597,12 +7521,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6612,12 +7542,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6627,12 +7563,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6647,7 +7589,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr"/>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6657,12 +7601,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -6672,12 +7622,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6692,7 +7648,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="110" t="inlineStr"/>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6702,12 +7660,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6717,12 +7681,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6734,12 +7704,18 @@
           <t>encore</t>
         </is>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6747,17 +7723,17 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6769,12 +7745,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6784,20 +7761,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -6807,12 +7794,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -6822,12 +7815,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6837,12 +7836,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6852,12 +7857,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6867,12 +7878,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -6882,12 +7899,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6897,12 +7920,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6912,12 +7941,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6932,7 +7967,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr"/>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -6942,12 +7979,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -6957,12 +8000,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -6970,16 +8019,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7023,22 +8072,22 @@
       <c r="K1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
+      <c r="D2" s="107" t="inlineStr">
         <is>
           <t># Songs</t>
         </is>
@@ -7048,32 +8097,32 @@
           <t>Gig Length</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
+      <c r="F2" s="107" t="inlineStr">
         <is>
           <t>Venue Name</t>
         </is>
       </c>
-      <c r="G2" s="98" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Venue Email</t>
         </is>
       </c>
-      <c r="H2" s="98" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="I2" s="98" t="inlineStr">
+      <c r="I2" s="107" t="inlineStr">
         <is>
           <t>Event Email</t>
         </is>
       </c>
-      <c r="J2" s="98" t="inlineStr">
+      <c r="J2" s="107" t="inlineStr">
         <is>
           <t>Pay</t>
         </is>
       </c>
-      <c r="K2" s="98" t="inlineStr">
+      <c r="K2" s="107" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7784,12 +8833,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7799,20 +8849,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -7822,12 +8882,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -7837,12 +8903,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -7852,12 +8924,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7867,12 +8945,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7882,12 +8966,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -7897,12 +8987,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -7912,12 +9008,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -7927,12 +9029,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7942,12 +9050,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -7957,12 +9071,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -7972,12 +9092,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -7987,12 +9113,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8002,12 +9134,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8017,12 +9155,18 @@
       <c r="A16" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
@@ -8037,7 +9181,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="110" t="inlineStr"/>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8052,7 +9198,9 @@
           <t>I'Ve Got A Feeling</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr"/>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8067,7 +9215,9 @@
           <t>Don'T Look Back In Anger</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr"/>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8077,12 +9227,18 @@
       <c r="A20" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8092,12 +9248,18 @@
       <c r="A21" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8107,12 +9269,18 @@
       <c r="A22" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8122,12 +9290,18 @@
       <c r="A23" s="97" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="inlineStr"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8137,12 +9311,18 @@
       <c r="A24" s="94" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="95" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D24" s="112" t="inlineStr"/>
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8152,12 +9332,18 @@
       <c r="A25" s="97" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C25" s="97" t="inlineStr">
+      <c r="C25" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="inlineStr"/>
+      <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8167,12 +9353,18 @@
       <c r="A26" s="94" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="95" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D26" s="112" t="inlineStr"/>
+      <c r="E26" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8182,12 +9374,18 @@
       <c r="A27" s="97" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="96" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C27" s="97" t="inlineStr">
+      <c r="C27" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D27" s="110" t="inlineStr"/>
+      <c r="E27" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8202,7 +9400,9 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="112" t="inlineStr"/>
+      <c r="D28" s="112" t="inlineStr"/>
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8210,28 +9410,28 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8243,12 +9443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8258,20 +9459,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -8281,12 +9492,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8296,12 +9513,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8311,12 +9534,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8326,12 +9555,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8341,12 +9576,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8356,12 +9597,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8371,12 +9618,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8386,12 +9639,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8401,12 +9660,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8416,12 +9681,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8431,12 +9702,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8446,12 +9723,18 @@
       <c r="A14" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
@@ -8466,7 +9749,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr"/>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8476,12 +9761,18 @@
       <c r="A16" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8491,12 +9782,18 @@
       <c r="A17" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8506,12 +9803,18 @@
       <c r="A18" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8521,12 +9824,18 @@
       <c r="A19" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="96" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" s="110" t="inlineStr"/>
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8536,12 +9845,18 @@
       <c r="A20" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr"/>
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8551,12 +9866,18 @@
       <c r="A21" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr"/>
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8566,12 +9887,18 @@
       <c r="A22" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr"/>
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8581,12 +9908,18 @@
       <c r="A23" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="inlineStr"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8594,26 +9927,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8625,12 +9958,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8640,20 +9974,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -8663,12 +10007,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8678,12 +10028,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8693,12 +10049,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8708,12 +10070,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8723,12 +10091,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8738,12 +10112,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8753,12 +10133,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8768,12 +10154,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8783,12 +10175,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8798,12 +10196,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8813,12 +10217,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8826,17 +10236,17 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8848,12 +10258,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8863,20 +10274,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -8886,12 +10307,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -8901,12 +10328,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8916,12 +10349,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8931,12 +10370,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -8946,12 +10391,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -8961,12 +10412,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -8976,12 +10433,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -8991,12 +10454,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9006,12 +10475,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9021,12 +10496,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9036,12 +10517,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -9051,12 +10538,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9066,12 +10559,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9081,12 +10580,18 @@
       <c r="A16" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9096,12 +10601,18 @@
       <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -9111,12 +10622,18 @@
       <c r="A18" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9124,22 +10641,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9151,12 +10668,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9166,20 +10684,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9189,12 +10717,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -9204,12 +10738,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9219,12 +10759,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9234,12 +10780,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9249,12 +10801,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9264,12 +10822,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9279,12 +10843,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9294,12 +10864,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9309,12 +10885,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9324,12 +10906,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9339,12 +10927,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9353,17 +10947,17 @@
     <row r="14" ht="22" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9375,12 +10969,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9390,20 +10985,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9413,12 +11018,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -9428,12 +11039,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9443,12 +11060,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -9458,12 +11081,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9473,12 +11102,18 @@
       <c r="A7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="96" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -9488,12 +11123,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -9508,7 +11149,9 @@
           <t>For What It'S Worth</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="110" t="inlineStr"/>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9518,12 +11161,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9533,12 +11182,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -9548,12 +11203,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -9561,15 +11222,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9603,27 +11264,27 @@
       <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Artist</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Who Suggested</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
+      <c r="D2" s="107" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9666,37 +11327,37 @@
       <c r="G1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
+      <c r="D2" s="107" t="inlineStr">
         <is>
           <t>Date Reached Out</t>
         </is>
       </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Proposed Date</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
+      <c r="F2" s="107" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G2" s="98" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9850,13 +11511,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9866,20 +11527,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9896,12 +11567,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9912,17 +11584,27 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9939,13 +11621,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9955,20 +11637,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -9985,13 +11677,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -10001,20 +11693,30 @@
         </is>
       </c>
       <c r="B1" s="72" t="n"/>
-      <c r="C1" s="73" t="n"/>
+      <c r="E1" s="73" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="108" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Vocals</t>
         </is>
@@ -10024,12 +11726,18 @@
       <c r="A3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="inlineStr">
+      <c r="B3" s="97" t="inlineStr">
         <is>
           <t>Don'T Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="110" t="inlineStr"/>
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
@@ -10039,12 +11747,18 @@
       <c r="A4" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="112" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -10054,12 +11768,18 @@
       <c r="A5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr"/>
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -10069,12 +11789,18 @@
       <c r="A6" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -10089,7 +11815,9 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr"/>
+      <c r="D7" s="110" t="inlineStr"/>
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -10099,12 +11827,18 @@
       <c r="A8" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -10114,12 +11848,18 @@
       <c r="A9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr"/>
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -10129,12 +11869,18 @@
       <c r="A10" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
@@ -10144,12 +11890,18 @@
       <c r="A11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr"/>
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -10159,12 +11911,18 @@
       <c r="A12" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -10174,12 +11932,18 @@
       <c r="A13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr"/>
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -10189,12 +11953,18 @@
       <c r="A14" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -10204,12 +11974,18 @@
       <c r="A15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr"/>
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -10224,7 +12000,9 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr"/>
+      <c r="D16" s="112" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
@@ -10234,12 +12012,18 @@
       <c r="A17" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr"/>
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
@@ -10249,12 +12033,18 @@
       <c r="A18" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
@@ -10262,20 +12052,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39320" yWindow="920" windowWidth="35780" windowHeight="18720" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39240" yWindow="860" windowWidth="35780" windowHeight="18720" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Song Tracker" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,16 +75,34 @@
     </font>
     <font>
       <name val="Courier New"/>
+      <family val="1"/>
       <color rgb="FF000000"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Courier New"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="FFCC0000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +119,13 @@
         <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -192,11 +215,31 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -216,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -266,6 +309,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -633,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -807,8 +880,8 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
+      <c r="B3" s="19" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
@@ -857,7 +930,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
+      <c r="C4" s="20" t="inlineStr"/>
       <c r="D4" s="12" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -910,7 +983,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
           <t>3:43</t>
@@ -983,7 +1060,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>3:55</t>
@@ -1040,7 +1117,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
           <t>4:55</t>
@@ -1092,12 +1173,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="20" t="inlineStr"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>2:31</t>
@@ -1178,7 +1255,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
           <t>3:09</t>
@@ -1278,8 +1359,8 @@
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -1319,12 +1400,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n"/>
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -1396,8 +1473,16 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
           <t>3:57</t>
@@ -1453,8 +1538,8 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
@@ -1498,8 +1583,8 @@
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1544,7 +1629,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
           <t>4:01</t>
@@ -1633,7 +1722,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>3:35</t>
@@ -1701,12 +1790,8 @@
           <t>From The Start</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n"/>
+      <c r="B17" s="19" t="inlineStr"/>
+      <c r="C17" s="19" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr">
         <is>
           <t>2:47</t>
@@ -1750,8 +1835,16 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1816,7 +1909,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
           <t>3:45</t>
@@ -1873,7 +1970,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
+      <c r="C20" s="20" t="inlineStr"/>
       <c r="D20" s="12" t="inlineStr">
         <is>
           <t>6:45</t>
@@ -1945,8 +2042,8 @@
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr"/>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
@@ -1991,7 +2088,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n"/>
+      <c r="C22" s="20" t="inlineStr"/>
       <c r="D22" s="12" t="inlineStr">
         <is>
           <t>3:43</t>
@@ -2087,8 +2184,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
+      <c r="B23" s="19" t="inlineStr"/>
+      <c r="C23" s="19" t="inlineStr"/>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -2156,12 +2253,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n"/>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
           <t>5:33</t>
@@ -2234,7 +2327,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n"/>
+      <c r="C25" s="19" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr">
         <is>
           <t>2:51</t>
@@ -2309,1398 +2402,1451 @@
       <c r="W25" s="1" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Let Me Roll It</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr"/>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>4:23</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
-      <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
-      <c r="U26" s="2" t="n"/>
-      <c r="V26" s="2" t="n"/>
-      <c r="W26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>4:07</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="n"/>
-      <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="n"/>
-      <c r="Q27" s="1" t="n"/>
-      <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="n"/>
-      <c r="T27" s="1" t="n"/>
-      <c r="U27" s="1" t="n"/>
-      <c r="V27" s="1" t="n"/>
-      <c r="W27" s="1" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="G28" s="1" t="n"/>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="n"/>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="n"/>
+      <c r="M28" s="1" t="n"/>
+      <c r="N28" s="1" t="n"/>
+      <c r="O28" s="1" t="n"/>
+      <c r="P28" s="1" t="n"/>
+      <c r="Q28" s="1" t="n"/>
+      <c r="R28" s="1" t="n"/>
+      <c r="S28" s="1" t="n"/>
+      <c r="T28" s="1" t="n"/>
+      <c r="U28" s="1" t="n"/>
+      <c r="V28" s="1" t="n"/>
+      <c r="W28" s="1" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>2:57</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>5:11</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="n"/>
-      <c r="P29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="1" t="n"/>
-      <c r="W29" s="1" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="G30" s="1" t="n"/>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="n"/>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="1" t="n"/>
+      <c r="W30" s="1" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>4:39</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="n"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N31" s="1" t="n"/>
-      <c r="O31" s="1" t="n"/>
-      <c r="P31" s="1" t="n"/>
-      <c r="Q31" s="1" t="n"/>
-      <c r="R31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="1" t="n"/>
-      <c r="W31" s="1" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="G32" s="1" t="n"/>
+      <c r="H32" s="1" t="n"/>
+      <c r="I32" s="1" t="n"/>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="n"/>
+      <c r="L32" s="1" t="n"/>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="n"/>
+      <c r="O32" s="1" t="n"/>
+      <c r="P32" s="1" t="n"/>
+      <c r="Q32" s="1" t="n"/>
+      <c r="R32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="1" t="n"/>
+      <c r="W32" s="1" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>4:15</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
-      <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="n"/>
-      <c r="W32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr"/>
+      <c r="C34" s="19" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>5:57</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="1" t="n"/>
-      <c r="I33" s="1" t="n"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="n"/>
-      <c r="L33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="n"/>
-      <c r="P33" s="1" t="n"/>
-      <c r="Q33" s="1" t="n"/>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T33" s="1" t="n"/>
-      <c r="U33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="1" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="n"/>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="n"/>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="n"/>
+      <c r="P34" s="1" t="n"/>
+      <c r="Q34" s="1" t="n"/>
+      <c r="R34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T34" s="1" t="n"/>
+      <c r="U34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="1" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Rockin' In The Free World</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>8:35</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="1" t="n"/>
-      <c r="I35" s="1" t="n"/>
-      <c r="J35" s="1" t="n"/>
-      <c r="K35" s="1" t="n"/>
-      <c r="L35" s="1" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
-      <c r="P35" s="1" t="n"/>
-      <c r="Q35" s="1" t="n"/>
-      <c r="R35" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T35" s="1" t="n"/>
-      <c r="U35" s="1" t="n"/>
-      <c r="V35" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="1" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="G36" s="1" t="n"/>
+      <c r="H36" s="1" t="n"/>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="1" t="n"/>
+      <c r="K36" s="1" t="n"/>
+      <c r="L36" s="1" t="n"/>
+      <c r="M36" s="1" t="n"/>
+      <c r="N36" s="1" t="n"/>
+      <c r="O36" s="1" t="n"/>
+      <c r="P36" s="1" t="n"/>
+      <c r="Q36" s="1" t="n"/>
+      <c r="R36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T36" s="1" t="n"/>
+      <c r="U36" s="1" t="n"/>
+      <c r="V36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W36" s="1" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>4:51</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
-      <c r="T36" s="2" t="n"/>
-      <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="n"/>
-      <c r="W36" s="2" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="n"/>
+      <c r="U37" s="2" t="n"/>
+      <c r="V37" s="2" t="n"/>
+      <c r="W37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Starlight</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="n"/>
-      <c r="L37" s="1" t="n"/>
-      <c r="M37" s="1" t="n"/>
-      <c r="N37" s="1" t="n"/>
-      <c r="O37" s="1" t="n"/>
-      <c r="P37" s="1" t="n"/>
-      <c r="Q37" s="1" t="n"/>
-      <c r="R37" s="1" t="n"/>
-      <c r="S37" s="1" t="n"/>
-      <c r="T37" s="1" t="n"/>
-      <c r="U37" s="1" t="n"/>
-      <c r="V37" s="1" t="n"/>
-      <c r="W37" s="1" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="n"/>
+      <c r="L38" s="1" t="n"/>
+      <c r="M38" s="1" t="n"/>
+      <c r="N38" s="1" t="n"/>
+      <c r="O38" s="1" t="n"/>
+      <c r="P38" s="1" t="n"/>
+      <c r="Q38" s="1" t="n"/>
+      <c r="R38" s="1" t="n"/>
+      <c r="S38" s="1" t="n"/>
+      <c r="T38" s="1" t="n"/>
+      <c r="U38" s="1" t="n"/>
+      <c r="V38" s="1" t="n"/>
+      <c r="W38" s="1" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="20" t="inlineStr"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
-      <c r="V38" s="2" t="n"/>
-      <c r="W38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G39" s="1" t="n"/>
-      <c r="H39" s="1" t="n"/>
-      <c r="I39" s="1" t="n"/>
-      <c r="J39" s="1" t="n"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="n"/>
-      <c r="M39" s="1" t="n"/>
-      <c r="N39" s="1" t="n"/>
-      <c r="O39" s="1" t="n"/>
-      <c r="P39" s="1" t="n"/>
-      <c r="Q39" s="1" t="n"/>
-      <c r="R39" s="1" t="n"/>
-      <c r="S39" s="1" t="n"/>
-      <c r="T39" s="1" t="n"/>
-      <c r="U39" s="1" t="n"/>
-      <c r="V39" s="1" t="n"/>
-      <c r="W39" s="1" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="G40" s="1" t="n"/>
+      <c r="H40" s="1" t="n"/>
+      <c r="I40" s="1" t="n"/>
+      <c r="J40" s="1" t="n"/>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="n"/>
+      <c r="M40" s="1" t="n"/>
+      <c r="N40" s="1" t="n"/>
+      <c r="O40" s="1" t="n"/>
+      <c r="P40" s="1" t="n"/>
+      <c r="Q40" s="1" t="n"/>
+      <c r="R40" s="1" t="n"/>
+      <c r="S40" s="1" t="n"/>
+      <c r="T40" s="1" t="n"/>
+      <c r="U40" s="1" t="n"/>
+      <c r="V40" s="1" t="n"/>
+      <c r="W40" s="1" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="20" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>4:59</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="2" t="n"/>
-      <c r="U40" s="2" t="n"/>
-      <c r="V40" s="2" t="n"/>
-      <c r="W40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr"/>
+      <c r="C42" s="19" t="inlineStr"/>
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G41" s="1" t="n"/>
-      <c r="H41" s="1" t="n"/>
-      <c r="I41" s="1" t="n"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="n"/>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N41" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="n"/>
-      <c r="P41" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="1" t="n"/>
-      <c r="R41" s="1" t="n"/>
-      <c r="S41" s="1" t="n"/>
-      <c r="T41" s="1" t="n"/>
-      <c r="U41" s="1" t="n"/>
-      <c r="V41" s="1" t="n"/>
-      <c r="W41" s="1" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
+      <c r="I42" s="1" t="n"/>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L42" s="1" t="n"/>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="n"/>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="n"/>
+      <c r="R42" s="1" t="n"/>
+      <c r="S42" s="1" t="n"/>
+      <c r="T42" s="1" t="n"/>
+      <c r="U42" s="1" t="n"/>
+      <c r="V42" s="1" t="n"/>
+      <c r="W42" s="1" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr"/>
+      <c r="C43" s="20" t="inlineStr"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr"/>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="1" t="n"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M43" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N43" s="1" t="n"/>
-      <c r="O43" s="1" t="n"/>
-      <c r="P43" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="1" t="n"/>
-      <c r="R43" s="1" t="n"/>
-      <c r="S43" s="1" t="n"/>
-      <c r="T43" s="1" t="n"/>
-      <c r="U43" s="1" t="n"/>
-      <c r="V43" s="1" t="n"/>
-      <c r="W43" s="1" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="G44" s="1" t="n"/>
+      <c r="H44" s="1" t="n"/>
+      <c r="I44" s="1" t="n"/>
+      <c r="J44" s="1" t="n"/>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="n"/>
+      <c r="O44" s="1" t="n"/>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="n"/>
+      <c r="R44" s="1" t="n"/>
+      <c r="S44" s="1" t="n"/>
+      <c r="T44" s="1" t="n"/>
+      <c r="U44" s="1" t="n"/>
+      <c r="V44" s="1" t="n"/>
+      <c r="W44" s="1" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr"/>
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>4:47</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G45" s="1" t="n"/>
-      <c r="H45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="n"/>
-      <c r="P45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="G46" s="1" t="n"/>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="n"/>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr"/>
+      <c r="C47" s="20" t="inlineStr"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Instrumental</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="n"/>
+      <c r="U47" s="2" t="n"/>
+      <c r="V47" s="2" t="n"/>
+      <c r="W47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>3:01</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G47" s="1" t="n"/>
-      <c r="H47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I47" s="1" t="n"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="n"/>
-      <c r="L47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N47" s="1" t="n"/>
-      <c r="O47" s="1" t="n"/>
-      <c r="P47" s="1" t="n"/>
-      <c r="Q47" s="1" t="n"/>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T47" s="1" t="n"/>
-      <c r="U47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W47" s="1" t="inlineStr">
+      <c r="G48" s="1" t="n"/>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="n"/>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="n"/>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="n"/>
+      <c r="O48" s="1" t="n"/>
+      <c r="P48" s="1" t="n"/>
+      <c r="Q48" s="1" t="n"/>
+      <c r="R48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T48" s="1" t="n"/>
+      <c r="U48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W48" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3710,35 +3856,47 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3816,13 +3974,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="19" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -3838,7 +3996,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -3864,7 +4026,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -3890,7 +4056,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3916,7 +4086,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -3937,14 +4107,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -3960,7 +4138,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3986,7 +4168,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -4012,7 +4198,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4038,7 +4224,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4064,7 +4254,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -4090,7 +4284,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4116,7 +4314,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4142,7 +4344,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4163,8 +4369,16 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4190,7 +4404,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -4216,7 +4434,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n"/>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4229,15 +4451,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="inlineStr"/>
+      <c r="A21" s="15" t="n"/>
       <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="15" t="inlineStr"/>
-      <c r="E21" s="15" t="inlineStr"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <t>60:01</t>
@@ -4248,19 +4470,35 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4336,7 +4574,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -4362,7 +4604,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4388,7 +4634,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4414,7 +4664,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4440,7 +4690,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -4466,7 +4720,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="20" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4492,7 +4746,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4518,7 +4776,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4539,8 +4801,16 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4566,7 +4836,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4579,15 +4853,15 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="15" t="inlineStr"/>
+      <c r="A14" s="15" t="n"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
       <c r="F14" s="16" t="inlineStr">
         <is>
           <t>40:18</t>
@@ -4597,14 +4871,23 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4680,7 +4963,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -4706,7 +4993,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4732,7 +5019,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -4758,7 +5045,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4779,12 +5066,16 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4805,8 +5096,16 @@
           <t>End of the World</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4832,7 +5131,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4858,7 +5157,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4879,12 +5182,8 @@
           <t>From the Start</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4905,8 +5204,8 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4932,7 +5231,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4958,7 +5261,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -4984,7 +5291,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5010,7 +5321,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5036,7 +5351,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5062,7 +5381,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5083,8 +5406,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5110,7 +5433,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5136,7 +5463,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5162,7 +5493,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5183,12 +5518,8 @@
           <t>Kings of Ewing</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n"/>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5209,12 +5540,8 @@
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n"/>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5240,7 +5567,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
+      <c r="D25" s="19" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5266,7 +5593,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
+      <c r="D26" s="20" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5287,12 +5614,8 @@
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n"/>
+      <c r="C27" s="19" t="inlineStr"/>
+      <c r="D27" s="19" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -5318,7 +5641,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n"/>
+      <c r="D28" s="20" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5344,7 +5667,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n"/>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5365,14 +5692,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr"/>
+      <c r="F30" s="18" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="1" t="n">
@@ -5383,12 +5710,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n"/>
+      <c r="C31" s="19" t="inlineStr"/>
+      <c r="D31" s="19" t="inlineStr"/>
       <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5409,14 +5732,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr"/>
+      <c r="F32" s="18" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="1" t="n">
@@ -5427,26 +5758,26 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
+      <c r="C33" s="19" t="inlineStr"/>
+      <c r="D33" s="19" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1"/>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="15" t="inlineStr"/>
+      <c r="A35" s="15" t="n"/>
       <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr"/>
-      <c r="D35" s="15" t="inlineStr"/>
-      <c r="E35" s="15" t="inlineStr"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
       <c r="F35" s="16" t="inlineStr">
         <is>
           <t>119:52</t>
@@ -5456,30 +5787,42 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5555,7 +5898,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5581,7 +5928,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -5607,7 +5958,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5633,7 +5984,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5659,13 +6014,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -5681,7 +6036,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5702,8 +6061,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5724,14 +6083,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -5747,7 +6114,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5768,14 +6139,14 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr"/>
+      <c r="F12" s="18" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -5786,8 +6157,16 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5813,7 +6192,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5839,7 +6218,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5852,15 +6235,15 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="15" t="inlineStr"/>
+      <c r="A17" s="15" t="n"/>
       <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr"/>
-      <c r="D17" s="15" t="inlineStr"/>
-      <c r="E17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
           <t>40:24</t>
@@ -5870,14 +6253,24 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5953,7 +6346,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -5979,7 +6376,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6005,7 +6402,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6031,7 +6432,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6052,14 +6457,14 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -6070,14 +6475,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -6093,7 +6506,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6119,7 +6536,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6145,7 +6566,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6166,14 +6591,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr"/>
+      <c r="F12" s="18" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -6184,12 +6609,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6210,14 +6631,14 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr"/>
+      <c r="F14" s="18" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="1" t="n">
@@ -6233,7 +6654,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6254,25 +6679,25 @@
           <t>Who'S That Lady</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Instrumental</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr"/>
+      <c r="F16" s="18" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="15" t="inlineStr"/>
+      <c r="A18" s="15" t="n"/>
       <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="15" t="inlineStr"/>
-      <c r="E18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>38:55</t>
@@ -6282,14 +6707,22 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6365,7 +6798,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -6391,7 +6828,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6417,7 +6854,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6438,18 +6879,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="n">
@@ -6465,7 +6902,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6486,8 +6927,8 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6513,7 +6954,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -6534,14 +6975,14 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -6552,14 +6993,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -6570,14 +7019,14 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr"/>
+      <c r="F12" s="18" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -6593,7 +7042,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6619,7 +7072,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6640,8 +7093,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6667,7 +7120,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6693,7 +7150,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6719,7 +7180,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="20" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6740,14 +7201,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -6763,7 +7224,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D20" s="20" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -6784,12 +7245,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n"/>
+      <c r="C21" s="19" t="inlineStr"/>
+      <c r="D21" s="19" t="inlineStr"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -6815,7 +7272,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6836,12 +7297,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n"/>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6862,12 +7319,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n"/>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6893,13 +7346,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
+      <c r="D25" s="19" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -6915,7 +7368,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
+      <c r="D26" s="20" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6936,14 +7389,14 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
+      <c r="C27" s="19" t="inlineStr"/>
+      <c r="D27" s="19" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -6959,7 +7412,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n"/>
+      <c r="D28" s="20" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6985,7 +7438,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n"/>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7006,12 +7463,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7024,15 +7477,15 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="15" t="inlineStr"/>
+      <c r="A32" s="15" t="n"/>
       <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr"/>
-      <c r="D32" s="15" t="inlineStr"/>
-      <c r="E32" s="15" t="inlineStr"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
           <t>92:13</t>
@@ -7042,26 +7495,31 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7137,7 +7595,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -7163,7 +7625,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7189,7 +7651,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7210,18 +7676,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="n">
@@ -7237,7 +7699,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7258,8 +7724,8 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7280,14 +7746,14 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -7303,7 +7769,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7324,14 +7790,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -7342,8 +7816,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7369,7 +7843,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7395,7 +7873,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7416,14 +7898,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -7439,7 +7921,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="20" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7460,12 +7942,8 @@
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7486,12 +7964,8 @@
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7512,12 +7986,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="n"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7543,7 +8013,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D20" s="20" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7569,7 +8039,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7592,12 +8066,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7610,15 +8080,15 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="15" t="inlineStr"/>
+      <c r="A24" s="15" t="n"/>
       <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
       <c r="F24" s="16" t="inlineStr">
         <is>
           <t>73:20</t>
@@ -7628,20 +8098,23 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7704,15 +8177,15 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr"/>
-      <c r="D4" s="15" t="inlineStr"/>
-      <c r="E4" s="15" t="inlineStr"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -7789,14 +8262,14 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
+      <c r="C3" s="19" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -7812,7 +8285,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7838,7 +8315,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7864,7 +8341,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7885,12 +8366,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7916,7 +8393,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7942,7 +8423,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7963,14 +8448,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -7986,7 +8471,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -8012,7 +8501,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8033,8 +8522,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8060,7 +8549,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8086,7 +8579,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8109,12 +8606,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -8127,15 +8620,15 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="15" t="inlineStr"/>
+      <c r="A18" s="15" t="n"/>
       <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="15" t="inlineStr"/>
-      <c r="E18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>50:58</t>
@@ -8145,16 +8638,21 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8230,7 +8728,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -8256,7 +8758,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8282,7 +8784,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -8308,7 +8810,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8329,18 +8835,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -8356,7 +8858,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8377,12 +8883,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8408,7 +8910,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8429,14 +8931,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -8447,12 +8949,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -8478,7 +8976,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8491,15 +8993,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr"/>
+      <c r="A15" s="15" t="n"/>
       <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
-      <c r="E15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
           <t>34:57</t>
@@ -8509,15 +9011,16 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9396,7 +9899,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -9422,7 +9929,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -9448,7 +9959,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -9474,7 +9989,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -9500,7 +10015,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -9526,7 +10041,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -9552,7 +10071,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -9578,13 +10101,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -9600,13 +10123,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -9617,18 +10140,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr"/>
+      <c r="F12" s="18" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -9639,12 +10158,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -9670,7 +10185,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -9696,7 +10211,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -9717,18 +10236,14 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr"/>
+      <c r="F16" s="18" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="1" t="n">
@@ -9739,14 +10254,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -9757,14 +10272,14 @@
           <t>I'Ve Got A Feeling</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr"/>
+      <c r="F18" s="18" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="1" t="n">
@@ -9775,14 +10290,14 @@
           <t>Don'T Look Back In Anger</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -9793,12 +10308,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -9824,7 +10335,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -9850,13 +10365,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="D22" s="20" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr"/>
+      <c r="F22" s="18" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="1" t="n">
@@ -9867,12 +10382,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n"/>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -9898,7 +10409,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n"/>
+      <c r="D24" s="20" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -9924,7 +10435,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
+      <c r="D25" s="19" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -9945,12 +10456,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n"/>
+      <c r="C26" s="20" t="inlineStr"/>
+      <c r="D26" s="20" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -9976,7 +10483,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n"/>
+      <c r="D27" s="19" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -9997,25 +10504,25 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr"/>
+      <c r="F28" s="18" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="15" t="inlineStr"/>
+      <c r="A30" s="15" t="n"/>
       <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr"/>
-      <c r="D30" s="15" t="inlineStr"/>
-      <c r="E30" s="15" t="inlineStr"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
       <c r="F30" s="16" t="inlineStr">
         <is>
           <t>75:13</t>
@@ -10025,27 +10532,28 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10121,7 +10629,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10147,7 +10659,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10173,7 +10689,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10199,7 +10719,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10225,7 +10745,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10251,7 +10771,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10277,7 +10801,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10303,13 +10831,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -10320,18 +10848,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -10342,12 +10866,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10373,7 +10893,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10394,18 +10914,14 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr"/>
+      <c r="F14" s="18" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="1" t="n">
@@ -10416,14 +10932,14 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -10434,12 +10950,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10465,13 +10977,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -10482,12 +10994,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10513,7 +11021,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n"/>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10539,7 +11047,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D20" s="20" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10565,7 +11073,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10586,12 +11098,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10617,7 +11125,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
+      <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10630,15 +11138,15 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="inlineStr"/>
+      <c r="A25" s="15" t="n"/>
       <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
           <t>70:58</t>
@@ -10648,24 +11156,24 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10742,7 +11250,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10768,7 +11280,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10794,7 +11306,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10820,7 +11332,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10846,7 +11362,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10872,7 +11388,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10898,7 +11418,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10924,7 +11444,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10945,18 +11465,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -10972,7 +11488,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10998,7 +11518,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11011,15 +11531,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr"/>
+      <c r="A15" s="15" t="n"/>
       <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
-      <c r="E15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
           <t>41:38</t>
@@ -11029,16 +11549,19 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11114,7 +11637,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -11140,7 +11667,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11166,7 +11697,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11192,7 +11727,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11218,7 +11753,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11244,7 +11779,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11270,7 +11809,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11296,7 +11839,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11317,18 +11860,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -11339,12 +11878,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11365,12 +11900,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11391,12 +11922,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11422,7 +11949,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11448,7 +11975,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11474,7 +12005,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -11495,12 +12026,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11513,15 +12040,15 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr"/>
+      <c r="A20" s="15" t="n"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr"/>
-      <c r="D20" s="15" t="inlineStr"/>
-      <c r="E20" s="15" t="inlineStr"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
       <c r="F20" s="16" t="inlineStr">
         <is>
           <t>64:13</t>
@@ -11531,21 +12058,22 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11621,7 +12149,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -11647,7 +12179,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11673,7 +12209,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11699,7 +12235,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11720,18 +12260,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -11747,13 +12283,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="20" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -11764,12 +12300,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11795,7 +12327,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11821,7 +12353,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11847,7 +12383,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11868,12 +12404,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11887,15 +12419,15 @@
     </row>
     <row r="14" ht="22" customHeight="1"/>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr"/>
+      <c r="A15" s="15" t="n"/>
       <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
-      <c r="E15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
           <t>42:55</t>
@@ -11905,16 +12437,17 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11990,7 +12523,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -12016,7 +12553,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="20" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12042,13 +12579,13 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -12059,18 +12596,14 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="n">
@@ -12081,12 +12614,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -12112,7 +12641,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12133,14 +12666,14 @@
           <t>For What It'S Worth</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -12156,7 +12689,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12182,7 +12715,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12208,7 +12745,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12221,15 +12758,15 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="15" t="inlineStr"/>
+      <c r="A14" s="15" t="n"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
       <c r="F14" s="16" t="inlineStr">
         <is>
           <t>27:31</t>
@@ -12239,14 +12776,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12258,7 +12796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12303,6 +12841,110 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Let It Roll</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Little Feat</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Down By the River replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Short Skirt/Long Jacket</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Cake</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Drew / Matt</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Matt will sing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Blinding Lights</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>The Weeknd</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Electric Feel</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Miles could sing — needs falsetto. 90% about finding right patches for Matt</t>
         </is>
       </c>
     </row>
@@ -12577,15 +13219,15 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr"/>
-      <c r="D4" s="15" t="inlineStr"/>
-      <c r="E4" s="15" t="inlineStr"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -12652,15 +13294,15 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr"/>
-      <c r="D4" s="15" t="inlineStr"/>
-      <c r="E4" s="15" t="inlineStr"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -12729,15 +13371,15 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr"/>
-      <c r="D4" s="15" t="inlineStr"/>
-      <c r="E4" s="15" t="inlineStr"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -12819,7 +13461,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -12845,7 +13491,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12871,7 +13521,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12897,7 +13551,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
+      <c r="D6" s="20" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12918,14 +13572,22 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -12941,7 +13603,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12967,7 +13633,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12988,12 +13658,16 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -13019,7 +13693,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -13045,7 +13723,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -13071,7 +13753,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -13097,7 +13783,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -13123,7 +13813,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -13144,8 +13838,16 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -13171,7 +13873,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -13197,7 +13903,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -13210,15 +13920,15 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr"/>
+      <c r="A20" s="15" t="n"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Total Set Length</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr"/>
-      <c r="D20" s="15" t="inlineStr"/>
-      <c r="E20" s="15" t="inlineStr"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
       <c r="F20" s="16" t="inlineStr">
         <is>
           <t>61:33</t>
@@ -13228,19 +13938,36 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -339,6 +339,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -880,8 +895,8 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr"/>
-      <c r="C3" s="19" t="inlineStr"/>
+      <c r="B3" s="30" t="inlineStr"/>
+      <c r="C3" s="30" t="inlineStr"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
@@ -930,7 +945,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr"/>
+      <c r="C4" s="31" t="inlineStr"/>
       <c r="D4" s="12" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1060,7 +1075,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>3:55</t>
@@ -1173,8 +1188,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="20" t="inlineStr"/>
+      <c r="B8" s="31" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>2:31</t>
@@ -1359,8 +1374,8 @@
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
+      <c r="B10" s="31" t="inlineStr"/>
+      <c r="C10" s="31" t="inlineStr"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -1400,8 +1415,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
+      <c r="B11" s="30" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -1473,12 +1488,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -1538,8 +1553,8 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="19" t="inlineStr"/>
+      <c r="B13" s="30" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
@@ -1583,8 +1598,8 @@
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
+      <c r="B14" s="31" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1722,7 +1737,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr"/>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>3:35</t>
@@ -1790,8 +1805,8 @@
           <t>From The Start</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr"/>
-      <c r="C17" s="19" t="inlineStr"/>
+      <c r="B17" s="30" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr">
         <is>
           <t>2:47</t>
@@ -1835,17 +1850,21 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -1970,7 +1989,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr"/>
+      <c r="C20" s="31" t="inlineStr"/>
       <c r="D20" s="12" t="inlineStr">
         <is>
           <t>6:45</t>
@@ -2042,8 +2061,8 @@
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="19" t="inlineStr"/>
+      <c r="B21" s="30" t="inlineStr"/>
+      <c r="C21" s="30" t="inlineStr"/>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
@@ -2088,7 +2107,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr"/>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
           <t>3:43</t>
@@ -2184,8 +2207,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="19" t="inlineStr"/>
+      <c r="B23" s="30" t="inlineStr"/>
+      <c r="C23" s="30" t="inlineStr"/>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -2253,8 +2276,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="20" t="inlineStr"/>
+      <c r="B24" s="31" t="inlineStr"/>
+      <c r="C24" s="31" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
           <t>5:33</t>
@@ -2327,7 +2350,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr"/>
+      <c r="C25" s="30" t="inlineStr"/>
       <c r="D25" s="10" t="inlineStr">
         <is>
           <t>2:51</t>
@@ -2417,13 +2440,13 @@
           <t>Web</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr"/>
+      <c r="D26" s="31" t="inlineStr"/>
       <c r="E26" s="25" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F26" s="27" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
@@ -2440,12 +2463,12 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -2559,7 +2582,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr"/>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/santana/no-one-to-depend-on-chords-3337193</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
           <t>2:57</t>
@@ -2749,7 +2776,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr"/>
+      <c r="C31" s="31" t="inlineStr"/>
       <c r="D31" s="12" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2798,7 +2825,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr"/>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/chappell-roan/pink-pony-club-official-5236500</t>
+        </is>
+      </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
           <t>4:39</t>
@@ -2867,7 +2898,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -2951,8 +2982,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr"/>
-      <c r="C34" s="19" t="inlineStr"/>
+      <c r="B34" s="30" t="inlineStr"/>
+      <c r="C34" s="30" t="inlineStr"/>
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>5:57</t>
@@ -3024,8 +3055,12 @@
           <t>Rockin' In The Free World</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="20" t="inlineStr"/>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/seven%20nation%20army.pdf</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr">
         <is>
           <t>8:35</t>
@@ -3098,7 +3133,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr"/>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/sade/smooth-operator-official-1979485</t>
+        </is>
+      </c>
       <c r="D36" s="10" t="n"/>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -3151,7 +3190,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -3284,8 +3323,12 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="20" t="inlineStr"/>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/Teach%20Your%20Children.pdf</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr"/>
       <c r="D39" s="12" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -3334,7 +3377,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr"/>
+      <c r="C40" s="30" t="inlineStr"/>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="1" t="inlineStr">
         <is>
@@ -3374,8 +3417,8 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="20" t="inlineStr"/>
+      <c r="B41" s="31" t="inlineStr"/>
+      <c r="C41" s="31" t="inlineStr"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>4:59</t>
@@ -3427,8 +3470,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr"/>
-      <c r="C42" s="19" t="inlineStr"/>
+      <c r="B42" s="30" t="inlineStr"/>
+      <c r="C42" s="30" t="inlineStr"/>
       <c r="D42" s="10" t="inlineStr">
         <is>
           <t>3:15</t>
@@ -3488,8 +3531,8 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr"/>
-      <c r="C43" s="20" t="inlineStr"/>
+      <c r="B43" s="31" t="inlineStr"/>
+      <c r="C43" s="31" t="inlineStr"/>
       <c r="D43" s="12" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3529,8 +3572,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr"/>
-      <c r="C44" s="19" t="inlineStr"/>
+      <c r="B44" s="30" t="inlineStr"/>
+      <c r="C44" s="30" t="inlineStr"/>
       <c r="D44" s="10" t="n"/>
       <c r="E44" s="1" t="inlineStr">
         <is>
@@ -3582,8 +3625,16 @@
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr"/>
-      <c r="C45" s="20" t="inlineStr"/>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/whipping_post.pdf</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/whipping-post-official-2639163</t>
+        </is>
+      </c>
       <c r="D45" s="12" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -3732,8 +3783,16 @@
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr"/>
-      <c r="C47" s="20" t="inlineStr"/>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/won%27t%20back%20down.pdf</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/tom-petty/i-wont-back-down-official-2175865</t>
+        </is>
+      </c>
       <c r="D47" s="12" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -3873,30 +3932,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3974,7 +4032,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr"/>
+      <c r="D3" s="30" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -3996,7 +4054,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4056,7 +4114,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4086,7 +4144,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4107,12 +4169,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4122,7 +4184,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -4168,7 +4234,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4198,7 +4264,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4224,7 +4290,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4284,7 +4350,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4344,7 +4410,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4404,7 +4470,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4450,6 +4516,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="15" t="n"/>
       <c r="B21" s="15" t="inlineStr">
@@ -4462,7 +4529,7 @@
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>60:01</t>
+          <t>63:31</t>
         </is>
       </c>
     </row>
@@ -4476,29 +4543,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4604,7 +4672,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4664,7 +4732,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -4720,7 +4792,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr"/>
+      <c r="D8" s="31" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -4776,7 +4848,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4836,7 +4908,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4852,6 +4924,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="15" t="n"/>
       <c r="B14" s="15" t="inlineStr">
@@ -4877,17 +4950,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4993,7 +5067,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="31" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5019,7 +5093,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -5045,7 +5119,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -5096,12 +5170,12 @@
           <t>End of the World</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5131,7 +5205,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5157,7 +5235,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5182,8 +5260,8 @@
           <t>From the Start</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5204,8 +5282,8 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5261,7 +5339,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5321,7 +5399,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5381,7 +5459,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5406,8 +5484,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5433,7 +5511,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5493,7 +5571,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5518,8 +5596,8 @@
           <t>Kings of Ewing</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr"/>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="C23" s="30" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5540,8 +5618,8 @@
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
+      <c r="C24" s="31" t="inlineStr"/>
+      <c r="D24" s="31" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5567,7 +5645,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr"/>
+      <c r="D25" s="30" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5593,7 +5671,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr"/>
+      <c r="D26" s="31" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5614,8 +5692,8 @@
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr"/>
-      <c r="D27" s="19" t="inlineStr"/>
+      <c r="C27" s="30" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -5641,7 +5719,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr"/>
+      <c r="D28" s="31" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5692,8 +5770,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
+      <c r="C30" s="31" t="inlineStr"/>
+      <c r="D30" s="31" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5710,8 +5788,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr"/>
-      <c r="D31" s="19" t="inlineStr"/>
+      <c r="C31" s="30" t="inlineStr"/>
+      <c r="D31" s="30" t="inlineStr"/>
       <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -5732,12 +5810,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5747,7 +5825,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F32" s="18" t="n"/>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="1" t="n">
@@ -5758,8 +5840,8 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr"/>
-      <c r="D33" s="19" t="inlineStr"/>
+      <c r="C33" s="30" t="inlineStr"/>
+      <c r="D33" s="30" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -5780,7 +5862,7 @@
       <c r="E35" s="15" t="n"/>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>119:52</t>
+          <t>123:22</t>
         </is>
       </c>
     </row>
@@ -5796,33 +5878,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5928,7 +6011,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5958,7 +6041,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -5984,7 +6067,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6014,7 +6097,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6036,7 +6119,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6061,8 +6144,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6083,12 +6166,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6098,7 +6181,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F10" s="18" t="n"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -6139,8 +6226,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6192,7 +6279,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6234,6 +6321,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="15" t="n"/>
       <c r="B17" s="15" t="inlineStr">
@@ -6246,7 +6334,7 @@
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>40:24</t>
+          <t>43:54</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6464,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6432,7 +6524,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6457,8 +6549,8 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6475,12 +6567,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6490,7 +6582,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -6536,7 +6632,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6591,8 +6687,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6609,8 +6705,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6631,8 +6727,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6679,8 +6775,8 @@
           <t>Who'S That Lady</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Instrumental</t>
@@ -6688,6 +6784,7 @@
       </c>
       <c r="F16" s="18" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="15" t="n"/>
       <c r="B18" s="15" t="inlineStr">
@@ -6700,7 +6797,7 @@
       <c r="E18" s="15" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>38:55</t>
+          <t>42:25</t>
         </is>
       </c>
     </row>
@@ -6709,20 +6806,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6828,7 +6926,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -6879,8 +6981,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -6927,8 +7029,8 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr"/>
+      <c r="D8" s="31" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -6954,7 +7056,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -6975,8 +7077,8 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="C10" s="31" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7008,7 +7110,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n"/>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -7019,8 +7125,8 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
@@ -7072,7 +7178,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7093,8 +7199,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7120,7 +7226,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7180,7 +7286,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7201,8 +7307,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7224,7 +7330,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr"/>
+      <c r="D20" s="31" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7245,8 +7351,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr"/>
-      <c r="D21" s="19" t="inlineStr"/>
+      <c r="C21" s="30" t="inlineStr"/>
+      <c r="D21" s="30" t="inlineStr"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7272,7 +7378,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7297,8 +7403,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr"/>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="C23" s="30" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7319,8 +7425,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
+      <c r="C24" s="31" t="inlineStr"/>
+      <c r="D24" s="31" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7346,7 +7452,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr"/>
+      <c r="D25" s="30" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7368,7 +7474,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr"/>
+      <c r="D26" s="31" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7389,8 +7495,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr"/>
-      <c r="D27" s="19" t="inlineStr"/>
+      <c r="C27" s="30" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7412,7 +7518,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr"/>
+      <c r="D28" s="31" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7463,8 +7569,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
+      <c r="C30" s="31" t="inlineStr"/>
+      <c r="D30" s="31" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7476,6 +7582,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="15" t="n"/>
       <c r="B32" s="15" t="inlineStr">
@@ -7488,7 +7595,7 @@
       <c r="E32" s="15" t="n"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>92:13</t>
+          <t>95:43</t>
         </is>
       </c>
     </row>
@@ -7497,29 +7604,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7625,7 +7733,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7676,8 +7788,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7724,8 +7836,8 @@
           <t>That'S What I Love</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr"/>
+      <c r="D8" s="31" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7746,8 +7858,8 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
@@ -7769,7 +7881,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7805,7 +7917,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n"/>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -7816,8 +7932,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -7873,7 +7989,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7898,8 +8014,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -7921,7 +8037,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7942,8 +8058,8 @@
           <t>Dedicated Follower of Fashion</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr"/>
-      <c r="D17" s="19" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -7964,8 +8080,8 @@
           <t>Riders on the Storm</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -7986,8 +8102,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8013,7 +8129,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr"/>
+      <c r="D20" s="31" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8066,8 +8182,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
+      <c r="C22" s="31" t="inlineStr"/>
+      <c r="D22" s="31" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -8079,6 +8195,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="15" t="n"/>
       <c r="B24" s="15" t="inlineStr">
@@ -8091,7 +8208,7 @@
       <c r="E24" s="15" t="n"/>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>73:20</t>
+          <t>76:50</t>
         </is>
       </c>
     </row>
@@ -8100,21 +8217,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8176,6 +8294,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
@@ -8262,8 +8381,8 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr"/>
-      <c r="D3" s="19" t="inlineStr"/>
+      <c r="C3" s="30" t="inlineStr"/>
+      <c r="D3" s="30" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -8285,7 +8404,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8315,7 +8434,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8341,7 +8464,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8366,8 +8489,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -8393,7 +8516,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8448,8 +8571,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="C10" s="31" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8501,7 +8624,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8522,8 +8645,8 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8549,7 +8672,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8606,8 +8729,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -8619,6 +8742,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="15" t="n"/>
       <c r="B18" s="15" t="inlineStr">
@@ -8640,19 +8764,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8758,7 +8883,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8784,7 +8913,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -8810,7 +8939,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8835,8 +8964,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -8858,7 +8987,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8883,8 +9012,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8910,7 +9039,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -8931,8 +9060,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -8949,8 +9078,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -8992,6 +9121,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="n"/>
       <c r="B15" s="15" t="inlineStr">
@@ -9013,14 +9143,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9929,7 +10060,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9989,7 +10120,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10015,7 +10146,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10041,7 +10172,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10101,7 +10232,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10123,7 +10254,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10140,8 +10271,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10158,8 +10289,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10185,7 +10316,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10236,8 +10367,8 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
@@ -10254,8 +10385,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr"/>
-      <c r="D17" s="19" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10272,8 +10403,8 @@
           <t>I'Ve Got A Feeling</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10290,8 +10421,8 @@
           <t>Don'T Look Back In Anger</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10308,8 +10439,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr"/>
-      <c r="D20" s="20" t="inlineStr"/>
+      <c r="C20" s="31" t="inlineStr"/>
+      <c r="D20" s="31" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10365,7 +10496,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr"/>
+      <c r="D22" s="31" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10382,8 +10513,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr"/>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="C23" s="30" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10409,7 +10540,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr"/>
+      <c r="D24" s="31" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10435,7 +10566,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr"/>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10456,8 +10591,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr"/>
-      <c r="D26" s="20" t="inlineStr"/>
+      <c r="C26" s="31" t="inlineStr"/>
+      <c r="D26" s="31" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10483,7 +10618,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10504,8 +10639,8 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
+      <c r="C28" s="31" t="inlineStr"/>
+      <c r="D28" s="31" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10513,6 +10648,7 @@
       </c>
       <c r="F28" s="18" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="15" t="n"/>
       <c r="B30" s="15" t="inlineStr">
@@ -10553,7 +10689,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10659,7 +10796,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10719,7 +10856,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10745,7 +10882,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -10771,7 +10908,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10831,7 +10968,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10848,8 +10985,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10866,8 +11003,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10893,7 +11030,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -10914,8 +11051,8 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
@@ -10932,8 +11069,8 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -10950,8 +11087,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -10977,7 +11114,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -10994,8 +11131,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11021,7 +11158,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11047,7 +11184,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr"/>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11098,8 +11239,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
+      <c r="C22" s="31" t="inlineStr"/>
+      <c r="D22" s="31" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11125,7 +11266,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11137,6 +11278,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="15" t="n"/>
       <c r="B25" s="15" t="inlineStr">
@@ -11172,9 +11314,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11280,7 +11423,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11306,7 +11453,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11332,7 +11479,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11362,7 +11509,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11388,7 +11535,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11418,7 +11565,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11444,7 +11591,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -11465,8 +11612,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11488,7 +11635,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11518,7 +11665,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11530,6 +11677,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="n"/>
       <c r="B15" s="15" t="inlineStr">
@@ -11551,17 +11699,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11667,7 +11816,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11727,7 +11876,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11753,7 +11902,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11779,7 +11928,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11839,7 +11988,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11860,8 +12009,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11878,8 +12027,8 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -11900,8 +12049,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -11922,8 +12071,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -11949,7 +12098,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -11975,7 +12128,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12005,7 +12158,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
@@ -12026,8 +12179,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12039,6 +12192,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="15" t="n"/>
       <c r="B20" s="15" t="inlineStr">
@@ -12071,9 +12225,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12179,7 +12334,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12209,7 +12364,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12235,7 +12394,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12260,8 +12419,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12283,7 +12442,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr"/>
+      <c r="D8" s="31" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12300,8 +12459,8 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12327,7 +12486,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12383,7 +12542,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12404,8 +12563,8 @@
           <t>Rockin' in the Free World</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12441,13 +12600,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12553,7 +12713,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="31" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
@@ -12579,7 +12739,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -12596,8 +12756,8 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12614,8 +12774,8 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
@@ -12641,7 +12801,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12666,8 +12826,8 @@
           <t>For What It'S Worth</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
@@ -12689,7 +12849,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr"/>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12745,7 +12909,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr"/>
+      <c r="D12" s="31" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -12757,6 +12921,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="15" t="n"/>
       <c r="B14" s="15" t="inlineStr">
@@ -12782,9 +12947,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12872,27 +13038,27 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Short Skirt/Long Jacket</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Cake</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Drew / Matt</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Matt will sing</t>
         </is>
@@ -12922,27 +13088,27 @@
       <c r="E5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Electric Feel</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>MGMT</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Miles could sing — needs falsetto. 90% about finding right patches for Matt</t>
         </is>
@@ -13218,6 +13384,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
@@ -13293,6 +13460,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
@@ -13370,6 +13538,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="n"/>
       <c r="B4" s="15" t="inlineStr">
@@ -13409,7 +13578,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>2026-05-14 — Fat Shallot (Covenant Nursery Dining for Dollars) — 5:30-7:30 PM</t>
+          <t>2026-05-14 — Fat Shallot (Covenant Nursery Dining for Dollars) — 5:30 PM</t>
         </is>
       </c>
       <c r="B1" s="5" t="n"/>
@@ -13491,7 +13660,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13551,7 +13720,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
@@ -13587,7 +13760,11 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n"/>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -13603,7 +13780,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13658,12 +13835,12 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13723,7 +13900,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13783,7 +13960,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13838,12 +14015,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13903,7 +14080,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13919,6 +14096,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="15" t="n"/>
       <c r="B20" s="15" t="inlineStr">
@@ -13931,7 +14109,7 @@
       <c r="E20" s="15" t="n"/>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>61:33</t>
+          <t>65:03</t>
         </is>
       </c>
     </row>
@@ -13944,30 +14122,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39240" yWindow="860" windowWidth="35780" windowHeight="18720" tabRatio="600" firstSheet="0" activeTab="10" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39220" yWindow="860" windowWidth="35780" windowHeight="18720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Song Tracker" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +109,12 @@
       <family val="1"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <u val="single"/>
     </font>
     <font>
@@ -121,12 +127,12 @@
       <name val="Courier New"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Courier New"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="4">
@@ -147,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -404,11 +410,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -510,10 +530,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -522,10 +542,28 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,20 +931,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" style="36" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26.1640625" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="19"/>
-    <col width="23.5" customWidth="1" min="20" max="20"/>
-    <col width="16.83203125" customWidth="1" min="21" max="21"/>
-    <col width="16.33203125" customWidth="1" min="22" max="23"/>
+    <col width="33.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="15.5" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" style="46" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="26.1640625" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="21"/>
+    <col width="23.5" customWidth="1" min="22" max="22"/>
+    <col width="16.83203125" customWidth="1" min="23" max="23"/>
+    <col width="16.33203125" customWidth="1" min="24" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" thickBot="1">
@@ -918,10 +957,10 @@
       <c r="B1" s="27" t="n"/>
       <c r="C1" s="25" t="n"/>
       <c r="D1" s="25" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="35" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
+      <c r="H1" s="35" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
@@ -936,7 +975,9 @@
       <c r="T1" s="3" t="n"/>
       <c r="U1" s="3" t="n"/>
       <c r="V1" s="3" t="n"/>
-      <c r="W1" s="4" t="n"/>
+      <c r="W1" s="3" t="n"/>
+      <c r="X1" s="3" t="n"/>
+      <c r="Y1" s="4" t="n"/>
     </row>
     <row r="2" ht="56" customFormat="1" customHeight="1" s="22" thickBot="1">
       <c r="A2" s="21" t="inlineStr">
@@ -956,115 +997,125 @@
       </c>
       <c r="D2" s="26" t="inlineStr">
         <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>Vocal(s)</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="G2" s="43" t="inlineStr">
+        <is>
+          <t>Gig Ready</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="I2" s="21" t="inlineStr">
         <is>
           <t>Never Played Live</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>2026-05-02
 Lincolnwood</t>
         </is>
       </c>
-      <c r="I2" s="21" t="inlineStr">
+      <c r="K2" s="21" t="inlineStr">
         <is>
           <t>2026-04-22
 Spring Cha Ching</t>
         </is>
       </c>
-      <c r="J2" s="21" t="inlineStr">
+      <c r="L2" s="21" t="inlineStr">
         <is>
           <t>2026-01-24
 Goat Village</t>
         </is>
       </c>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="M2" s="21" t="inlineStr">
         <is>
           <t>2025-11-16
 Double Clutch</t>
         </is>
       </c>
-      <c r="L2" s="21" t="inlineStr">
+      <c r="N2" s="21" t="inlineStr">
         <is>
           <t>2025-09-06
 Block Party</t>
         </is>
       </c>
-      <c r="M2" s="21" t="inlineStr">
+      <c r="O2" s="21" t="inlineStr">
         <is>
           <t>2025-06-25
 American Legion</t>
         </is>
       </c>
-      <c r="N2" s="21" t="inlineStr">
+      <c r="P2" s="21" t="inlineStr">
         <is>
           <t>2025-06-07
 Fat Shallot</t>
         </is>
       </c>
-      <c r="O2" s="21" t="inlineStr">
+      <c r="Q2" s="21" t="inlineStr">
         <is>
           <t>2025-05-21
 Post 42</t>
         </is>
       </c>
-      <c r="P2" s="21" t="inlineStr">
+      <c r="R2" s="21" t="inlineStr">
         <is>
           <t>2025-05-03
 Lincolnwood</t>
         </is>
       </c>
-      <c r="Q2" s="21" t="inlineStr">
+      <c r="S2" s="21" t="inlineStr">
         <is>
           <t>2024-10-09
 Fat Shallot</t>
         </is>
       </c>
-      <c r="R2" s="21" t="inlineStr">
+      <c r="T2" s="21" t="inlineStr">
         <is>
           <t>2024-09-07
 Block Party</t>
         </is>
       </c>
-      <c r="S2" s="21" t="inlineStr">
+      <c r="U2" s="21" t="inlineStr">
         <is>
           <t>2024-08-10
 Fat Shallot</t>
         </is>
       </c>
-      <c r="T2" s="21" t="inlineStr">
+      <c r="V2" s="21" t="inlineStr">
         <is>
           <t>2024-07-13
 Chicago Union</t>
         </is>
       </c>
-      <c r="U2" s="21" t="inlineStr">
+      <c r="W2" s="21" t="inlineStr">
         <is>
           <t>2024-06-08
 Fat Shallot</t>
         </is>
       </c>
-      <c r="V2" s="21" t="inlineStr">
+      <c r="X2" s="21" t="inlineStr">
         <is>
           <t>2024-04-27
 Lincolnwood</t>
         </is>
       </c>
-      <c r="W2" s="21" t="inlineStr">
+      <c r="Y2" s="21" t="inlineStr">
         <is>
           <t>2023-09-09
 Block Party</t>
@@ -1077,36 +1128,44 @@
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr"/>
+      <c r="C3" s="47" t="inlineStr"/>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>John Prine</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
       <c r="I3" s="1" t="n"/>
       <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="n"/>
-      <c r="O3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="n"/>
       <c r="Q3" s="1" t="n"/>
       <c r="R3" s="1" t="n"/>
@@ -1115,6 +1174,8 @@
       <c r="U3" s="1" t="n"/>
       <c r="V3" s="1" t="n"/>
       <c r="W3" s="1" t="n"/>
+      <c r="X3" s="1" t="n"/>
+      <c r="Y3" s="1" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1122,52 +1183,58 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="inlineStr"/>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>Pearl Jam</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -1175,35 +1242,39 @@
           <t>Bohemian Like You</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C5" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>Dandy Warhols</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>3:43</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>00s</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I5" s="1" t="n"/>
@@ -1213,38 +1284,44 @@
         </is>
       </c>
       <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n"/>
       <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="n"/>
       <c r="Q5" s="1" t="n"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T5" s="1" t="n"/>
+      <c r="S5" s="1" t="n"/>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="V5" s="1" t="n"/>
-      <c r="W5" s="1" t="n"/>
+      <c r="W5" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n"/>
+      <c r="Y5" s="1" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1252,48 +1329,56 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr"/>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>Beatles</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>3:55</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
@@ -1302,6 +1387,8 @@
       <c r="U6" s="2" t="n"/>
       <c r="V6" s="2" t="n"/>
       <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
+      <c r="Y6" s="2" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -1309,49 +1396,57 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C7" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>4:55</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K7" s="1" t="n"/>
-      <c r="L7" s="1" t="n"/>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="1" t="n"/>
       <c r="O7" s="1" t="n"/>
@@ -1363,6 +1458,8 @@
       <c r="U7" s="1" t="n"/>
       <c r="V7" s="1" t="n"/>
       <c r="W7" s="1" t="n"/>
+      <c r="X7" s="1" t="n"/>
+      <c r="Y7" s="1" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1370,54 +1467,58 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr"/>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>The King</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>2:31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1428,7 +1529,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1440,6 +1545,12 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -1447,42 +1558,42 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>Beatles</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>3:09</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1508,17 +1619,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O9" s="1" t="n"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q9" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q9" s="1" t="n"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1545,6 +1656,16 @@
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y9" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1556,21 +1677,25 @@
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr"/>
+      <c r="C10" s="49" t="inlineStr"/>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
@@ -1580,16 +1705,18 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="2" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -1597,47 +1724,47 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr"/>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="1" t="n"/>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="n"/>
-      <c r="P11" s="1" t="n"/>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M11" s="1" t="n"/>
+      <c r="N11" s="1" t="n"/>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="n"/>
+      <c r="R11" s="1" t="n"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1659,6 +1786,16 @@
         </is>
       </c>
       <c r="W11" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1670,42 +1807,42 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>R.E.M.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>3:57</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1716,8 +1853,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
@@ -1728,6 +1873,8 @@
       <c r="U12" s="2" t="n"/>
       <c r="V12" s="2" t="n"/>
       <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -1735,37 +1882,45 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr"/>
+      <c r="C13" s="47" t="inlineStr"/>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>Kasey Musgraves</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Matt / Miles</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="n"/>
       <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="n"/>
-      <c r="P13" s="1" t="n"/>
+      <c r="M13" s="1" t="n"/>
+      <c r="N13" s="1" t="n"/>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q13" s="1" t="n"/>
       <c r="R13" s="1" t="n"/>
       <c r="S13" s="1" t="n"/>
@@ -1773,6 +1928,8 @@
       <c r="U13" s="1" t="n"/>
       <c r="V13" s="1" t="n"/>
       <c r="W13" s="1" t="n"/>
+      <c r="X13" s="1" t="n"/>
+      <c r="Y13" s="1" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1780,21 +1937,25 @@
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr"/>
+      <c r="C14" s="49" t="inlineStr"/>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>Buffalo Springfield</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
@@ -1809,7 +1970,9 @@
       <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n"/>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1821,35 +1984,39 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>Credence Clearwater Revival</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>4:01</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>60s</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -1864,17 +2031,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M15" s="1" t="n"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" s="1" t="n"/>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1886,11 +2053,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S15" s="1" t="n"/>
       <c r="T15" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1906,7 +2069,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W15" s="1" t="n"/>
+      <c r="W15" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1914,56 +2087,56 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr"/>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>Gin Blossom</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>3:35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1974,8 +2147,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V16" s="2" t="n"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1987,33 +2170,45 @@
           <t>From The Start</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr"/>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>Laufey</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>2:47</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
-      <c r="L17" s="1" t="n"/>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M17" s="1" t="n"/>
       <c r="N17" s="1" t="n"/>
       <c r="O17" s="1" t="n"/>
@@ -2025,6 +2220,8 @@
       <c r="U17" s="1" t="n"/>
       <c r="V17" s="1" t="n"/>
       <c r="W17" s="1" t="n"/>
+      <c r="X17" s="1" t="n"/>
+      <c r="Y17" s="1" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2032,35 +2229,39 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>Jeff Tweedy</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>3:30</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>20s</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I18" s="2" t="n"/>
@@ -2069,11 +2270,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2089,8 +2286,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
@@ -2098,6 +2303,8 @@
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
@@ -2105,49 +2312,57 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>Tears for Fears</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G19" s="1" t="n"/>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I19" s="1" t="n"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K19" s="1" t="n"/>
-      <c r="L19" s="1" t="n"/>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="1" t="n"/>
       <c r="O19" s="1" t="n"/>
@@ -2159,6 +2374,8 @@
       <c r="U19" s="1" t="n"/>
       <c r="V19" s="1" t="n"/>
       <c r="W19" s="1" t="n"/>
+      <c r="X19" s="1" t="n"/>
+      <c r="Y19" s="1" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2166,72 +2383,82 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr"/>
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>6:45</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="2" t="n"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2243,21 +2470,25 @@
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr"/>
+      <c r="C21" s="47" t="inlineStr"/>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>Beates</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
       <c r="I21" s="1" t="n"/>
       <c r="J21" s="1" t="n"/>
       <c r="K21" s="1" t="n"/>
@@ -2267,16 +2498,18 @@
       <c r="O21" s="1" t="n"/>
       <c r="P21" s="1" t="n"/>
       <c r="Q21" s="1" t="n"/>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R21" s="1" t="n"/>
       <c r="S21" s="1" t="n"/>
-      <c r="T21" s="1" t="n"/>
+      <c r="T21" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U21" s="1" t="n"/>
       <c r="V21" s="1" t="n"/>
       <c r="W21" s="1" t="n"/>
+      <c r="X21" s="1" t="n"/>
+      <c r="Y21" s="1" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2284,74 +2517,74 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>3:43</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2378,6 +2611,16 @@
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2389,54 +2632,54 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr"/>
+      <c r="C23" s="47" t="inlineStr"/>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>The Cars</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
       <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="n"/>
       <c r="K23" s="1" t="n"/>
       <c r="L23" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M23" s="1" t="n"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O23" s="1" t="n"/>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q23" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q23" s="1" t="n"/>
       <c r="R23" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2447,10 +2690,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T23" s="1" t="n"/>
-      <c r="U23" s="1" t="n"/>
+      <c r="T23" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V23" s="1" t="n"/>
       <c r="W23" s="1" t="n"/>
+      <c r="X23" s="1" t="n"/>
+      <c r="Y23" s="1" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2458,68 +2711,82 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr"/>
+      <c r="D24" s="45" t="inlineStr">
+        <is>
+          <t>Kings of Ewing</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>5:33</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="T24" s="2" t="n"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="V24" s="2" t="n"/>
-      <c r="W24" s="2" t="n"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
@@ -2527,67 +2794,67 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr"/>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>2:51</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I25" s="1" t="n"/>
       <c r="J25" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K25" s="1" t="n"/>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="n"/>
-      <c r="P25" s="1" t="n"/>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="n"/>
+      <c r="N25" s="1" t="n"/>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="n"/>
+      <c r="R25" s="1" t="n"/>
       <c r="S25" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2603,8 +2870,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V25" s="1" t="n"/>
-      <c r="W25" s="1" t="n"/>
+      <c r="V25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X25" s="1" t="n"/>
+      <c r="Y25" s="1" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
@@ -2612,28 +2889,38 @@
           <t>Let Me Roll It</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Wings</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2645,41 +2932,45 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr"/>
+      <c r="D27" s="45" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>4:23</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
@@ -2691,6 +2982,8 @@
       <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="n"/>
       <c r="W27" s="2" t="n"/>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -2698,35 +2991,35 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr"/>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>The Police</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>4:07</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>80s</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -2735,13 +3028,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
+      <c r="K28" s="1" t="n"/>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N28" s="1" t="n"/>
       <c r="O28" s="1" t="n"/>
       <c r="P28" s="1" t="n"/>
@@ -2752,6 +3049,8 @@
       <c r="U28" s="1" t="n"/>
       <c r="V28" s="1" t="n"/>
       <c r="W28" s="1" t="n"/>
+      <c r="X28" s="1" t="n"/>
+      <c r="Y28" s="1" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2759,66 +3058,62 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/santana/no-one-to-depend-on-chords-3337193</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr"/>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>The Allman Brothers Band</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>2:57</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2844,7 +3139,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W29" s="2" t="n"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
@@ -2852,42 +3157,42 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>Santana</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>5:11</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I30" s="1" t="n"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2913,17 +3218,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O30" s="1" t="n"/>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q30" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q30" s="1" t="n"/>
       <c r="R30" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2944,8 +3249,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="1" t="n"/>
-      <c r="W30" s="1" t="n"/>
+      <c r="V30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X30" s="1" t="n"/>
+      <c r="Y30" s="1" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2953,25 +3268,29 @@
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="B31" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr"/>
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>Beatles</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="45" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
@@ -2981,16 +3300,18 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="n"/>
       <c r="V31" s="2" t="n"/>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="n"/>
+      <c r="X31" s="2" t="n"/>
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3002,60 +3323,56 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/chappell-roan/pink-pony-club-official-5236500</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr"/>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>CSNY</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>4:39</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
       <c r="I32" s="1" t="n"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="n"/>
       <c r="K32" s="1" t="n"/>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="n"/>
       <c r="N32" s="1" t="n"/>
-      <c r="O32" s="1" t="n"/>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="n"/>
       <c r="Q32" s="1" t="n"/>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R32" s="1" t="n"/>
+      <c r="S32" s="1" t="n"/>
       <c r="T32" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3066,8 +3383,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V32" s="1" t="n"/>
-      <c r="W32" s="1" t="n"/>
+      <c r="V32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X32" s="1" t="n"/>
+      <c r="Y32" s="1" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -3075,42 +3402,42 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="B33" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>Chappel Roan</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>4:15</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3136,27 +3463,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="n"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="n"/>
       <c r="W33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
+      <c r="Y33" s="2" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
@@ -3164,72 +3501,82 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr"/>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>The Door</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>5:57</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G34" s="1" t="n"/>
-      <c r="H34" s="1" t="n"/>
       <c r="I34" s="1" t="n"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="n"/>
       <c r="K34" s="1" t="n"/>
       <c r="L34" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M34" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M34" s="1" t="n"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O34" s="1" t="n"/>
-      <c r="P34" s="1" t="n"/>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q34" s="1" t="n"/>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T34" s="1" t="n"/>
+      <c r="R34" s="1" t="n"/>
+      <c r="S34" s="1" t="n"/>
+      <c r="T34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U34" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V34" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="1" t="n"/>
+      <c r="V34" s="1" t="n"/>
+      <c r="W34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X34" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y34" s="1" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3237,72 +3584,82 @@
           <t>Rockin' In The Free World</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/seven%20nation%20army.pdf</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="B35" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C35" s="47" t="inlineStr"/>
+      <c r="D35" s="45" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>8:35</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
@@ -3310,29 +3667,29 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/sade/smooth-operator-official-1979485</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr"/>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>White Stripes</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="G36" s="44" t="n"/>
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="1" t="n"/>
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
@@ -3342,24 +3699,26 @@
       <c r="O36" s="1" t="n"/>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
-      <c r="R36" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T36" s="1" t="n"/>
-      <c r="U36" s="1" t="n"/>
-      <c r="V36" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R36" s="1" t="n"/>
+      <c r="S36" s="1" t="n"/>
+      <c r="T36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="1" t="n"/>
       <c r="W36" s="1" t="n"/>
+      <c r="X36" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y36" s="1" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3367,35 +3726,39 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D37" s="45" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>4:51</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>80s</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I37" s="2" t="n"/>
@@ -3404,11 +3767,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3424,19 +3783,29 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="Q37" s="2" t="n"/>
-      <c r="R37" s="2" t="n"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="n"/>
       <c r="V37" s="2" t="n"/>
       <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
+      <c r="Y37" s="2" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
@@ -3444,49 +3813,57 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>Muse</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I38" s="1" t="n"/>
       <c r="J38" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K38" s="1" t="n"/>
-      <c r="L38" s="1" t="n"/>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M38" s="1" t="n"/>
       <c r="N38" s="1" t="n"/>
       <c r="O38" s="1" t="n"/>
@@ -3498,6 +3875,8 @@
       <c r="U38" s="1" t="n"/>
       <c r="V38" s="1" t="n"/>
       <c r="W38" s="1" t="n"/>
+      <c r="X38" s="1" t="n"/>
+      <c r="Y38" s="1" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -3505,25 +3884,29 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/Teach%20Your%20Children.pdf</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="B39" s="50" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C39" s="47" t="inlineStr"/>
+      <c r="D39" s="45" t="inlineStr">
+        <is>
+          <t>Rolling Stones</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="45" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
@@ -3533,20 +3916,22 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V39" s="2" t="n"/>
       <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
+      <c r="Y39" s="2" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
@@ -3554,34 +3939,38 @@
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="B40" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr"/>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>CSNY</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="44" t="n"/>
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="1" t="n"/>
       <c r="I40" s="1" t="n"/>
       <c r="J40" s="1" t="n"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="n"/>
       <c r="L40" s="1" t="n"/>
-      <c r="M40" s="1" t="n"/>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N40" s="1" t="n"/>
       <c r="O40" s="1" t="n"/>
       <c r="P40" s="1" t="n"/>
@@ -3592,6 +3981,8 @@
       <c r="U40" s="1" t="n"/>
       <c r="V40" s="1" t="n"/>
       <c r="W40" s="1" t="n"/>
+      <c r="X40" s="1" t="n"/>
+      <c r="Y40" s="1" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -3599,45 +3990,53 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="B41" s="47" t="inlineStr"/>
+      <c r="C41" s="47" t="inlineStr"/>
+      <c r="D41" s="45" t="inlineStr">
+        <is>
+          <t>Leon Bridges</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>4:59</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
@@ -3645,6 +4044,8 @@
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n"/>
       <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
+      <c r="Y41" s="2" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
@@ -3652,60 +4053,70 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr"/>
+      <c r="C42" s="49" t="inlineStr"/>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>The Who</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>3:15</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="1" t="n"/>
       <c r="I42" s="1" t="n"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="n"/>
+      <c r="J42" s="1" t="n"/>
+      <c r="K42" s="1" t="n"/>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="n"/>
+      <c r="N42" s="1" t="n"/>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n"/>
-      <c r="R42" s="1" t="n"/>
+      <c r="R42" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S42" s="1" t="n"/>
       <c r="T42" s="1" t="n"/>
       <c r="U42" s="1" t="n"/>
       <c r="V42" s="1" t="n"/>
       <c r="W42" s="1" t="n"/>
+      <c r="X42" s="1" t="n"/>
+      <c r="Y42" s="1" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3713,29 +4124,33 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="B43" s="47" t="inlineStr"/>
+      <c r="C43" s="47" t="inlineStr"/>
+      <c r="D43" s="45" t="inlineStr">
+        <is>
+          <t>Jimi Hendrix</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="45" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
@@ -3747,6 +4162,8 @@
       <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="n"/>
       <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+      <c r="Y43" s="2" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
@@ -3754,52 +4171,62 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr"/>
+      <c r="C44" s="49" t="inlineStr"/>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>90s</t>
         </is>
       </c>
-      <c r="G44" s="1" t="n"/>
-      <c r="H44" s="1" t="n"/>
       <c r="I44" s="1" t="n"/>
       <c r="J44" s="1" t="n"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="n"/>
+      <c r="L44" s="1" t="n"/>
       <c r="M44" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N44" s="1" t="n"/>
-      <c r="O44" s="1" t="n"/>
-      <c r="P44" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P44" s="1" t="n"/>
       <c r="Q44" s="1" t="n"/>
-      <c r="R44" s="1" t="n"/>
+      <c r="R44" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S44" s="1" t="n"/>
       <c r="T44" s="1" t="n"/>
       <c r="U44" s="1" t="n"/>
       <c r="V44" s="1" t="n"/>
       <c r="W44" s="1" t="n"/>
+      <c r="X44" s="1" t="n"/>
+      <c r="Y44" s="1" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3807,34 +4234,30 @@
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/whipping_post.pdf</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/whipping-post-official-2639163</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="B45" s="47" t="inlineStr"/>
+      <c r="C45" s="47" t="inlineStr"/>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Black Sabbath </t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="45" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
@@ -3849,6 +4272,8 @@
       <c r="U45" s="2" t="n"/>
       <c r="V45" s="2" t="n"/>
       <c r="W45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
+      <c r="Y45" s="2" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
@@ -3856,42 +4281,42 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="B46" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>The Allman Brothers Band</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>4:47</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I46" s="1" t="n"/>
       <c r="J46" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3917,17 +4342,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O46" s="1" t="n"/>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q46" s="1" t="n"/>
       <c r="R46" s="1" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3954,6 +4379,16 @@
         </is>
       </c>
       <c r="W46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X46" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y46" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3965,39 +4400,35 @@
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/won%27t%20back%20down.pdf</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/tom-petty/i-wont-back-down-official-2175865</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="B47" s="47" t="inlineStr"/>
+      <c r="C47" s="47" t="inlineStr"/>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>The Isley Brothers</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Instrumental</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="45" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="n"/>
@@ -4007,6 +4438,8 @@
       <c r="U47" s="2" t="n"/>
       <c r="V47" s="2" t="n"/>
       <c r="W47" s="2" t="n"/>
+      <c r="X47" s="2" t="n"/>
+      <c r="Y47" s="2" t="n"/>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
@@ -4014,35 +4447,39 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="B48" s="48" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Tom Petty and the Heartbreakers</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>3:01</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>80s</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="n"/>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="I48" s="1" t="n"/>
@@ -4057,41 +4494,50 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M48" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N48" s="1" t="n"/>
-      <c r="O48" s="1" t="n"/>
+      <c r="M48" s="1" t="n"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="n"/>
       <c r="Q48" s="1" t="n"/>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T48" s="1" t="n"/>
+      <c r="R48" s="1" t="n"/>
+      <c r="S48" s="1" t="n"/>
+      <c r="T48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U48" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V48" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V48" s="1" t="n"/>
       <c r="W48" s="1" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="X48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y48" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="46" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4101,42 +4547,49 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4701,7 +5154,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="11" t="n"/>
       <c r="B21" s="11" t="inlineStr">
@@ -5112,7 +5564,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="n"/>
       <c r="B14" s="11" t="inlineStr">
@@ -6515,7 +6966,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="11" t="n"/>
       <c r="B17" s="11" t="inlineStr">
@@ -6981,7 +7431,6 @@
       </c>
       <c r="F16" s="14" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="11" t="inlineStr">
@@ -7782,7 +8231,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="11" t="n"/>
       <c r="B32" s="11" t="inlineStr">
@@ -8398,7 +8846,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="11" t="n"/>
       <c r="B24" s="11" t="inlineStr">
@@ -8500,7 +8947,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="11" t="n"/>
       <c r="B4" s="11" t="inlineStr">
@@ -8951,7 +9397,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="11" t="inlineStr">
@@ -9333,7 +9778,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="11" t="n"/>
       <c r="B15" s="11" t="inlineStr">
@@ -9470,12 +9914,12 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
@@ -9502,12 +9946,12 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9534,12 +9978,12 @@
       <c r="L4" s="2" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9570,12 +10014,12 @@
       <c r="L5" s="1" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9610,12 +10054,12 @@
       <c r="L6" s="2" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9646,12 +10090,12 @@
       <c r="L7" s="1" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
@@ -9678,12 +10122,12 @@
       <c r="L8" s="2" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9718,12 +10162,12 @@
       <c r="L9" s="1" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9750,12 +10194,12 @@
       <c r="L10" s="2" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n"/>
+      <c r="B11" s="38" t="n"/>
       <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Post 42</t>
@@ -9772,12 +10216,12 @@
       <c r="L11" s="1" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9808,12 +10252,12 @@
       <c r="L12" s="2" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -9836,12 +10280,12 @@
       <c r="L13" s="1" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
@@ -9868,12 +10312,12 @@
       <c r="L14" s="2" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>2025-10-18</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n"/>
+      <c r="B15" s="38" t="n"/>
       <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Mack's Bike &amp; Goods</t>
@@ -9902,12 +10346,12 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
@@ -9952,12 +10396,12 @@
       <c r="L16" s="2" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
@@ -9988,12 +10432,12 @@
       <c r="L17" s="1" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -10022,12 +10466,12 @@
       <c r="L18" s="2" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -10056,12 +10500,12 @@
       <c r="L19" s="1" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>5:30 PM</t>
         </is>
@@ -10104,12 +10548,12 @@
       <c r="L20" s="2" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
@@ -10152,12 +10596,12 @@
       <c r="L21" s="1" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -10186,12 +10630,12 @@
       <c r="L22" s="2" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
@@ -10225,26 +10669,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId20"/>
+    <hyperlink ref="A3" location="'2023-09-09 Block Party'!A1" display="2023-09-09"/>
+    <hyperlink ref="A4" location="'2024-04-27 Lincolnwood'!A1" display="2024-04-27"/>
+    <hyperlink ref="A5" location="'2024-06-08 Fat Shallot'!A1" display="2024-06-08"/>
+    <hyperlink ref="A6" location="'2024-07-13 Chicago Union'!A1" display="2024-07-13"/>
+    <hyperlink ref="A7" location="'2024-08-10 Fat Shallot'!A1" display="2024-08-10"/>
+    <hyperlink ref="A8" location="'2024-09-07 Block Party'!A1" display="2024-09-07"/>
+    <hyperlink ref="A9" location="'2024-10-09 Fat Shallot'!A1" display="2024-10-09"/>
+    <hyperlink ref="A10" location="'2025-05-03 Lincolnwood'!A1" display="2025-05-03"/>
+    <hyperlink ref="A11" location="'2025-05-21 Post 42'!A1" display="2025-05-21"/>
+    <hyperlink ref="A12" location="'2025-06-07 Fat Shallot'!A1" display="2025-06-07"/>
+    <hyperlink ref="A13" location="'2025-06-25 American Legion'!A1" display="2025-06-25"/>
+    <hyperlink ref="A14" location="'2025-09-06 Block Party'!A1" display="2025-09-06"/>
+    <hyperlink ref="A16" location="'2025-11-16 Double Clutch'!A1" display="2025-11-16"/>
+    <hyperlink ref="A17" location="'2026-01-24 Goat Village'!A1" display="2026-01-24"/>
+    <hyperlink ref="A18" location="'2026-04-22 Spring Cha Ching'!A1" display="2026-04-22"/>
+    <hyperlink ref="A19" location="'2026-05-02 Lincolnwood'!A1" display="2026-05-02"/>
+    <hyperlink ref="A20" location="'2026-05-14 Fat Shallot'!A1" display="2026-05-14"/>
+    <hyperlink ref="A21" location="'2026-05-16 Fat Shallot'!A1" display="2026-05-16"/>
+    <hyperlink ref="A22" location="'2026-06-24 Ridgeville Parks'!A1" display="2026-06-24"/>
+    <hyperlink ref="A23" location="'2026-06-21 Chicago Union'!A1" display="2026-06-21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10941,7 +11385,6 @@
       </c>
       <c r="F28" s="14" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="11" t="n"/>
       <c r="B30" s="11" t="inlineStr">
@@ -11574,7 +12017,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="11" t="n"/>
       <c r="B25" s="11" t="inlineStr">
@@ -11976,7 +12418,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="11" t="n"/>
       <c r="B15" s="11" t="inlineStr">
@@ -12494,7 +12935,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="11" t="n"/>
       <c r="B20" s="11" t="inlineStr">
@@ -13229,7 +13669,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="n"/>
       <c r="B14" s="11" t="inlineStr">
@@ -13695,7 +14134,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="11" t="n"/>
       <c r="B4" s="11" t="inlineStr">
@@ -13776,7 +14214,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="11" t="n"/>
       <c r="B4" s="11" t="inlineStr">
@@ -13857,7 +14294,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="11" t="n"/>
       <c r="B4" s="11" t="inlineStr">
@@ -14418,7 +14854,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="11" t="n"/>
       <c r="B20" s="11" t="inlineStr">

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -428,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -565,6 +565,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1837,9 +1840,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>60s</t>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>80s</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -4189,9 +4192,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t>90s</t>
+      <c r="H44" s="51" t="inlineStr">
+        <is>
+          <t>70s</t>
         </is>
       </c>
       <c r="I44" s="1" t="n"/>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -428,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -567,6 +567,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4015,9 +4018,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>10s</t>
+      <c r="H41" s="52" t="inlineStr">
+        <is>
+          <t>20s</t>
         </is>
       </c>
       <c r="I41" s="2" t="n"/>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39420" yWindow="820" windowWidth="35900" windowHeight="18680" tabRatio="600" firstSheet="11" activeTab="16" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39380" yWindow="820" windowWidth="35900" windowHeight="18680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Song Tracker" sheetId="1" state="visible" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,13 +124,6 @@
       <family val="1"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <family val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Courier New"/>
@@ -167,8 +160,21 @@
     </font>
     <font>
       <name val="Courier New"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
       <color rgb="000563C1"/>
       <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="000563C1"/>
+      <sz val="13"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -191,12 +197,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -493,11 +499,11 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -584,38 +590,29 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -636,7 +633,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -681,16 +678,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -700,24 +717,26 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1089,161 +1108,159 @@
     <col width="15.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="7"/>
     <col width="16" customWidth="1" style="28" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="21"/>
+    <col width="16" customWidth="1" min="9" max="21"/>
     <col width="23.5" customWidth="1" min="22" max="22"/>
     <col width="16.83203125" customWidth="1" min="23" max="23"/>
     <col width="16.33203125" customWidth="1" min="24" max="25"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="28" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>KINGS OF EWING — SONG TRACKER</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="H1" s="53" t="n"/>
-      <c r="Y1" s="54" t="n"/>
-    </row>
-    <row r="2" ht="56" customFormat="1" customHeight="1" s="56" thickBot="1" thickTop="1">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="B1" s="49" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="Y1" s="51" t="n"/>
+    </row>
+    <row r="2" ht="56" customFormat="1" customHeight="1" s="53" thickBot="1" thickTop="1">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B2" s="55" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C2" s="55" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D2" s="55" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>Artist</t>
         </is>
       </c>
-      <c r="E2" s="55" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="F2" s="55" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>Vocal(s)</t>
         </is>
       </c>
-      <c r="G2" s="55" t="inlineStr">
+      <c r="G2" s="52" t="inlineStr">
         <is>
           <t>Gig Ready</t>
         </is>
       </c>
-      <c r="H2" s="55" t="inlineStr">
+      <c r="H2" s="52" t="inlineStr">
         <is>
           <t>Decade</t>
         </is>
       </c>
-      <c r="I2" s="55" t="inlineStr">
+      <c r="I2" s="52" t="inlineStr">
         <is>
           <t>Never Played Live</t>
         </is>
       </c>
-      <c r="J2" s="83" t="inlineStr">
+      <c r="J2" s="75" t="inlineStr">
         <is>
           <t>2026-05-14
 Fat Shallot</t>
         </is>
       </c>
-      <c r="K2" s="55" t="inlineStr">
+      <c r="K2" s="75" t="inlineStr">
         <is>
           <t>2026-05-02
 Lincolnwood</t>
         </is>
       </c>
-      <c r="L2" s="55" t="inlineStr">
+      <c r="L2" s="75" t="inlineStr">
         <is>
           <t>2026-04-22
 Spring Cha Ching</t>
         </is>
       </c>
-      <c r="M2" s="55" t="inlineStr">
+      <c r="M2" s="75" t="inlineStr">
         <is>
           <t>2026-01-24
 Goat Village</t>
         </is>
       </c>
-      <c r="N2" s="55" t="inlineStr">
+      <c r="N2" s="75" t="inlineStr">
         <is>
           <t>2025-11-16
 Double Clutch</t>
         </is>
       </c>
-      <c r="O2" s="55" t="inlineStr">
+      <c r="O2" s="75" t="inlineStr">
         <is>
           <t>2025-09-06
 Block Party</t>
         </is>
       </c>
-      <c r="P2" s="55" t="inlineStr">
+      <c r="P2" s="75" t="inlineStr">
         <is>
           <t>2025-06-25
 American Legion</t>
         </is>
       </c>
-      <c r="Q2" s="55" t="inlineStr">
+      <c r="Q2" s="75" t="inlineStr">
         <is>
           <t>2025-06-07
 Fat Shallot</t>
         </is>
       </c>
-      <c r="R2" s="55" t="inlineStr">
+      <c r="R2" s="75" t="inlineStr">
         <is>
           <t>2025-05-03
 Lincolnwood</t>
         </is>
       </c>
-      <c r="S2" s="55" t="inlineStr">
+      <c r="S2" s="75" t="inlineStr">
         <is>
           <t>2024-10-09
 Fat Shallot</t>
         </is>
       </c>
-      <c r="T2" s="55" t="inlineStr">
+      <c r="T2" s="75" t="inlineStr">
         <is>
           <t>2024-09-07
 Block Party</t>
         </is>
       </c>
-      <c r="U2" s="55" t="inlineStr">
+      <c r="U2" s="75" t="inlineStr">
         <is>
           <t>2024-08-10
 Fat Shallot</t>
         </is>
       </c>
-      <c r="V2" s="55" t="inlineStr">
+      <c r="V2" s="75" t="inlineStr">
         <is>
           <t>2024-07-13
 Chicago Union</t>
         </is>
       </c>
-      <c r="W2" s="55" t="inlineStr">
+      <c r="W2" s="75" t="inlineStr">
         <is>
           <t>2024-06-08
 Fat Shallot</t>
         </is>
       </c>
-      <c r="X2" s="55" t="inlineStr">
+      <c r="X2" s="75" t="inlineStr">
         <is>
           <t>2024-04-27
 Lincolnwood</t>
         </is>
       </c>
-      <c r="Y2" s="55" t="inlineStr">
+      <c r="Y2" s="75" t="inlineStr">
         <is>
           <t>2023-09-09
 Block Party</t>
@@ -1251,58 +1268,58 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" thickTop="1">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Angel From Montgomery</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="50" t="n"/>
-      <c r="D3" s="44" t="inlineStr">
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>John Prine</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
-      <c r="F3" s="44" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="G3" s="44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H3" s="44" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="41" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="I3" s="44" t="n"/>
-      <c r="K3" s="44" t="n"/>
-      <c r="L3" s="44" t="n"/>
-      <c r="M3" s="44" t="n"/>
-      <c r="N3" s="44" t="n"/>
-      <c r="O3" s="44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P3" s="44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="44" t="n"/>
-      <c r="R3" s="44" t="n"/>
-      <c r="S3" s="44" t="n"/>
-      <c r="T3" s="44" t="n"/>
-      <c r="U3" s="44" t="n"/>
-      <c r="V3" s="44" t="n"/>
-      <c r="W3" s="44" t="n"/>
-      <c r="X3" s="44" t="n"/>
-      <c r="Y3" s="44" t="n"/>
+      <c r="I3" s="41" t="n"/>
+      <c r="K3" s="41" t="n"/>
+      <c r="L3" s="41" t="n"/>
+      <c r="M3" s="41" t="n"/>
+      <c r="N3" s="41" t="n"/>
+      <c r="O3" s="41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P3" s="41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="41" t="n"/>
+      <c r="R3" s="41" t="n"/>
+      <c r="S3" s="41" t="n"/>
+      <c r="T3" s="41" t="n"/>
+      <c r="U3" s="41" t="n"/>
+      <c r="V3" s="41" t="n"/>
+      <c r="W3" s="41" t="n"/>
+      <c r="X3" s="41" t="n"/>
+      <c r="Y3" s="41" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1310,13 +1327,13 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C4" s="38" t="n"/>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Pearl Jam</t>
         </is>
@@ -1327,7 +1344,7 @@
           <t>Drew</t>
         </is>
       </c>
-      <c r="G4" s="35" t="n"/>
+      <c r="G4" s="33" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>90s</t>
@@ -1368,17 +1385,17 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C5" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C5" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Dandy Warhols</t>
         </is>
@@ -1404,7 +1421,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n"/>
-      <c r="J5" s="84" t="inlineStr">
+      <c r="J5" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1459,13 +1476,13 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Beatles</t>
         </is>
@@ -1525,17 +1542,17 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Cream</t>
         </is>
@@ -1561,7 +1578,7 @@
         </is>
       </c>
       <c r="I7" s="1" t="n"/>
-      <c r="J7" s="84" t="inlineStr">
+      <c r="J7" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1600,13 +1617,13 @@
           <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>The King</t>
         </is>
@@ -1690,17 +1707,17 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C9" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Beatles</t>
         </is>
@@ -1726,7 +1743,7 @@
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
-      <c r="J9" s="84" t="inlineStr">
+      <c r="J9" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1813,9 +1830,9 @@
           <t>Don't Look Back In Anger</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Oasis</t>
         </is>
@@ -1859,13 +1876,13 @@
           <t>Down By The River</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Neil Young</t>
         </is>
@@ -1876,7 +1893,7 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="G11" s="34" t="n"/>
+      <c r="G11" s="32" t="n"/>
       <c r="H11" s="1" t="inlineStr">
         <is>
           <t>70s</t>
@@ -1941,17 +1958,17 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>R.E.M.</t>
         </is>
@@ -1971,13 +1988,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" s="40" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr">
         <is>
           <t>80s</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="85" t="inlineStr">
+      <c r="J12" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2020,9 +2037,9 @@
           <t>Follow Your Arrow</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Kasey Musgraves</t>
         </is>
@@ -2074,9 +2091,9 @@
           <t>For What It's Worth</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Buffalo Springfield</t>
         </is>
@@ -2087,7 +2104,7 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="G14" s="35" t="n"/>
+      <c r="G14" s="33" t="n"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>60s</t>
@@ -2120,17 +2137,17 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C15" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Credence Clearwater Revival</t>
         </is>
@@ -2156,7 +2173,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
-      <c r="J15" s="84" t="inlineStr">
+      <c r="J15" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2227,13 +2244,13 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Gin Blossom</t>
         </is>
@@ -2309,13 +2326,13 @@
           <t>From The Start</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Laufey</t>
         </is>
@@ -2367,17 +2384,17 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="B18" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Jeff Tweedy</t>
         </is>
@@ -2403,7 +2420,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="85" t="inlineStr">
+      <c r="J18" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2454,17 +2471,17 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="B19" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C19" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Tears for Fears</t>
         </is>
@@ -2490,7 +2507,7 @@
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
-      <c r="J19" s="84" t="inlineStr">
+      <c r="J19" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2529,13 +2546,17 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C20" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>David Bowie</t>
         </is>
@@ -2615,9 +2636,9 @@
           <t>I've Got A Feeling</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Beates</t>
         </is>
@@ -2628,7 +2649,7 @@
           <t>Miles / Matt</t>
         </is>
       </c>
-      <c r="G21" s="34" t="n"/>
+      <c r="G21" s="32" t="n"/>
       <c r="H21" s="1" t="inlineStr">
         <is>
           <t>60s</t>
@@ -2661,17 +2682,17 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="B22" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C22" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>The Cure</t>
         </is>
@@ -2697,7 +2718,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="85" t="inlineStr">
+      <c r="J22" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2780,9 +2801,9 @@
           <t>Just What I Needed</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>The Cars</t>
         </is>
@@ -2858,13 +2879,13 @@
           <t>Kings Of Ewing</t>
         </is>
       </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>Kings of Ewing</t>
         </is>
@@ -2940,13 +2961,13 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="B25" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>James</t>
         </is>
@@ -3034,17 +3055,17 @@
           <t>Let Me Roll It</t>
         </is>
       </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C26" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="B26" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C26" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>Wings</t>
         </is>
@@ -3077,13 +3098,13 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="B27" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Oasis</t>
         </is>
@@ -3109,7 +3130,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="84" t="inlineStr">
+      <c r="J27" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3140,13 +3161,13 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="B28" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>The Police</t>
         </is>
@@ -3172,7 +3193,7 @@
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
-      <c r="J28" s="85" t="inlineStr">
+      <c r="J28" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3211,13 +3232,13 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="B29" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>The Allman Brothers Band</t>
         </is>
@@ -3309,17 +3330,17 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="B30" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>Santana</t>
         </is>
@@ -3345,7 +3366,7 @@
         </is>
       </c>
       <c r="I30" s="1" t="n"/>
-      <c r="J30" s="85" t="inlineStr">
+      <c r="J30" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3424,13 +3445,13 @@
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="B31" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>Beatles</t>
         </is>
@@ -3441,7 +3462,7 @@
           <t>Jack</t>
         </is>
       </c>
-      <c r="G31" s="35" t="n"/>
+      <c r="G31" s="33" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>60s</t>
@@ -3478,13 +3499,13 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B32" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="B32" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>CSNY</t>
         </is>
@@ -3556,17 +3577,17 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="B33" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C33" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Chappel Roan</t>
         </is>
@@ -3592,7 +3613,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
-      <c r="J33" s="84" t="inlineStr">
+      <c r="J33" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3659,13 +3680,13 @@
           <t>Riders On The Storm</t>
         </is>
       </c>
-      <c r="B34" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="B34" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>The Door</t>
         </is>
@@ -3741,13 +3762,13 @@
           <t>Rockin' In The Free World</t>
         </is>
       </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="B35" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>Neil Young</t>
         </is>
@@ -3823,13 +3844,13 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="B36" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="34" t="inlineStr">
+      <c r="B36" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>White Stripes</t>
         </is>
@@ -3840,7 +3861,7 @@
           <t>Drew</t>
         </is>
       </c>
-      <c r="G36" s="34" t="n"/>
+      <c r="G36" s="32" t="n"/>
       <c r="H36" s="1" t="inlineStr">
         <is>
           <t>00s</t>
@@ -3881,17 +3902,17 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C37" s="39" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="B37" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C37" s="77" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>Sade</t>
         </is>
@@ -3917,7 +3938,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n"/>
-      <c r="J37" s="84" t="inlineStr">
+      <c r="J37" s="72" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -3972,17 +3993,17 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="B38" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>Muse</t>
         </is>
@@ -4008,7 +4029,7 @@
         </is>
       </c>
       <c r="I38" s="1" t="n"/>
-      <c r="J38" s="85" t="inlineStr">
+      <c r="J38" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -4047,13 +4068,13 @@
           <t>Sympathy For The Devil</t>
         </is>
       </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="B39" s="77" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="33" t="inlineStr">
         <is>
           <t>Rolling Stones</t>
         </is>
@@ -4064,7 +4085,7 @@
           <t>Nate</t>
         </is>
       </c>
-      <c r="G39" s="35" t="n"/>
+      <c r="G39" s="33" t="n"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>60s</t>
@@ -4101,13 +4122,13 @@
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="34" t="inlineStr">
+      <c r="B40" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>CSNY</t>
         </is>
@@ -4118,7 +4139,7 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="G40" s="34" t="n"/>
+      <c r="G40" s="32" t="n"/>
       <c r="H40" s="1" t="inlineStr">
         <is>
           <t>70s</t>
@@ -4151,9 +4172,9 @@
           <t>That's What I Love</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n"/>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="B41" s="34" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>Leon Bridges</t>
         </is>
@@ -4173,7 +4194,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H41" s="41" t="inlineStr">
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
@@ -4213,9 +4234,9 @@
           <t>The Seeker</t>
         </is>
       </c>
-      <c r="B42" s="38" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="B42" s="36" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>The Who</t>
         </is>
@@ -4283,9 +4304,9 @@
           <t>Voodoo Child</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="33" t="inlineStr">
         <is>
           <t>Jimi Hendrix</t>
         </is>
@@ -4296,7 +4317,7 @@
           <t>Drew</t>
         </is>
       </c>
-      <c r="G43" s="35" t="n"/>
+      <c r="G43" s="33" t="n"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>60s</t>
@@ -4329,9 +4350,9 @@
           <t>Walk On</t>
         </is>
       </c>
-      <c r="B44" s="38" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="34" t="inlineStr">
+      <c r="B44" s="36" t="n"/>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>Neil Young</t>
         </is>
@@ -4347,7 +4368,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H44" s="40" t="inlineStr">
+      <c r="H44" s="38" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
@@ -4391,9 +4412,9 @@
           <t>War Pigs</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n"/>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="35" t="inlineStr">
+      <c r="B45" s="34" t="n"/>
+      <c r="C45" s="34" t="n"/>
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Black Sabbath </t>
         </is>
@@ -4404,7 +4425,7 @@
           <t>Miles</t>
         </is>
       </c>
-      <c r="G45" s="35" t="n"/>
+      <c r="G45" s="33" t="n"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>70s</t>
@@ -4437,17 +4458,17 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="B46" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>The Allman Brothers Band</t>
         </is>
@@ -4473,7 +4494,7 @@
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
-      <c r="J46" s="85" t="inlineStr">
+      <c r="J46" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -4560,9 +4581,9 @@
           <t>Who's That Lady</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n"/>
-      <c r="C47" s="36" t="n"/>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="B47" s="34" t="n"/>
+      <c r="C47" s="34" t="n"/>
+      <c r="D47" s="33" t="inlineStr">
         <is>
           <t>The Isley Brothers</t>
         </is>
@@ -4573,7 +4594,7 @@
           <t>Instrumental</t>
         </is>
       </c>
-      <c r="G47" s="35" t="n"/>
+      <c r="G47" s="33" t="n"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>70s</t>
@@ -4606,17 +4627,17 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="B48" s="76" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C48" s="76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>Tom Petty and the Heartbreakers</t>
         </is>
@@ -4642,7 +4663,7 @@
         </is>
       </c>
       <c r="I48" s="1" t="n"/>
-      <c r="J48" s="85" t="inlineStr">
+      <c r="J48" s="73" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -4704,6 +4725,22 @@
     </row>
   </sheetData>
   <hyperlinks>
+    <hyperlink ref="J2" location="'2026-05-14 Fat Shallot'!A1"/>
+    <hyperlink ref="K2" location="'2026-05-02 Lincolnwood'!A1"/>
+    <hyperlink ref="L2" location="'2026-04-22 Spring Cha Ching'!A1"/>
+    <hyperlink ref="M2" location="'2026-01-24 Goat Village'!A1"/>
+    <hyperlink ref="N2" location="'2025-11-16 Double Clutch'!A1"/>
+    <hyperlink ref="O2" location="'2025-09-06 Block Party'!A1"/>
+    <hyperlink ref="P2" location="'2025-06-25 American Legion'!A1"/>
+    <hyperlink ref="Q2" location="'2025-06-07 Fat Shallot'!A1"/>
+    <hyperlink ref="R2" location="'2025-05-03 Lincolnwood'!A1"/>
+    <hyperlink ref="S2" location="'2024-10-09 Fat Shallot'!A1"/>
+    <hyperlink ref="T2" location="'2024-09-07 Block Party'!A1"/>
+    <hyperlink ref="U2" location="'2024-08-10 Fat Shallot'!A1"/>
+    <hyperlink ref="V2" location="'2024-07-13 Chicago Union'!A1"/>
+    <hyperlink ref="W2" location="'2024-06-08 Fat Shallot'!A1"/>
+    <hyperlink ref="X2" location="'2024-04-27 Lincolnwood'!A1"/>
+    <hyperlink ref="Y2" location="'2023-09-09 Block Party'!A1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
@@ -4725,34 +4762,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4828,7 +4866,7 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -4850,12 +4888,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4880,12 +4918,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4910,12 +4948,12 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4940,12 +4978,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -4970,12 +5008,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5000,7 +5038,7 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5030,12 +5068,12 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5060,7 +5098,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5086,12 +5124,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5116,12 +5154,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5146,12 +5184,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5176,12 +5214,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5206,12 +5244,12 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5236,12 +5274,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="C17" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5266,12 +5304,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5296,12 +5334,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5317,6 +5355,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="inlineStr">
@@ -5440,12 +5479,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5470,12 +5509,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5500,12 +5539,12 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5530,12 +5569,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5560,12 +5599,12 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5590,7 +5629,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5616,12 +5655,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5646,12 +5685,12 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5676,12 +5715,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5706,12 +5745,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5727,6 +5766,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="inlineStr">
@@ -5837,12 +5877,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -5867,7 +5907,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5893,7 +5933,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5919,7 +5959,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5945,7 +5985,7 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="89" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -5975,12 +6015,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6005,12 +6045,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6035,12 +6075,12 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6109,12 +6149,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6139,12 +6179,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6169,12 +6209,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6199,12 +6239,12 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6229,12 +6269,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6259,12 +6299,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6311,12 +6351,12 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6341,12 +6381,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6371,12 +6411,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="C22" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6445,7 +6485,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6471,7 +6511,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6519,7 +6559,7 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6545,7 +6585,7 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6615,12 +6655,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="C32" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D32" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6784,7 +6824,7 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6814,12 +6854,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6844,7 +6884,7 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6870,12 +6910,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6900,7 +6940,7 @@
           <t>Teach Your Children</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -6922,12 +6962,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -6974,12 +7014,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7004,12 +7044,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7052,12 +7092,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7082,7 +7122,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -7108,12 +7148,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7129,6 +7169,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="9" t="inlineStr">
@@ -7239,12 +7280,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7269,12 +7310,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7299,12 +7340,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7329,12 +7370,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7377,12 +7418,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7407,12 +7448,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7437,12 +7478,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7467,12 +7508,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7555,12 +7596,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7594,6 +7635,7 @@
       </c>
       <c r="F16" s="12" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="9" t="inlineStr">
@@ -7703,12 +7745,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7733,12 +7775,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7763,12 +7805,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7811,12 +7853,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7863,7 +7905,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -7907,12 +7949,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7955,12 +7997,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -7985,7 +8027,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8033,12 +8075,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8063,12 +8105,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8093,7 +8135,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8137,7 +8179,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8185,12 +8227,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="C22" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8259,7 +8301,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8281,7 +8323,7 @@
           <t>Come Together</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8325,7 +8367,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8351,12 +8393,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="C29" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8394,6 +8436,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="inlineStr">
@@ -8512,12 +8555,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8542,12 +8585,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8572,12 +8615,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8620,12 +8663,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8690,7 +8733,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8716,12 +8759,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8768,12 +8811,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8798,12 +8841,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -8846,7 +8889,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8938,7 +8981,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -8964,12 +9007,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9009,6 +9052,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="inlineStr">
@@ -9137,12 +9181,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9167,12 +9211,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9197,12 +9241,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9249,12 +9293,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9279,12 +9323,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9327,12 +9371,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9357,7 +9401,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -9405,12 +9449,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9435,12 +9479,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9480,6 +9524,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="9" t="inlineStr">
@@ -9588,12 +9633,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9618,12 +9663,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9648,7 +9693,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -9674,12 +9719,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9722,12 +9767,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9774,7 +9819,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -9840,12 +9885,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9861,6 +9906,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="inlineStr">
@@ -9964,12 +10010,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -9994,12 +10040,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10024,12 +10070,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10054,7 +10100,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10080,7 +10126,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10106,12 +10152,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10136,12 +10182,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10166,7 +10212,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10188,7 +10234,7 @@
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10250,7 +10296,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10276,12 +10322,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10400,12 +10446,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10430,7 +10476,7 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10474,7 +10520,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10500,12 +10546,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -10552,7 +10598,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -10587,6 +10633,7 @@
       </c>
       <c r="F28" s="12" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="n"/>
       <c r="B30" s="9" t="inlineStr">
@@ -10653,113 +10700,113 @@
     <col width="33" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="8.1640625" bestFit="1" customWidth="1" style="74" min="11" max="11"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" style="78" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="28" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>KINGS OF EWING — GIG LOG</t>
         </is>
       </c>
-      <c r="K1" s="75" t="n"/>
-    </row>
-    <row r="2" ht="22" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="K1" s="79" t="n"/>
+    </row>
+    <row r="2" ht="22" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="48" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C2" s="47" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E2" s="44" t="inlineStr">
         <is>
           <t># Songs</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="46" t="inlineStr">
         <is>
           <t>Gig Length</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="G2" s="44" t="inlineStr">
         <is>
           <t>Venue Name</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
+      <c r="H2" s="44" t="inlineStr">
         <is>
           <t>Venue Email</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="I2" s="44" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="J2" s="44" t="inlineStr">
         <is>
           <t>Event Email</t>
         </is>
       </c>
-      <c r="K2" s="76" t="inlineStr">
+      <c r="K2" s="80" t="inlineStr">
         <is>
           <t>Pay</t>
         </is>
       </c>
-      <c r="L2" s="47" t="inlineStr">
+      <c r="L2" s="44" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" thickTop="1">
-      <c r="A3" s="86" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="C3" s="44" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>Block Party</t>
         </is>
       </c>
-      <c r="D3" s="44" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>Ewing Block Party</t>
         </is>
       </c>
-      <c r="E3" s="44" t="n">
+      <c r="E3" s="41" t="n">
         <v>10</v>
       </c>
       <c r="F3" s="19" t="n"/>
-      <c r="G3" s="44" t="n"/>
-      <c r="H3" s="44" t="n"/>
-      <c r="I3" s="44" t="n"/>
-      <c r="J3" s="44" t="n"/>
-      <c r="K3" s="77" t="n"/>
-      <c r="L3" s="44" t="n"/>
+      <c r="G3" s="41" t="n"/>
+      <c r="H3" s="41" t="n"/>
+      <c r="I3" s="41" t="n"/>
+      <c r="J3" s="41" t="n"/>
+      <c r="K3" s="82" t="n"/>
+      <c r="L3" s="41" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="86" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>2024-04-27</t>
         </is>
@@ -10787,11 +10834,11 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="78" t="n"/>
+      <c r="K4" s="83" t="n"/>
       <c r="L4" s="2" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
@@ -10823,11 +10870,11 @@
       </c>
       <c r="I5" s="1" t="n"/>
       <c r="J5" s="1" t="n"/>
-      <c r="K5" s="79" t="n"/>
+      <c r="K5" s="84" t="n"/>
       <c r="L5" s="1" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>2024-07-13</t>
         </is>
@@ -10863,13 +10910,13 @@
       </c>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
-      <c r="K6" s="78" t="n">
+      <c r="K6" s="83" t="n">
         <v>100</v>
       </c>
       <c r="L6" s="2" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>2024-08-10</t>
         </is>
@@ -10901,11 +10948,11 @@
       </c>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
-      <c r="K7" s="79" t="n"/>
+      <c r="K7" s="84" t="n"/>
       <c r="L7" s="1" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
@@ -10933,11 +10980,11 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
-      <c r="K8" s="78" t="n"/>
+      <c r="K8" s="83" t="n"/>
       <c r="L8" s="2" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>2024-10-09</t>
         </is>
@@ -10973,11 +11020,11 @@
       </c>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
-      <c r="K9" s="79" t="n"/>
+      <c r="K9" s="84" t="n"/>
       <c r="L9" s="1" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
@@ -11005,11 +11052,11 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="78" t="n"/>
+      <c r="K10" s="83" t="n"/>
       <c r="L10" s="2" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
@@ -11041,11 +11088,11 @@
       </c>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
-      <c r="K11" s="78" t="n"/>
+      <c r="K11" s="83" t="n"/>
       <c r="L11" s="2" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>2025-06-25</t>
         </is>
@@ -11069,11 +11116,11 @@
       <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
-      <c r="K12" s="79" t="n"/>
+      <c r="K12" s="84" t="n"/>
       <c r="L12" s="1" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
@@ -11101,11 +11148,11 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="78" t="n"/>
+      <c r="K13" s="83" t="n"/>
       <c r="L13" s="2" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>2025-10-18</t>
         </is>
@@ -11131,7 +11178,7 @@
       </c>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="n"/>
-      <c r="K14" s="79" t="n"/>
+      <c r="K14" s="84" t="n"/>
       <c r="L14" s="1" t="inlineStr">
         <is>
           <t>Cancelled due to weather</t>
@@ -11139,7 +11186,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
@@ -11185,11 +11232,11 @@
           <t>krys@faithatfirst.com</t>
         </is>
       </c>
-      <c r="K15" s="78" t="n"/>
+      <c r="K15" s="83" t="n"/>
       <c r="L15" s="2" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
@@ -11221,11 +11268,11 @@
       </c>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
-      <c r="K16" s="79" t="n"/>
+      <c r="K16" s="84" t="n"/>
       <c r="L16" s="1" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -11255,11 +11302,11 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
-      <c r="K17" s="78" t="n"/>
+      <c r="K17" s="83" t="n"/>
       <c r="L17" s="2" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
@@ -11289,11 +11336,11 @@
       <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="n"/>
-      <c r="K18" s="79" t="n"/>
+      <c r="K18" s="84" t="n"/>
       <c r="L18" s="1" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="86" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -11337,11 +11384,11 @@
           <t>kims@covenantnurseryschool.org</t>
         </is>
       </c>
-      <c r="K19" s="78" t="n"/>
+      <c r="K19" s="83" t="n"/>
       <c r="L19" s="2" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
@@ -11385,13 +11432,13 @@
           <t>Jenny.Sprenzel@rushortho.com</t>
         </is>
       </c>
-      <c r="K20" s="79" t="n">
+      <c r="K20" s="84" t="n">
         <v>150</v>
       </c>
       <c r="L20" s="1" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
@@ -11421,11 +11468,11 @@
       </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
-      <c r="K21" s="78" t="n"/>
+      <c r="K21" s="83" t="n"/>
       <c r="L21" s="2" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
@@ -11459,31 +11506,31 @@
       </c>
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="n"/>
-      <c r="K22" s="79" t="n"/>
+      <c r="K22" s="84" t="n"/>
       <c r="L22" s="1" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
+    <hyperlink ref="A3" location="'2023-09-09 Block Party'!A1"/>
+    <hyperlink ref="A4" location="'2024-04-27 Lincolnwood'!A1"/>
+    <hyperlink ref="A5" location="'2024-06-08 Fat Shallot'!A1"/>
+    <hyperlink ref="A6" location="'2024-07-13 Chicago Union'!A1"/>
+    <hyperlink ref="A7" location="'2024-08-10 Fat Shallot'!A1"/>
+    <hyperlink ref="A8" location="'2024-09-07 Block Party'!A1"/>
+    <hyperlink ref="A9" location="'2024-10-09 Fat Shallot'!A1"/>
+    <hyperlink ref="A10" location="'2025-05-03 Lincolnwood'!A1"/>
+    <hyperlink ref="A11" location="'2025-06-07 Fat Shallot'!A1"/>
+    <hyperlink ref="A12" location="'2025-06-25 American Legion'!A1"/>
+    <hyperlink ref="A13" location="'2025-09-06 Block Party'!A1"/>
+    <hyperlink ref="A15" location="'2025-11-16 Double Clutch'!A1"/>
+    <hyperlink ref="A16" location="'2026-01-24 Goat Village'!A1"/>
+    <hyperlink ref="A17" location="'2026-04-22 Spring Cha Ching'!A1"/>
+    <hyperlink ref="A18" location="'2026-05-02 Lincolnwood'!A1"/>
+    <hyperlink ref="A19" location="'2026-05-14 Fat Shallot'!A1"/>
+    <hyperlink ref="A20" location="'2026-05-16 Fat Shallot'!A1"/>
+    <hyperlink ref="A21" location="'2026-06-24 Ridgeville Parks'!A1"/>
+    <hyperlink ref="A22" location="'2026-06-21 Chicago Union'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11557,12 +11604,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11587,12 +11634,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11617,12 +11664,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11647,7 +11694,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11673,7 +11720,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11699,12 +11746,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11729,12 +11776,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -11759,7 +11806,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11821,7 +11868,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11905,7 +11952,7 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11949,7 +11996,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -11975,12 +12022,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12005,12 +12052,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12057,7 +12104,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12074,6 +12121,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="inlineStr">
@@ -12186,12 +12234,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12216,12 +12264,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12246,7 +12294,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12272,12 +12320,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12302,7 +12350,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12328,12 +12376,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12358,7 +12406,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12384,7 +12432,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12428,12 +12476,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12458,7 +12506,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12475,6 +12523,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="inlineStr">
@@ -12581,12 +12630,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12611,12 +12660,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12641,12 +12690,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12671,7 +12720,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12697,7 +12746,7 @@
           <t>Laid</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12723,12 +12772,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12753,12 +12802,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12783,7 +12832,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12893,12 +12942,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12923,12 +12972,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -12953,7 +13002,7 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -12992,6 +13041,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="inlineStr">
@@ -13101,12 +13151,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13131,12 +13181,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13161,12 +13211,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13191,12 +13241,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13239,7 +13289,7 @@
           <t>Seven Nation Army</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13283,7 +13333,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13309,12 +13359,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13339,7 +13389,7 @@
           <t>Midnight Rider</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13483,12 +13533,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13513,7 +13563,7 @@
           <t>Found Out About You</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13539,7 +13589,7 @@
           <t>Octopus's Garden</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13601,12 +13651,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13649,12 +13699,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13679,12 +13729,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -13709,7 +13759,7 @@
           <t>Heroes</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13726,6 +13776,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="inlineStr">
@@ -13766,149 +13817,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="31.5" customWidth="1" min="1" max="1"/>
+    <col width="19.1640625" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="28" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>KINGS OF EWING — POTENTIAL SONGS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A2" s="47" t="inlineStr">
-        <is>
-          <t>Song</t>
-        </is>
-      </c>
-      <c r="B2" s="47" t="inlineStr">
-        <is>
-          <t>Artist</t>
-        </is>
-      </c>
-      <c r="C2" s="47" t="inlineStr">
-        <is>
-          <t>Who Suggested</t>
-        </is>
-      </c>
-      <c r="D2" s="47" t="inlineStr">
-        <is>
-          <t>Decade</t>
-        </is>
-      </c>
-      <c r="E2" s="47" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" thickTop="1">
-      <c r="A3" s="57" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" thickTop="1">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Let It Roll</t>
         </is>
       </c>
-      <c r="B3" s="57" t="inlineStr">
+      <c r="B2" s="54" t="inlineStr">
         <is>
           <t>Little Feat</t>
         </is>
       </c>
-      <c r="C3" s="57" t="inlineStr">
+      <c r="C2" s="54" t="inlineStr">
         <is>
           <t>Jim</t>
         </is>
       </c>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D2" s="54" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="E3" s="57" t="inlineStr">
+      <c r="E2" s="54" t="inlineStr">
         <is>
           <t>Down By the River replacement</t>
         </is>
       </c>
     </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Short Skirt/Long Jacket</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Cake</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Drew / Matt</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Matt will sing</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Short Skirt/Long Jacket</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Cake</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Drew / Matt</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Blinding Lights</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>The Weeknd</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Electric Feel</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>00s</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>Matt will sing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Blinding Lights</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>The Weeknd</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>20s</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Electric Feel</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>MGMT</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>00s</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Miles could sing — needs falsetto. 90% about finding right patches for Matt</t>
         </is>
@@ -13937,78 +13961,78 @@
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customFormat="1" customHeight="1" s="60" thickBot="1" thickTop="1">
-      <c r="A1" s="59" t="inlineStr">
+    <row r="1" ht="28" customFormat="1" customHeight="1" s="57" thickBot="1" thickTop="1">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>KINGS OF EWING — POTENTIAL GIGS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customFormat="1" customHeight="1" s="60" thickBot="1" thickTop="1">
-      <c r="A2" s="61" t="inlineStr">
+    <row r="2" ht="22" customFormat="1" customHeight="1" s="57" thickBot="1" thickTop="1">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="58" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="58" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="58" t="inlineStr">
         <is>
           <t>Date Reached Out</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="58" t="inlineStr">
         <is>
           <t>Proposed Date</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr">
+      <c r="F2" s="58" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G2" s="61" t="inlineStr">
+      <c r="G2" s="58" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" thickTop="1">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Downtown Evanston</t>
         </is>
       </c>
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>Andy Vick</t>
         </is>
       </c>
-      <c r="C3" s="44" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>avick@downtownevanston.org</t>
         </is>
       </c>
-      <c r="D3" s="44" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="E3" s="44" t="n"/>
-      <c r="F3" s="44" t="inlineStr">
+      <c r="E3" s="41" t="n"/>
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>Waiting</t>
         </is>
       </c>
-      <c r="G3" s="44" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>Puts music line-up together in January — follow up Jan 2026</t>
         </is>
@@ -14072,308 +14096,308 @@
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="28" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>KINGS OF EWING — EXPENSES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customFormat="1" customHeight="1" s="46" thickBot="1" thickTop="1">
-      <c r="A2" s="58" t="inlineStr">
+    <row r="2" ht="22" customFormat="1" customHeight="1" s="43" thickBot="1" thickTop="1">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>Paid By</t>
         </is>
       </c>
-      <c r="D2" s="58" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E2" s="58" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" thickTop="1">
-      <c r="A3" s="71" t="n">
+      <c r="A3" s="68" t="n">
         <v>46154</v>
       </c>
-      <c r="B3" s="69" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>polytune 3 from sweetwater</t>
         </is>
       </c>
-      <c r="C3" s="69" t="inlineStr">
+      <c r="C3" s="66" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="D3" s="80" t="n">
+      <c r="D3" s="85" t="n">
         <v>86.98999999999999</v>
       </c>
-      <c r="E3" s="69" t="inlineStr">
+      <c r="E3" s="66" t="inlineStr">
         <is>
           <t>replacement for lost one</t>
         </is>
       </c>
-      <c r="F3" s="69" t="n"/>
-      <c r="G3" s="69" t="n"/>
-      <c r="H3" s="69" t="n"/>
+      <c r="F3" s="66" t="n"/>
+      <c r="G3" s="66" t="n"/>
+      <c r="H3" s="66" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="69" t="n"/>
-      <c r="B4" s="69" t="n"/>
-      <c r="C4" s="69" t="n"/>
-      <c r="D4" s="80" t="n"/>
-      <c r="E4" s="69" t="n"/>
-      <c r="F4" s="69" t="n"/>
-      <c r="G4" s="69" t="n"/>
-      <c r="H4" s="69" t="n"/>
+      <c r="A4" s="66" t="n"/>
+      <c r="B4" s="66" t="n"/>
+      <c r="C4" s="66" t="n"/>
+      <c r="D4" s="85" t="n"/>
+      <c r="E4" s="66" t="n"/>
+      <c r="F4" s="66" t="n"/>
+      <c r="G4" s="66" t="n"/>
+      <c r="H4" s="66" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="69" t="n"/>
-      <c r="B5" s="69" t="n"/>
-      <c r="C5" s="69" t="n"/>
-      <c r="D5" s="80" t="n"/>
-      <c r="E5" s="69" t="n"/>
-      <c r="F5" s="69" t="n"/>
-      <c r="G5" s="69" t="n"/>
-      <c r="H5" s="69" t="n"/>
+      <c r="A5" s="66" t="n"/>
+      <c r="B5" s="66" t="n"/>
+      <c r="C5" s="66" t="n"/>
+      <c r="D5" s="85" t="n"/>
+      <c r="E5" s="66" t="n"/>
+      <c r="F5" s="66" t="n"/>
+      <c r="G5" s="66" t="n"/>
+      <c r="H5" s="66" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="69" t="n"/>
-      <c r="B6" s="69" t="n"/>
-      <c r="C6" s="69" t="n"/>
-      <c r="D6" s="80" t="n"/>
-      <c r="E6" s="69" t="n"/>
-      <c r="F6" s="69" t="n"/>
-      <c r="G6" s="69" t="n"/>
-      <c r="H6" s="69" t="n"/>
+      <c r="A6" s="66" t="n"/>
+      <c r="B6" s="66" t="n"/>
+      <c r="C6" s="66" t="n"/>
+      <c r="D6" s="85" t="n"/>
+      <c r="E6" s="66" t="n"/>
+      <c r="F6" s="66" t="n"/>
+      <c r="G6" s="66" t="n"/>
+      <c r="H6" s="66" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="69" t="n"/>
-      <c r="B7" s="69" t="n"/>
-      <c r="C7" s="69" t="n"/>
-      <c r="D7" s="80" t="n"/>
-      <c r="E7" s="69" t="n"/>
-      <c r="F7" s="69" t="n"/>
-      <c r="G7" s="69" t="n"/>
-      <c r="H7" s="69" t="n"/>
+      <c r="A7" s="66" t="n"/>
+      <c r="B7" s="66" t="n"/>
+      <c r="C7" s="66" t="n"/>
+      <c r="D7" s="85" t="n"/>
+      <c r="E7" s="66" t="n"/>
+      <c r="F7" s="66" t="n"/>
+      <c r="G7" s="66" t="n"/>
+      <c r="H7" s="66" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="69" t="n"/>
-      <c r="B8" s="69" t="n"/>
-      <c r="C8" s="69" t="n"/>
-      <c r="D8" s="80" t="n"/>
-      <c r="E8" s="69" t="n"/>
-      <c r="F8" s="69" t="n"/>
-      <c r="G8" s="69" t="n"/>
-      <c r="H8" s="69" t="n"/>
+      <c r="A8" s="66" t="n"/>
+      <c r="B8" s="66" t="n"/>
+      <c r="C8" s="66" t="n"/>
+      <c r="D8" s="85" t="n"/>
+      <c r="E8" s="66" t="n"/>
+      <c r="F8" s="66" t="n"/>
+      <c r="G8" s="66" t="n"/>
+      <c r="H8" s="66" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="69" t="n"/>
-      <c r="B9" s="69" t="n"/>
-      <c r="C9" s="69" t="n"/>
-      <c r="D9" s="80" t="n"/>
-      <c r="E9" s="69" t="n"/>
-      <c r="F9" s="69" t="n"/>
-      <c r="G9" s="69" t="n"/>
-      <c r="H9" s="69" t="n"/>
+      <c r="A9" s="66" t="n"/>
+      <c r="B9" s="66" t="n"/>
+      <c r="C9" s="66" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="66" t="n"/>
+      <c r="F9" s="66" t="n"/>
+      <c r="G9" s="66" t="n"/>
+      <c r="H9" s="66" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="69" t="n"/>
-      <c r="B10" s="69" t="n"/>
-      <c r="C10" s="69" t="n"/>
-      <c r="D10" s="80" t="n"/>
-      <c r="E10" s="69" t="n"/>
-      <c r="F10" s="69" t="n"/>
-      <c r="G10" s="69" t="n"/>
-      <c r="H10" s="69" t="n"/>
+      <c r="A10" s="66" t="n"/>
+      <c r="B10" s="66" t="n"/>
+      <c r="C10" s="66" t="n"/>
+      <c r="D10" s="85" t="n"/>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="66" t="n"/>
+      <c r="G10" s="66" t="n"/>
+      <c r="H10" s="66" t="n"/>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="69" t="n"/>
-      <c r="B11" s="69" t="n"/>
-      <c r="C11" s="69" t="n"/>
-      <c r="D11" s="80" t="n"/>
-      <c r="E11" s="69" t="n"/>
-      <c r="F11" s="69" t="n"/>
-      <c r="G11" s="69" t="n"/>
-      <c r="H11" s="69" t="n"/>
+      <c r="A11" s="66" t="n"/>
+      <c r="B11" s="66" t="n"/>
+      <c r="C11" s="66" t="n"/>
+      <c r="D11" s="85" t="n"/>
+      <c r="E11" s="66" t="n"/>
+      <c r="F11" s="66" t="n"/>
+      <c r="G11" s="66" t="n"/>
+      <c r="H11" s="66" t="n"/>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="69" t="n"/>
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="69" t="n"/>
-      <c r="D12" s="80" t="n"/>
-      <c r="E12" s="69" t="n"/>
-      <c r="F12" s="69" t="n"/>
-      <c r="G12" s="69" t="n"/>
-      <c r="H12" s="69" t="n"/>
+      <c r="A12" s="66" t="n"/>
+      <c r="B12" s="66" t="n"/>
+      <c r="C12" s="66" t="n"/>
+      <c r="D12" s="85" t="n"/>
+      <c r="E12" s="66" t="n"/>
+      <c r="F12" s="66" t="n"/>
+      <c r="G12" s="66" t="n"/>
+      <c r="H12" s="66" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="69" t="n"/>
-      <c r="B13" s="69" t="n"/>
-      <c r="C13" s="69" t="n"/>
-      <c r="D13" s="80" t="n"/>
-      <c r="E13" s="69" t="n"/>
-      <c r="F13" s="69" t="n"/>
-      <c r="G13" s="69" t="n"/>
-      <c r="H13" s="69" t="n"/>
+      <c r="A13" s="66" t="n"/>
+      <c r="B13" s="66" t="n"/>
+      <c r="C13" s="66" t="n"/>
+      <c r="D13" s="85" t="n"/>
+      <c r="E13" s="66" t="n"/>
+      <c r="F13" s="66" t="n"/>
+      <c r="G13" s="66" t="n"/>
+      <c r="H13" s="66" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="69" t="n"/>
-      <c r="B14" s="69" t="n"/>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="80" t="n"/>
-      <c r="E14" s="69" t="n"/>
-      <c r="F14" s="69" t="n"/>
-      <c r="G14" s="69" t="n"/>
-      <c r="H14" s="69" t="n"/>
+      <c r="A14" s="66" t="n"/>
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="85" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="66" t="n"/>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="69" t="n"/>
-      <c r="B15" s="69" t="n"/>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="80" t="n"/>
-      <c r="E15" s="69" t="n"/>
-      <c r="F15" s="69" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="69" t="n"/>
+      <c r="A15" s="66" t="n"/>
+      <c r="B15" s="66" t="n"/>
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="85" t="n"/>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="66" t="n"/>
+      <c r="G15" s="66" t="n"/>
+      <c r="H15" s="66" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="69" t="n"/>
-      <c r="B16" s="69" t="n"/>
-      <c r="C16" s="69" t="n"/>
-      <c r="D16" s="80" t="n"/>
-      <c r="E16" s="69" t="n"/>
-      <c r="F16" s="69" t="n"/>
-      <c r="G16" s="69" t="n"/>
-      <c r="H16" s="69" t="n"/>
+      <c r="A16" s="66" t="n"/>
+      <c r="B16" s="66" t="n"/>
+      <c r="C16" s="66" t="n"/>
+      <c r="D16" s="85" t="n"/>
+      <c r="E16" s="66" t="n"/>
+      <c r="F16" s="66" t="n"/>
+      <c r="G16" s="66" t="n"/>
+      <c r="H16" s="66" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="69" t="n"/>
-      <c r="C17" s="69" t="n"/>
-      <c r="D17" s="80" t="n"/>
-      <c r="E17" s="69" t="n"/>
-      <c r="F17" s="69" t="n"/>
-      <c r="G17" s="69" t="n"/>
-      <c r="H17" s="69" t="n"/>
+      <c r="A17" s="66" t="n"/>
+      <c r="B17" s="66" t="n"/>
+      <c r="C17" s="66" t="n"/>
+      <c r="D17" s="85" t="n"/>
+      <c r="E17" s="66" t="n"/>
+      <c r="F17" s="66" t="n"/>
+      <c r="G17" s="66" t="n"/>
+      <c r="H17" s="66" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="69" t="n"/>
-      <c r="B18" s="69" t="n"/>
-      <c r="C18" s="69" t="n"/>
-      <c r="D18" s="80" t="n"/>
-      <c r="E18" s="69" t="n"/>
-      <c r="F18" s="69" t="n"/>
-      <c r="G18" s="69" t="n"/>
-      <c r="H18" s="69" t="n"/>
+      <c r="A18" s="66" t="n"/>
+      <c r="B18" s="66" t="n"/>
+      <c r="C18" s="66" t="n"/>
+      <c r="D18" s="85" t="n"/>
+      <c r="E18" s="66" t="n"/>
+      <c r="F18" s="66" t="n"/>
+      <c r="G18" s="66" t="n"/>
+      <c r="H18" s="66" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="69" t="n"/>
-      <c r="B19" s="69" t="n"/>
-      <c r="C19" s="69" t="n"/>
-      <c r="D19" s="80" t="n"/>
-      <c r="E19" s="69" t="n"/>
-      <c r="F19" s="69" t="n"/>
-      <c r="G19" s="69" t="n"/>
-      <c r="H19" s="69" t="n"/>
+      <c r="A19" s="66" t="n"/>
+      <c r="B19" s="66" t="n"/>
+      <c r="C19" s="66" t="n"/>
+      <c r="D19" s="85" t="n"/>
+      <c r="E19" s="66" t="n"/>
+      <c r="F19" s="66" t="n"/>
+      <c r="G19" s="66" t="n"/>
+      <c r="H19" s="66" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="69" t="n"/>
-      <c r="B20" s="69" t="n"/>
-      <c r="C20" s="69" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="69" t="n"/>
-      <c r="F20" s="69" t="n"/>
-      <c r="G20" s="69" t="n"/>
-      <c r="H20" s="69" t="n"/>
+      <c r="A20" s="66" t="n"/>
+      <c r="B20" s="66" t="n"/>
+      <c r="C20" s="66" t="n"/>
+      <c r="D20" s="85" t="n"/>
+      <c r="E20" s="66" t="n"/>
+      <c r="F20" s="66" t="n"/>
+      <c r="G20" s="66" t="n"/>
+      <c r="H20" s="66" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="69" t="n"/>
-      <c r="B21" s="69" t="n"/>
-      <c r="C21" s="69" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="69" t="n"/>
-      <c r="F21" s="69" t="n"/>
-      <c r="G21" s="69" t="n"/>
-      <c r="H21" s="69" t="n"/>
+      <c r="A21" s="66" t="n"/>
+      <c r="B21" s="66" t="n"/>
+      <c r="C21" s="66" t="n"/>
+      <c r="D21" s="85" t="n"/>
+      <c r="E21" s="66" t="n"/>
+      <c r="F21" s="66" t="n"/>
+      <c r="G21" s="66" t="n"/>
+      <c r="H21" s="66" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="69" t="n"/>
-      <c r="B22" s="69" t="n"/>
-      <c r="C22" s="69" t="n"/>
-      <c r="D22" s="80" t="n"/>
-      <c r="E22" s="69" t="n"/>
-      <c r="F22" s="69" t="n"/>
-      <c r="G22" s="69" t="n"/>
-      <c r="H22" s="69" t="n"/>
+      <c r="A22" s="66" t="n"/>
+      <c r="B22" s="66" t="n"/>
+      <c r="C22" s="66" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="66" t="n"/>
+      <c r="F22" s="66" t="n"/>
+      <c r="G22" s="66" t="n"/>
+      <c r="H22" s="66" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="69" t="n"/>
-      <c r="B23" s="69" t="n"/>
-      <c r="C23" s="69" t="n"/>
-      <c r="D23" s="80" t="n"/>
-      <c r="E23" s="69" t="n"/>
-      <c r="F23" s="69" t="n"/>
-      <c r="G23" s="69" t="n"/>
-      <c r="H23" s="69" t="n"/>
+      <c r="A23" s="66" t="n"/>
+      <c r="B23" s="66" t="n"/>
+      <c r="C23" s="66" t="n"/>
+      <c r="D23" s="85" t="n"/>
+      <c r="E23" s="66" t="n"/>
+      <c r="F23" s="66" t="n"/>
+      <c r="G23" s="66" t="n"/>
+      <c r="H23" s="66" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="69" t="n"/>
-      <c r="B24" s="69" t="n"/>
-      <c r="C24" s="69" t="n"/>
-      <c r="D24" s="80" t="n"/>
-      <c r="E24" s="69" t="n"/>
-      <c r="F24" s="69" t="n"/>
-      <c r="G24" s="69" t="n"/>
-      <c r="H24" s="69" t="n"/>
+      <c r="A24" s="66" t="n"/>
+      <c r="B24" s="66" t="n"/>
+      <c r="C24" s="66" t="n"/>
+      <c r="D24" s="85" t="n"/>
+      <c r="E24" s="66" t="n"/>
+      <c r="F24" s="66" t="n"/>
+      <c r="G24" s="66" t="n"/>
+      <c r="H24" s="66" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="69" t="n"/>
-      <c r="B25" s="69" t="n"/>
-      <c r="C25" s="69" t="n"/>
-      <c r="D25" s="80" t="n"/>
-      <c r="E25" s="69" t="n"/>
-      <c r="F25" s="69" t="n"/>
-      <c r="G25" s="69" t="n"/>
-      <c r="H25" s="69" t="n"/>
+      <c r="A25" s="66" t="n"/>
+      <c r="B25" s="66" t="n"/>
+      <c r="C25" s="66" t="n"/>
+      <c r="D25" s="85" t="n"/>
+      <c r="E25" s="66" t="n"/>
+      <c r="F25" s="66" t="n"/>
+      <c r="G25" s="66" t="n"/>
+      <c r="H25" s="66" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="69" t="n"/>
-      <c r="B26" s="69" t="n"/>
-      <c r="C26" s="69" t="n"/>
-      <c r="D26" s="80" t="n"/>
-      <c r="E26" s="69" t="n"/>
-      <c r="F26" s="69" t="n"/>
-      <c r="G26" s="69" t="n"/>
-      <c r="H26" s="69" t="n"/>
+      <c r="A26" s="66" t="n"/>
+      <c r="B26" s="66" t="n"/>
+      <c r="C26" s="66" t="n"/>
+      <c r="D26" s="85" t="n"/>
+      <c r="E26" s="66" t="n"/>
+      <c r="F26" s="66" t="n"/>
+      <c r="G26" s="66" t="n"/>
+      <c r="H26" s="66" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="70" t="n"/>
-      <c r="B27" s="70" t="n"/>
-      <c r="C27" s="70" t="n"/>
-      <c r="D27" s="81" t="n"/>
-      <c r="E27" s="70" t="n"/>
-      <c r="F27" s="70" t="n"/>
-      <c r="G27" s="70" t="n"/>
-      <c r="H27" s="70" t="n"/>
+      <c r="A27" s="67" t="n"/>
+      <c r="B27" s="67" t="n"/>
+      <c r="C27" s="67" t="n"/>
+      <c r="D27" s="86" t="n"/>
+      <c r="E27" s="67" t="n"/>
+      <c r="F27" s="67" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="82" t="n"/>
+      <c r="D28" s="87" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14439,6 +14463,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="inlineStr">
@@ -14519,6 +14544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="inlineStr">
@@ -14599,6 +14625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="inlineStr">
@@ -14632,7 +14659,8 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="4"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" thickBot="1">
@@ -14688,12 +14716,12 @@
           <t>Don't Let Me Down</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14718,12 +14746,12 @@
           <t>Pink Pony Club</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14748,12 +14776,12 @@
           <t>Head Over Heels</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14778,12 +14806,12 @@
           <t>Just Like Heaven</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14808,12 +14836,12 @@
           <t>Guess Again</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="89" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14838,7 +14866,7 @@
           <t>Message In A Bottle</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -14868,12 +14896,12 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14898,7 +14926,7 @@
           <t>Little By Little</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -14928,12 +14956,12 @@
           <t>No One To Depend On</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14958,12 +14986,12 @@
           <t>Fortunate Son</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -14988,12 +15016,12 @@
           <t>Smooth Operator</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15018,12 +15046,12 @@
           <t>Bohemian Like Me</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15048,12 +15076,12 @@
           <t>Starlight</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15078,12 +15106,12 @@
           <t>End Of The World</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="C16" s="91" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15108,12 +15136,12 @@
           <t>Won't Back Down</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15138,12 +15166,12 @@
           <t>Whipping Post</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
@@ -15159,6 +15187,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="inlineStr">

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7DCEFE-C52E-9946-84A8-07803D3C7213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DC5669-7DED-EA43-ABB6-E97FFF9F3261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43040" yWindow="3360" windowWidth="25600" windowHeight="16000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -1020,7 +1020,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1150,6 +1150,19 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Courier New"/>
       <family val="1"/>
     </font>
@@ -1479,7 +1492,7 @@
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1704,12 +1717,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2118,10 +2130,10 @@
       <c r="A3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="89" t="s">
+      <c r="B3" s="88" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="88" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="51" t="s">
@@ -2699,7 +2711,7 @@
       <c r="A14" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="88" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="55" t="s">
@@ -3190,7 +3202,7 @@
       <c r="A23" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="89" t="s">
+      <c r="B23" s="88" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="64" t="s">
@@ -11761,39 +11773,40 @@
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="5" max="5" width="93.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="23" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="89" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+    <row r="2" spans="1:8" s="89" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="90" t="s">
         <v>305</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="90" t="s">
         <v>306</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="90" t="s">
         <v>307</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="90" t="s">
         <v>308</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="90" t="s">
         <v>309</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-    </row>
-    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+    </row>
+    <row r="3" spans="1:8" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>310</v>
       </c>
@@ -11928,8 +11941,8 @@
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69C2D30-4EE1-9C41-9203-38F0784F325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F4438F-6F37-DB4F-8D23-6EAA88FE6AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="35860" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="321">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -1504,7 +1504,7 @@
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1742,6 +1742,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3399,7 +3402,9 @@
         <v>94</v>
       </c>
       <c r="K24" s="54"/>
-      <c r="L24" s="58"/>
+      <c r="L24" s="59" t="s">
+        <v>29</v>
+      </c>
       <c r="M24" s="54"/>
       <c r="N24" s="54"/>
       <c r="O24" s="54" t="s">
@@ -3463,9 +3468,6 @@
       </c>
       <c r="K25" s="59"/>
       <c r="L25" s="53"/>
-      <c r="M25" s="59" t="s">
-        <v>29</v>
-      </c>
       <c r="N25" s="59" t="s">
         <v>29</v>
       </c>
@@ -5137,24 +5139,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="59">
-        <v>8</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="77" t="s">
-        <v>97</v>
-      </c>
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="54">
@@ -5354,24 +5344,22 @@
     <hyperlink ref="D9" r:id="rId14" xr:uid="{00000000-0004-0000-0900-00000D000000}"/>
     <hyperlink ref="C10" r:id="rId15" xr:uid="{00000000-0004-0000-0900-00000E000000}"/>
     <hyperlink ref="D10" r:id="rId16" xr:uid="{00000000-0004-0000-0900-00000F000000}"/>
-    <hyperlink ref="C11" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000010000000}"/>
-    <hyperlink ref="D11" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000011000000}"/>
-    <hyperlink ref="C12" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
-    <hyperlink ref="D12" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
-    <hyperlink ref="C13" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
-    <hyperlink ref="D13" r:id="rId22" xr:uid="{00000000-0004-0000-0900-000015000000}"/>
-    <hyperlink ref="C14" r:id="rId23" xr:uid="{00000000-0004-0000-0900-000016000000}"/>
-    <hyperlink ref="D14" r:id="rId24" xr:uid="{00000000-0004-0000-0900-000017000000}"/>
-    <hyperlink ref="C15" r:id="rId25" xr:uid="{00000000-0004-0000-0900-000018000000}"/>
-    <hyperlink ref="D15" r:id="rId26" xr:uid="{00000000-0004-0000-0900-000019000000}"/>
-    <hyperlink ref="C16" r:id="rId27" xr:uid="{00000000-0004-0000-0900-00001A000000}"/>
-    <hyperlink ref="D16" r:id="rId28" xr:uid="{00000000-0004-0000-0900-00001B000000}"/>
-    <hyperlink ref="C17" r:id="rId29" xr:uid="{00000000-0004-0000-0900-00001C000000}"/>
-    <hyperlink ref="D17" r:id="rId30" xr:uid="{00000000-0004-0000-0900-00001D000000}"/>
-    <hyperlink ref="C18" r:id="rId31" xr:uid="{00000000-0004-0000-0900-00001E000000}"/>
-    <hyperlink ref="D18" r:id="rId32" xr:uid="{00000000-0004-0000-0900-00001F000000}"/>
-    <hyperlink ref="C19" r:id="rId33" xr:uid="{00000000-0004-0000-0900-000020000000}"/>
-    <hyperlink ref="D19" r:id="rId34" xr:uid="{00000000-0004-0000-0900-000021000000}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000015000000}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000016000000}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{00000000-0004-0000-0900-000017000000}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{00000000-0004-0000-0900-000018000000}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{00000000-0004-0000-0900-000019000000}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{00000000-0004-0000-0900-00001A000000}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{00000000-0004-0000-0900-00001B000000}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{00000000-0004-0000-0900-00001C000000}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{00000000-0004-0000-0900-00001D000000}"/>
+    <hyperlink ref="C18" r:id="rId29" xr:uid="{00000000-0004-0000-0900-00001E000000}"/>
+    <hyperlink ref="D18" r:id="rId30" xr:uid="{00000000-0004-0000-0900-00001F000000}"/>
+    <hyperlink ref="C19" r:id="rId31" xr:uid="{00000000-0004-0000-0900-000020000000}"/>
+    <hyperlink ref="D19" r:id="rId32" xr:uid="{00000000-0004-0000-0900-000021000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12935,19 +12923,17 @@
         <v>8</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="79" t="s">
-        <v>3</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="79"/>
       <c r="E10" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="80" t="s">
-        <v>101</v>
+        <v>33</v>
+      </c>
+      <c r="F10" s="94">
+        <v>0.23125000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13146,24 +13132,23 @@
     <hyperlink ref="D8" r:id="rId12" xr:uid="{00000000-0004-0000-0800-00000B000000}"/>
     <hyperlink ref="C9" r:id="rId13" xr:uid="{00000000-0004-0000-0800-00000C000000}"/>
     <hyperlink ref="D9" r:id="rId14" xr:uid="{00000000-0004-0000-0800-00000D000000}"/>
-    <hyperlink ref="C10" r:id="rId15" xr:uid="{00000000-0004-0000-0800-00000E000000}"/>
-    <hyperlink ref="D10" r:id="rId16" xr:uid="{00000000-0004-0000-0800-00000F000000}"/>
-    <hyperlink ref="C11" r:id="rId17" xr:uid="{00000000-0004-0000-0800-000010000000}"/>
-    <hyperlink ref="D11" r:id="rId18" xr:uid="{00000000-0004-0000-0800-000011000000}"/>
-    <hyperlink ref="C12" r:id="rId19" xr:uid="{00000000-0004-0000-0800-000012000000}"/>
-    <hyperlink ref="D12" r:id="rId20" xr:uid="{00000000-0004-0000-0800-000013000000}"/>
-    <hyperlink ref="C13" r:id="rId21" xr:uid="{00000000-0004-0000-0800-000014000000}"/>
-    <hyperlink ref="D13" r:id="rId22" xr:uid="{00000000-0004-0000-0800-000015000000}"/>
-    <hyperlink ref="C14" r:id="rId23" xr:uid="{00000000-0004-0000-0800-000016000000}"/>
-    <hyperlink ref="D14" r:id="rId24" xr:uid="{00000000-0004-0000-0800-000017000000}"/>
-    <hyperlink ref="C15" r:id="rId25" xr:uid="{00000000-0004-0000-0800-000018000000}"/>
-    <hyperlink ref="D15" r:id="rId26" xr:uid="{00000000-0004-0000-0800-000019000000}"/>
-    <hyperlink ref="C16" r:id="rId27" xr:uid="{00000000-0004-0000-0800-00001A000000}"/>
-    <hyperlink ref="D16" r:id="rId28" xr:uid="{00000000-0004-0000-0800-00001B000000}"/>
-    <hyperlink ref="C17" r:id="rId29" xr:uid="{00000000-0004-0000-0800-00001C000000}"/>
-    <hyperlink ref="D17" r:id="rId30" xr:uid="{00000000-0004-0000-0800-00001D000000}"/>
-    <hyperlink ref="C18" r:id="rId31" xr:uid="{00000000-0004-0000-0800-00001E000000}"/>
-    <hyperlink ref="D18" r:id="rId32" xr:uid="{00000000-0004-0000-0800-00001F000000}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{00000000-0004-0000-0800-000010000000}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{00000000-0004-0000-0800-000011000000}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{00000000-0004-0000-0800-000012000000}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{00000000-0004-0000-0800-000013000000}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{00000000-0004-0000-0800-000014000000}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{00000000-0004-0000-0800-000015000000}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{00000000-0004-0000-0800-000016000000}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{00000000-0004-0000-0800-000017000000}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{00000000-0004-0000-0800-000018000000}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{00000000-0004-0000-0800-000019000000}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{00000000-0004-0000-0800-00001A000000}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{00000000-0004-0000-0800-00001B000000}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{00000000-0004-0000-0800-00001C000000}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{00000000-0004-0000-0800-00001D000000}"/>
+    <hyperlink ref="C18" r:id="rId29" xr:uid="{00000000-0004-0000-0800-00001E000000}"/>
+    <hyperlink ref="D18" r:id="rId30" xr:uid="{00000000-0004-0000-0800-00001F000000}"/>
+    <hyperlink ref="C10" r:id="rId31" xr:uid="{ADD2DDD8-7967-3346-BBC9-47DD7C1C4AE2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F4438F-6F37-DB4F-8D23-6EAA88FE6AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517665C-4B61-E249-AEF0-AECDF0EDFC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="35860" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="35860" windowHeight="21000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -38,12 +38,25 @@
     <sheet name="2024-04-27 Lincolnwood" sheetId="23" r:id="rId23"/>
     <sheet name="2023-09-09 Block Party" sheetId="24" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="324">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -1022,6 +1035,15 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>BREAK</t>
+  </si>
+  <si>
+    <t>Rockin’ in the Free World</t>
+  </si>
+  <si>
+    <t>Miles/ Matt</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1526,7 @@
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1744,6 +1766,48 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12672,66 +12736,668 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="99" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="103" t="s">
         <v>259</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="104" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="103" t="s">
         <v>260</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="104" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
+    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="59">
+        <v>1</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="95" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73" t="s">
+      <c r="A4" s="54">
+        <v>2</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="96" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="59">
+        <v>3</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="95" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="54">
+        <v>4</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="59">
+        <v>5</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="97" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="54">
+        <v>6</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="59">
+        <v>7</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="95" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="54">
+        <v>8</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="98"/>
+    </row>
+    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="59">
+        <v>9</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="95" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="54">
+        <v>10</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="59">
+        <v>11</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="95" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="54">
+        <v>12</v>
+      </c>
+      <c r="B14" s="84" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="59">
+        <v>13</v>
+      </c>
+      <c r="B15" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="95" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="54">
+        <v>14</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="96" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="59">
+        <v>15</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="95" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="54">
+        <v>16</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="96" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="105" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+    </row>
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="106">
+        <v>17</v>
+      </c>
+      <c r="B20" s="91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="106" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="108">
+        <v>0.16319444444444445</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="106">
+        <v>18</v>
+      </c>
+      <c r="B21" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="106" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="107"/>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="106">
+        <v>19</v>
+      </c>
+      <c r="B22" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="109" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A23" s="106">
+        <v>20</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="106" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="92"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="110"/>
+    </row>
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A24" s="106">
+        <v>21</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="106" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="91"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="91"/>
+    </row>
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A25" s="106">
+        <v>22</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="F25" s="109" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="91"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="L25" s="109"/>
+    </row>
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A26" s="106">
+        <v>23</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="106" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="110" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="92"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="L26" s="110"/>
+    </row>
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A27" s="106">
+        <v>24</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="106" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="109" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="91"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="109"/>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A28" s="106">
+        <v>25</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="106" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="91"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="109"/>
+    </row>
+    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A29" s="106">
+        <v>26</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="C29" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="106" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="110" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="92"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="110"/>
+    </row>
+    <row r="30" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="E30" s="53"/>
+    </row>
+    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="73"/>
+      <c r="B31" s="73" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74" t="s">
-        <v>262</v>
-      </c>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{2F836F78-0606-CB45-9213-7E4FB33ED76C}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{2714936D-9DA9-224E-B69B-9855F8113DE6}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{C35B7771-B1A9-E849-A532-B4A5E7335BBF}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{ADDC67F9-A435-E94D-8141-2447977E476E}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{5A5AF45B-C486-EB4B-93D5-666C468BD5AC}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{EB1287AA-F158-3342-9673-D17B10B43AEF}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{CC678B3E-7538-814A-A886-330E6FF7D67A}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{9DDEEB26-4FA0-804D-804E-E7631FB5A7BC}"/>
+    <hyperlink ref="C7" r:id="rId9" xr:uid="{6C4E25CF-29F5-384D-B027-C098AD72CC2E}"/>
+    <hyperlink ref="D7" r:id="rId10" xr:uid="{3F30DDF6-D519-CF46-8E9D-BBF032DED358}"/>
+    <hyperlink ref="C8" r:id="rId11" xr:uid="{939A850D-88E1-9C46-93CD-4E3186741F72}"/>
+    <hyperlink ref="D8" r:id="rId12" xr:uid="{3D03B04E-8A8E-A045-86CD-7EFF2B726511}"/>
+    <hyperlink ref="C9" r:id="rId13" xr:uid="{4F6E08FF-DDC0-2543-B55E-01E070CBABC0}"/>
+    <hyperlink ref="D9" r:id="rId14" xr:uid="{F0075BE6-AE02-EF46-8A62-A8B4DD8ECF7F}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{AE828057-AAA0-9145-86D3-CC452DBCC417}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{4138AE1E-760E-E34C-AD02-817163E0F045}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{1370C4C6-5889-584F-A262-5C31F351296D}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{6A02F5A2-A9A0-5C40-9486-E13F65EC61E0}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{E5A4896C-A2FB-F94A-8612-FE8288DCF436}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{F4BCF21A-B489-6C4F-B5FB-5D9FED22D817}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{1C2C5E8F-5656-3B49-B01C-CAD73D43C84E}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{5224E286-7B2A-D442-BC73-5886A018D30A}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{03388A01-83BB-484D-870E-51B6D3C88D99}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{1C86A3A4-5E59-5A43-ACEB-2F7E2B3DC0D8}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{67BE0CAC-2671-F648-8682-A39370A6CCF4}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{C8767EA2-F060-434D-A5A9-C26AE9B20B95}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{1F4464F5-FC6E-EF44-8FC0-79ABC7686F88}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{147E8A90-5601-9348-B945-5781395ADACB}"/>
+    <hyperlink ref="C18" r:id="rId29" xr:uid="{42E717DB-9CAF-DB4A-B994-060904C88D2F}"/>
+    <hyperlink ref="D18" r:id="rId30" xr:uid="{C65D9E2B-BF96-2841-81F2-B6DC0FABDA85}"/>
+    <hyperlink ref="C20" r:id="rId31" xr:uid="{FAFE8E3C-365F-B54B-B270-0517767557EB}"/>
+    <hyperlink ref="D20" r:id="rId32" xr:uid="{AD664161-6EDE-CE40-B5AA-C6A1431F704C}"/>
+    <hyperlink ref="C21" r:id="rId33" xr:uid="{61D7EDDA-5651-824B-9142-667804813FA2}"/>
+    <hyperlink ref="D21" r:id="rId34" xr:uid="{82DE01C5-7B04-4F46-8318-14FABFF01220}"/>
+    <hyperlink ref="C22" r:id="rId35" xr:uid="{FB46E2EC-8221-B743-BD4C-893A12B307E0}"/>
+    <hyperlink ref="D22" r:id="rId36" xr:uid="{1E99BC16-0829-5A4E-BEA7-DB1F10449A0B}"/>
+    <hyperlink ref="C23" r:id="rId37" xr:uid="{24CEEFD3-3B63-2045-ADE4-7D9B1BF183B5}"/>
+    <hyperlink ref="D23" r:id="rId38" xr:uid="{D426010D-E18A-5645-BB76-B74D5AFD661A}"/>
+    <hyperlink ref="C24" r:id="rId39" xr:uid="{58658114-9B56-A442-8959-4170B2ACB69A}"/>
+    <hyperlink ref="D24" r:id="rId40" xr:uid="{01037297-FF79-934B-A0D5-92747E2A0195}"/>
+    <hyperlink ref="C25" r:id="rId41" xr:uid="{4A50256C-79AC-6342-9FED-A5328D3CE53A}"/>
+    <hyperlink ref="D25" r:id="rId42" xr:uid="{4C4A9314-4D0D-3E44-93CB-017CB1A36FEC}"/>
+    <hyperlink ref="C26" r:id="rId43" xr:uid="{B31FCB6C-1C41-7F45-81D4-DAC978EA8130}"/>
+    <hyperlink ref="D26" r:id="rId44" xr:uid="{D526EC23-C0E4-D94E-B9AD-84EDB2CFB018}"/>
+    <hyperlink ref="C27" r:id="rId45" xr:uid="{CCAF9E9A-A9A6-B648-BB8D-950BC56FA81D}"/>
+    <hyperlink ref="D27" r:id="rId46" xr:uid="{6E232019-EFBF-4D45-869E-58814AEC857A}"/>
+    <hyperlink ref="C28" r:id="rId47" xr:uid="{ABDAB66F-A0CE-A841-AFF6-E32478EF664F}"/>
+    <hyperlink ref="D28" r:id="rId48" xr:uid="{1914CCC1-5048-E040-B935-F69DCFF4ED1B}"/>
+    <hyperlink ref="C29" r:id="rId49" xr:uid="{EDA8309E-55AA-DC44-9535-554DF92D4A9F}"/>
+    <hyperlink ref="D29" r:id="rId50" xr:uid="{930AD90F-F409-FA42-ABA5-18E5E24C4DEA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B83FDB-9BF1-3941-AC14-B65E258D745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E11FA92-E63B-914E-A215-889FB7817DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="35860" windowHeight="21000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1050,9 +1050,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="[m]:ss"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1536,7 +1537,7 @@
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1806,19 +1807,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1827,17 +1819,11 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1845,15 +1831,35 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="17" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -12809,7 +12815,7 @@
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -12858,27 +12864,27 @@
       <c r="E3" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="107" t="s">
+      <c r="F3" s="118" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108">
-        <v>2</v>
-      </c>
-      <c r="B4" s="108" t="s">
+      <c r="A4" s="107">
+        <v>2</v>
+      </c>
+      <c r="B4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="108" t="s">
+      <c r="C4" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="110" t="s">
+      <c r="F4" s="119" t="s">
         <v>11</v>
       </c>
     </row>
@@ -12898,27 +12904,27 @@
       <c r="E5" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="107" t="s">
+      <c r="F5" s="118" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108">
+      <c r="A6" s="107">
         <v>4</v>
       </c>
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="108" t="s">
+      <c r="C6" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="110" t="s">
+      <c r="F6" s="119" t="s">
         <v>16</v>
       </c>
     </row>
@@ -12938,27 +12944,27 @@
       <c r="E7" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="107" t="s">
+      <c r="F7" s="118" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="108">
+      <c r="A8" s="107">
         <v>6</v>
       </c>
-      <c r="B8" s="108" t="s">
+      <c r="B8" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="108" t="s">
+      <c r="C8" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="110" t="s">
+      <c r="F8" s="119" t="s">
         <v>21</v>
       </c>
     </row>
@@ -12978,27 +12984,27 @@
       <c r="E9" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="118" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="108">
+      <c r="A10" s="107">
         <v>8</v>
       </c>
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="108" t="s">
+      <c r="C10" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="111" t="s">
+      <c r="F10" s="119" t="s">
         <v>26</v>
       </c>
     </row>
@@ -13018,27 +13024,27 @@
       <c r="E11" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="107" t="s">
+      <c r="F11" s="118" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="108">
+      <c r="A12" s="107">
         <v>10</v>
       </c>
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="108" t="s">
+      <c r="C12" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="110" t="s">
+      <c r="F12" s="119" t="s">
         <v>30</v>
       </c>
     </row>
@@ -13058,27 +13064,27 @@
       <c r="E13" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="107" t="s">
+      <c r="F13" s="118" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="108">
+      <c r="A14" s="107">
         <v>12</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="108" t="s">
+      <c r="C14" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="110" t="s">
+      <c r="F14" s="119" t="s">
         <v>16</v>
       </c>
     </row>
@@ -13098,27 +13104,27 @@
       <c r="E15" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="107" t="s">
+      <c r="F15" s="118" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="108">
+      <c r="A16" s="107">
         <v>14</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="108" t="s">
+      <c r="C16" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="110" t="s">
+      <c r="F16" s="119" t="s">
         <v>36</v>
       </c>
     </row>
@@ -13138,27 +13144,27 @@
       <c r="E17" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="107" t="s">
+      <c r="F17" s="118" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="108">
+      <c r="A18" s="107">
         <v>16</v>
       </c>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="108" t="s">
+      <c r="C18" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="110" t="s">
+      <c r="F18" s="119" t="s">
         <v>40</v>
       </c>
     </row>
@@ -13170,10 +13176,10 @@
       <c r="C19" s="104"/>
       <c r="D19" s="104"/>
       <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
+      <c r="F19" s="120"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="113">
+      <c r="A20" s="110">
         <v>17</v>
       </c>
       <c r="B20" s="54" t="s">
@@ -13185,36 +13191,36 @@
       <c r="D20" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="114" t="s">
+      <c r="F20" s="121" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="115">
+      <c r="A21" s="111">
         <v>18</v>
       </c>
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="115" t="s">
+      <c r="C21" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="117"/>
+      <c r="F21" s="122"/>
     </row>
     <row r="22" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="118">
+      <c r="A22" s="113">
         <v>19</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="114" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="106" t="s">
@@ -13223,30 +13229,30 @@
       <c r="D22" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="119" t="s">
+      <c r="E22" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="120" t="s">
+      <c r="F22" s="123" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="115">
+      <c r="A23" s="111">
         <v>20</v>
       </c>
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="115" t="s">
+      <c r="C23" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="122" t="s">
+      <c r="F23" s="124" t="s">
         <v>48</v>
       </c>
       <c r="G23" s="92"/>
@@ -13257,10 +13263,10 @@
       <c r="L23" s="96"/>
     </row>
     <row r="24" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="118">
+      <c r="A24" s="113">
         <v>21</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="116" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="106" t="s">
@@ -13269,32 +13275,32 @@
       <c r="D24" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="118" t="s">
+      <c r="E24" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="124"/>
+      <c r="F24" s="125"/>
       <c r="G24" s="91"/>
       <c r="H24" s="55"/>
       <c r="I24" s="55"/>
       <c r="J24" s="91"/>
     </row>
     <row r="25" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="115">
+      <c r="A25" s="111">
         <v>22</v>
       </c>
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="115" t="s">
+      <c r="C25" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="122" t="s">
+      <c r="F25" s="124" t="s">
         <v>51</v>
       </c>
       <c r="G25" s="91"/>
@@ -13303,10 +13309,10 @@
       <c r="L25" s="95"/>
     </row>
     <row r="26" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="118">
+      <c r="A26" s="113">
         <v>23</v>
       </c>
-      <c r="B26" s="123" t="s">
+      <c r="B26" s="116" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="106" t="s">
@@ -13315,34 +13321,34 @@
       <c r="D26" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="118" t="s">
+      <c r="E26" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="120" t="s">
+      <c r="F26" s="123" t="s">
         <v>53</v>
       </c>
       <c r="G26" s="92"/>
-      <c r="H26" s="64"/>
+      <c r="H26" s="127"/>
       <c r="I26" s="64"/>
       <c r="L26" s="96"/>
     </row>
     <row r="27" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="115">
+      <c r="A27" s="111">
         <v>24</v>
       </c>
-      <c r="B27" s="121" t="s">
+      <c r="B27" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="115" t="s">
+      <c r="C27" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="122" t="s">
+      <c r="F27" s="124" t="s">
         <v>55</v>
       </c>
       <c r="G27" s="91"/>
@@ -13353,10 +13359,10 @@
       <c r="L27" s="95"/>
     </row>
     <row r="28" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="118">
+      <c r="A28" s="113">
         <v>25</v>
       </c>
-      <c r="B28" s="123" t="s">
+      <c r="B28" s="116" t="s">
         <v>56</v>
       </c>
       <c r="C28" s="106" t="s">
@@ -13365,10 +13371,10 @@
       <c r="D28" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="E28" s="118" t="s">
+      <c r="E28" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="120" t="s">
+      <c r="F28" s="123" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="91"/>
@@ -13379,22 +13385,22 @@
       <c r="L28" s="95"/>
     </row>
     <row r="29" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="115">
+      <c r="A29" s="111">
         <v>26</v>
       </c>
-      <c r="B29" s="121" t="s">
+      <c r="B29" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="115" t="s">
+      <c r="C29" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="122" t="s">
+      <c r="F29" s="124" t="s">
         <v>59</v>
       </c>
       <c r="G29" s="92"/>
@@ -13408,6 +13414,7 @@
       <c r="A30" s="53"/>
       <c r="B30" s="53"/>
       <c r="E30" s="53"/>
+      <c r="F30" s="126"/>
     </row>
     <row r="31" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="73"/>
@@ -13417,9 +13424,9 @@
       <c r="C31" s="73"/>
       <c r="D31" s="73"/>
       <c r="E31" s="73"/>
-      <c r="F31" s="74" t="str">
-        <f>TEXT(SUM(F3:F30),"[m]:ss")</f>
-        <v>0:00</v>
+      <c r="F31" s="117">
+        <f>SUM(F3:F30)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE1660D-C211-404B-BD31-E26E70D40A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99876235-2DCE-0A49-B4F1-3C34EB239718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40040" yWindow="1840" windowWidth="34560" windowHeight="19220" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1822,41 +1822,14 @@
     </xf>
     <xf numFmtId="14" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1887,6 +1860,33 @@
     </xf>
     <xf numFmtId="46" fontId="26" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1922,10 +1922,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2359,7 +2355,7 @@
       <c r="E3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="94">
+      <c r="F3" s="89">
         <v>2.7662037037037039E-3</v>
       </c>
       <c r="G3" s="13" t="s">
@@ -2410,7 +2406,7 @@
       <c r="E4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="89">
         <v>3.9583333333333337E-3</v>
       </c>
       <c r="G4" s="14" t="s">
@@ -2459,7 +2455,7 @@
       <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
       <c r="G5" s="14" t="s">
@@ -2522,7 +2518,7 @@
       <c r="E6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="89">
         <v>2.7199074074074074E-3</v>
       </c>
       <c r="G6" s="14" t="s">
@@ -2575,7 +2571,7 @@
       <c r="E7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="89">
         <v>3.414351851851852E-3</v>
       </c>
       <c r="G7" s="14" t="s">
@@ -2630,7 +2626,7 @@
       <c r="E8" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="94">
+      <c r="F8" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
       <c r="G8" s="14" t="s">
@@ -2697,7 +2693,7 @@
       <c r="E9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="94">
+      <c r="F9" s="89">
         <v>2.1875000000000002E-3</v>
       </c>
       <c r="G9" s="14" t="s">
@@ -2776,7 +2772,7 @@
       <c r="E10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="94">
+      <c r="F10" s="89">
         <v>3.3449074074074076E-3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -2825,7 +2821,7 @@
       <c r="E11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="94">
+      <c r="F11" s="89">
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -2888,7 +2884,7 @@
       <c r="E12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="94">
+      <c r="F12" s="89">
         <v>2.7430555555555554E-3</v>
       </c>
       <c r="G12" s="14" t="s">
@@ -2945,7 +2941,7 @@
       <c r="E13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="94">
+      <c r="F13" s="89">
         <v>2.3032407407407407E-3</v>
       </c>
       <c r="G13" s="14" t="s">
@@ -2996,7 +2992,7 @@
       <c r="E14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="94">
+      <c r="F14" s="89">
         <v>1.7708333333333332E-3</v>
       </c>
       <c r="G14" s="14" t="s">
@@ -3043,7 +3039,7 @@
       <c r="E15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="94">
+      <c r="F15" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
       <c r="G15" s="14" t="s">
@@ -3114,7 +3110,7 @@
       <c r="E16" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="94">
+      <c r="F16" s="89">
         <v>2.488425925925926E-3</v>
       </c>
       <c r="G16" s="14" t="s">
@@ -3175,7 +3171,7 @@
       <c r="E17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="94">
+      <c r="F17" s="89">
         <v>1.9328703703703704E-3</v>
       </c>
       <c r="G17" s="14" t="s">
@@ -3224,7 +3220,7 @@
       <c r="E18" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="94">
+      <c r="F18" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="G18" s="14" t="s">
@@ -3285,7 +3281,7 @@
       <c r="E19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="94">
+      <c r="F19" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G19" s="14" t="s">
@@ -3340,7 +3336,7 @@
       <c r="E20" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="94">
+      <c r="F20" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
       <c r="G20" s="14" t="s">
@@ -3403,7 +3399,7 @@
       <c r="E21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="94">
+      <c r="F21" s="89">
         <v>2.5115740740740741E-3</v>
       </c>
       <c r="G21" s="14" t="s">
@@ -3450,7 +3446,7 @@
       <c r="E22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="94">
+      <c r="F22" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
       <c r="G22" s="14" t="s">
@@ -3527,7 +3523,7 @@
       <c r="E23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="94">
+      <c r="F23" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G23" s="14" t="s">
@@ -3588,7 +3584,7 @@
       <c r="E24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="94">
+      <c r="F24" s="89">
         <v>3.8541666666666668E-3</v>
       </c>
       <c r="G24" s="14" t="s">
@@ -3651,7 +3647,7 @@
       <c r="E25" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="94">
+      <c r="F25" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
       <c r="G25" s="14" t="s">
@@ -3718,7 +3714,7 @@
       <c r="E26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="94">
+      <c r="F26" s="89">
         <v>2.650462962962963E-3</v>
       </c>
       <c r="G26" s="14" t="s">
@@ -3767,7 +3763,7 @@
       <c r="E27" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="94">
+      <c r="F27" s="89">
         <v>3.0439814814814813E-3</v>
       </c>
       <c r="G27" s="14" t="s">
@@ -3818,7 +3814,7 @@
       <c r="E28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="94">
+      <c r="F28" s="89">
         <v>2.8587962962962963E-3</v>
       </c>
       <c r="G28" s="14" t="s">
@@ -3873,7 +3869,7 @@
       <c r="E29" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="94">
+      <c r="F29" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
       <c r="G29" s="14" t="s">
@@ -3942,7 +3938,7 @@
       <c r="E30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="94">
+      <c r="F30" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
       <c r="G30" s="14" t="s">
@@ -4017,7 +4013,7 @@
       <c r="E31" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="94">
+      <c r="F31" s="89">
         <v>1.9675925925925924E-3</v>
       </c>
       <c r="G31" s="14" t="s">
@@ -4068,7 +4064,7 @@
       <c r="E32" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="94">
+      <c r="F32" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -4127,7 +4123,7 @@
       <c r="E33" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="94">
+      <c r="F33" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
       <c r="G33" s="14" t="s">
@@ -4196,7 +4192,7 @@
       <c r="E34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="94">
+      <c r="F34" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
       <c r="G34" s="14" t="s">
@@ -4257,7 +4253,7 @@
       <c r="E35" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="94">
+      <c r="F35" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
       <c r="G35" s="14" t="s">
@@ -4320,7 +4316,7 @@
       <c r="E36" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="94">
+      <c r="F36" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="G36" s="14" t="s">
@@ -4373,7 +4369,7 @@
       <c r="E37" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="94">
+      <c r="F37" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
       <c r="G37" s="14" t="s">
@@ -4436,7 +4432,7 @@
       <c r="E38" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="94">
+      <c r="F38" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G38" s="14" t="s">
@@ -4491,7 +4487,7 @@
       <c r="E39" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="94">
+      <c r="F39" s="89">
         <v>3.472222222222222E-3</v>
       </c>
       <c r="G39" s="14" t="s">
@@ -4540,7 +4536,7 @@
       <c r="E40" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="94">
+      <c r="F40" s="89">
         <v>2.0023148148148148E-3</v>
       </c>
       <c r="G40" s="14" t="s">
@@ -4587,7 +4583,7 @@
       <c r="E41" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="94">
+      <c r="F41" s="89">
         <v>3.460648148148148E-3</v>
       </c>
       <c r="G41" s="14" t="s">
@@ -4640,7 +4636,7 @@
       <c r="E42" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="94">
+      <c r="F42" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
       <c r="G42" s="14" t="s">
@@ -4697,7 +4693,7 @@
       <c r="E43" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="94">
+      <c r="F43" s="89">
         <v>3.472222222222222E-3</v>
       </c>
       <c r="G43" s="14" t="s">
@@ -4746,7 +4742,7 @@
       <c r="E44" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="94">
+      <c r="F44" s="89">
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="G44" s="14" t="s">
@@ -4801,7 +4797,7 @@
       <c r="E45" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="94">
+      <c r="F45" s="89">
         <v>3.1250000000000002E-3</v>
       </c>
       <c r="G45" s="14" t="s">
@@ -4848,7 +4844,7 @@
       <c r="E46" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="94">
+      <c r="F46" s="89">
         <v>3.3217592592592591E-3</v>
       </c>
       <c r="G46" s="14" t="s">
@@ -4923,7 +4919,7 @@
       <c r="E47" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="94"/>
+      <c r="F47" s="89"/>
       <c r="G47" s="14" t="s">
         <v>128</v>
       </c>
@@ -4968,7 +4964,7 @@
       <c r="E48" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="94">
+      <c r="F48" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
       <c r="G48" s="14" t="s">
@@ -5218,7 +5214,7 @@
       <c r="E3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -5239,7 +5235,7 @@
       <c r="E4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5259,7 +5255,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -5279,7 +5275,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5299,7 +5295,7 @@
       <c r="E7" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5319,7 +5315,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -5339,7 +5335,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -5359,7 +5355,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -5369,7 +5365,7 @@
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>
       <c r="E11" s="45"/>
-      <c r="F11" s="95"/>
+      <c r="F11" s="90"/>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="60">
@@ -5387,7 +5383,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -5407,7 +5403,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -5427,7 +5423,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -5447,7 +5443,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5467,7 +5463,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5487,7 +5483,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -5507,7 +5503,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -5527,7 +5523,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -5537,7 +5533,7 @@
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="44"/>
-      <c r="F20" s="97"/>
+      <c r="F20" s="91"/>
     </row>
     <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54"/>
@@ -5650,7 +5646,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5670,7 +5666,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -5690,7 +5686,7 @@
       <c r="E5" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5710,7 +5706,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5730,7 +5726,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -5750,7 +5746,7 @@
       <c r="E8" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -5770,7 +5766,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -5790,7 +5786,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5810,7 +5806,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -5830,7 +5826,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -5840,7 +5836,7 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="97"/>
+      <c r="F13" s="91"/>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54"/>
@@ -5941,7 +5937,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5961,7 +5957,7 @@
       <c r="E4" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -5981,7 +5977,7 @@
       <c r="E5" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -6001,7 +5997,7 @@
       <c r="E6" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -6021,7 +6017,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>3.0439814814814817E-3</v>
       </c>
     </row>
@@ -6041,7 +6037,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -6061,7 +6057,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -6081,7 +6077,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -6101,7 +6097,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>1.9328703703703704E-3</v>
       </c>
     </row>
@@ -6121,7 +6117,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -6141,7 +6137,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -6161,7 +6157,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -6181,7 +6177,7 @@
       <c r="E15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -6201,7 +6197,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -6221,7 +6217,7 @@
       <c r="E17" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -6241,7 +6237,7 @@
       <c r="E18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -6261,7 +6257,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -6281,7 +6277,7 @@
       <c r="E20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="90">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -6301,7 +6297,7 @@
       <c r="E21" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -6321,7 +6317,7 @@
       <c r="E22" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -6339,7 +6335,7 @@
       <c r="E23" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -6359,7 +6355,7 @@
       <c r="E24" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -6379,7 +6375,7 @@
       <c r="E25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -6399,7 +6395,7 @@
       <c r="E26" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -6419,7 +6415,7 @@
       <c r="E27" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -6439,7 +6435,7 @@
       <c r="E28" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="90">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -6459,7 +6455,7 @@
       <c r="E29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="90">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -6477,7 +6473,7 @@
       <c r="E30" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="95">
+      <c r="F30" s="90">
         <f>VLOOKUP(B30,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -6498,7 +6494,7 @@
       <c r="E31" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -6518,7 +6514,7 @@
       <c r="E32" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="95">
+      <c r="F32" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -6538,7 +6534,7 @@
       <c r="E33" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="95">
+      <c r="F33" s="90">
         <f>VLOOKUP(B33,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -6549,7 +6545,7 @@
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="97"/>
+      <c r="F34" s="91"/>
     </row>
     <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="54"/>
@@ -6690,7 +6686,7 @@
       <c r="E3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -6710,7 +6706,7 @@
       <c r="E4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -6730,7 +6726,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -6750,7 +6746,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -6770,7 +6766,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0023148148148148E-3</v>
       </c>
@@ -6791,7 +6787,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -6811,7 +6807,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -6831,7 +6827,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -6851,7 +6847,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -6871,7 +6867,7 @@
       <c r="E12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -6892,7 +6888,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -6912,7 +6908,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -6932,7 +6928,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -6942,7 +6938,7 @@
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="97"/>
+      <c r="F16" s="91"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54"/>
@@ -7049,7 +7045,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -7069,7 +7065,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7089,7 +7085,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -7109,7 +7105,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -7125,7 +7121,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7662037037037039E-3</v>
       </c>
@@ -7146,7 +7142,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -7166,7 +7162,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -7186,7 +7182,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -7206,7 +7202,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -7224,7 +7220,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -7245,7 +7241,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -7265,7 +7261,7 @@
       <c r="E14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -7286,7 +7282,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -7302,7 +7298,7 @@
       <c r="E16" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="95"/>
+      <c r="F16" s="90"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
@@ -7310,7 +7306,7 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="44"/>
-      <c r="F17" s="97"/>
+      <c r="F17" s="91"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54"/>
@@ -7414,7 +7410,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -7434,7 +7430,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7454,7 +7450,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -7474,7 +7470,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -7495,7 +7491,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -7515,7 +7511,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -7535,7 +7531,7 @@
       <c r="E9" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -7551,7 +7547,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7662037037037039E-3</v>
       </c>
@@ -7572,7 +7568,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -7592,7 +7588,7 @@
       <c r="E12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.3032407407407407E-3</v>
       </c>
@@ -7613,7 +7609,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -7633,7 +7629,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -7653,7 +7649,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -7673,7 +7669,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -7693,7 +7689,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -7713,7 +7709,7 @@
       <c r="E18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -7731,7 +7727,7 @@
       <c r="E19" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -7752,7 +7748,7 @@
       <c r="E20" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -7772,7 +7768,7 @@
       <c r="E21" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -7792,7 +7788,7 @@
       <c r="E22" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7812,7 +7808,7 @@
       <c r="E23" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -7830,7 +7826,7 @@
       <c r="E24" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -7850,7 +7846,7 @@
       <c r="E25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="90">
         <f>VLOOKUP(B25,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -7871,7 +7867,7 @@
       <c r="E26" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="90">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -7891,7 +7887,7 @@
       <c r="E27" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="90">
         <f>VLOOKUP(B27,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -7912,7 +7908,7 @@
       <c r="E28" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -7932,7 +7928,7 @@
       <c r="E29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -7952,7 +7948,7 @@
       <c r="E30" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="95">
+      <c r="F30" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -7962,7 +7958,7 @@
       <c r="C31" s="51"/>
       <c r="D31" s="51"/>
       <c r="E31" s="44"/>
-      <c r="F31" s="97"/>
+      <c r="F31" s="91"/>
     </row>
     <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="54"/>
@@ -8095,7 +8091,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -8115,7 +8111,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8135,7 +8131,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -8155,7 +8151,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -8176,7 +8172,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -8196,7 +8192,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -8216,7 +8212,7 @@
       <c r="E9" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.3032407407407407E-3</v>
       </c>
@@ -8237,7 +8233,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -8257,7 +8253,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -8277,7 +8273,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -8297,7 +8293,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -8317,7 +8313,7 @@
       <c r="E14" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -8335,7 +8331,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -8356,7 +8352,7 @@
       <c r="E16" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -8376,7 +8372,7 @@
       <c r="E17" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -8396,7 +8392,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -8414,7 +8410,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -8434,7 +8430,7 @@
       <c r="E20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -8454,7 +8450,7 @@
       <c r="E21" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -8474,7 +8470,7 @@
       <c r="E22" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -8484,7 +8480,7 @@
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="97"/>
+      <c r="F23" s="91"/>
     </row>
     <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="54"/>
@@ -8603,7 +8599,7 @@
       <c r="E3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -8624,7 +8620,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -8644,7 +8640,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8664,7 +8660,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -8684,7 +8680,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -8704,7 +8700,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -8724,7 +8720,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -8742,7 +8738,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -8763,7 +8759,7 @@
       <c r="E11" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -8783,7 +8779,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -8803,7 +8799,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -8823,7 +8819,7 @@
       <c r="E14" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8843,7 +8839,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -8863,7 +8859,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -8873,7 +8869,7 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="44"/>
-      <c r="F17" s="97"/>
+      <c r="F17" s="91"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54"/>
@@ -8981,7 +8977,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -9001,7 +8997,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9021,7 +9017,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -9041,7 +9037,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -9061,7 +9057,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -9082,7 +9078,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -9100,7 +9096,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -9120,7 +9116,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -9138,7 +9134,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -9159,7 +9155,7 @@
       <c r="E12" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -9179,7 +9175,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -9189,7 +9185,7 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="97"/>
+      <c r="F14" s="91"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
@@ -9290,7 +9286,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -9310,7 +9306,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -9330,7 +9326,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -9350,7 +9346,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -9370,7 +9366,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -9390,7 +9386,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -9410,7 +9406,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9430,7 +9426,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -9451,7 +9447,7 @@
       <c r="E11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9675925925925924E-3</v>
       </c>
@@ -9472,7 +9468,7 @@
       <c r="E12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -9491,7 +9487,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -9511,7 +9507,7 @@
       <c r="E14" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -9531,7 +9527,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -9551,7 +9547,7 @@
       <c r="E16" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -9570,7 +9566,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -9591,7 +9587,7 @@
       <c r="E18" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5115740740740741E-3</v>
       </c>
@@ -9612,7 +9608,7 @@
       <c r="E19" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3449074074074076E-3</v>
       </c>
@@ -9633,7 +9629,7 @@
       <c r="E20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -9653,7 +9649,7 @@
       <c r="E21" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="90">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -9673,7 +9669,7 @@
       <c r="E22" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="90">
         <f>VLOOKUP(B22,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -9694,7 +9690,7 @@
       <c r="E23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -9714,7 +9710,7 @@
       <c r="E24" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -9734,7 +9730,7 @@
       <c r="E25" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9754,7 +9750,7 @@
       <c r="E26" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -9774,7 +9770,7 @@
       <c r="E27" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -9794,7 +9790,7 @@
       <c r="E28" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="90">
         <f>VLOOKUP(B28,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -9805,7 +9801,7 @@
       <c r="C29" s="51"/>
       <c r="D29" s="51"/>
       <c r="E29" s="44"/>
-      <c r="F29" s="97"/>
+      <c r="F29" s="91"/>
     </row>
     <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="54"/>
@@ -10566,7 +10562,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -10586,7 +10582,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -10606,7 +10602,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -10626,7 +10622,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -10646,7 +10642,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -10666,7 +10662,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -10686,7 +10682,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -10706,7 +10702,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -10727,7 +10723,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -10746,7 +10742,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -10766,7 +10762,7 @@
       <c r="E13" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -10786,7 +10782,7 @@
       <c r="E14" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -10805,7 +10801,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -10826,7 +10822,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -10846,7 +10842,7 @@
       <c r="E17" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -10867,7 +10863,7 @@
       <c r="E18" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -10887,7 +10883,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -10907,7 +10903,7 @@
       <c r="E20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -10927,7 +10923,7 @@
       <c r="E21" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -10947,7 +10943,7 @@
       <c r="E22" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -10967,7 +10963,7 @@
       <c r="E23" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -10977,7 +10973,7 @@
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="44"/>
-      <c r="F24" s="97"/>
+      <c r="F24" s="91"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54"/>
@@ -11098,7 +11094,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11118,7 +11114,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11138,7 +11134,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -11158,7 +11154,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -11178,7 +11174,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -11198,7 +11194,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -11218,7 +11214,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -11238,7 +11234,7 @@
       <c r="E10" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -11258,7 +11254,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11279,7 +11275,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11299,7 +11295,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -11309,7 +11305,7 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="97"/>
+      <c r="F14" s="91"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
@@ -11412,7 +11408,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11432,7 +11428,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -11452,7 +11448,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -11472,7 +11468,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -11492,7 +11488,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -11512,7 +11508,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -11532,7 +11528,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11552,7 +11548,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -11572,7 +11568,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11591,7 +11587,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -11611,7 +11607,7 @@
       <c r="E13" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -11631,7 +11627,7 @@
       <c r="E14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -11651,7 +11647,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11671,7 +11667,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11691,7 +11687,7 @@
       <c r="E17" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="90">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -11711,7 +11707,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -11721,7 +11717,7 @@
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="44"/>
-      <c r="F19" s="97"/>
+      <c r="F19" s="91"/>
     </row>
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54"/>
@@ -11833,7 +11829,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11853,7 +11849,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -11873,7 +11869,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11893,7 +11889,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11913,7 +11909,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11934,7 +11930,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -11955,7 +11951,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -11975,7 +11971,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -11995,7 +11991,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -12015,7 +12011,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -12035,7 +12031,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="90">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -12045,7 +12041,7 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="97"/>
+      <c r="F14" s="91"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
@@ -12148,7 +12144,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="90">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -12168,7 +12164,7 @@
       <c r="E4" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="90">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -12188,7 +12184,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="90">
         <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9675925925925924E-3</v>
       </c>
@@ -12209,7 +12205,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="90">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -12230,7 +12226,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="90">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -12250,7 +12246,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="90">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -12268,7 +12264,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="90">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.7708333333333332E-3</v>
       </c>
@@ -12289,7 +12285,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="90">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -12309,7 +12305,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="90">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -12329,7 +12325,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="90">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -12339,7 +12335,7 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="97"/>
+      <c r="F13" s="91"/>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54"/>
@@ -13118,14 +13114,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="105" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="91"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="107"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
@@ -13468,14 +13464,14 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="108" t="s">
         <v>257</v>
       </c>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="96"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="110"/>
     </row>
     <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
@@ -13783,17 +13779,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="102" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="104"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="92" t="s">
         <v>251</v>
       </c>
       <c r="B2" s="42" t="s">
@@ -13808,12 +13804,12 @@
       <c r="E2" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="F2" s="102" t="s">
+      <c r="F2" s="93" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="103">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
       <c r="B3" s="45" t="s">
@@ -13828,12 +13824,12 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="104">
+      <c r="F3" s="95">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="103">
+      <c r="A4" s="94">
         <v>2</v>
       </c>
       <c r="B4" s="45" t="s">
@@ -13848,12 +13844,12 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="104">
+      <c r="F4" s="95">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="103">
+      <c r="A5" s="94">
         <v>3</v>
       </c>
       <c r="B5" s="45" t="s">
@@ -13868,12 +13864,12 @@
       <c r="E5" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="104">
+      <c r="F5" s="95">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="103">
+      <c r="A6" s="94">
         <v>4</v>
       </c>
       <c r="B6" s="45" t="s">
@@ -13888,12 +13884,12 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="104">
+      <c r="F6" s="95">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="103">
+      <c r="A7" s="94">
         <v>5</v>
       </c>
       <c r="B7" s="45" t="s">
@@ -13908,12 +13904,12 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="104">
+      <c r="F7" s="95">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="103">
+      <c r="A8" s="94">
         <v>6</v>
       </c>
       <c r="B8" s="45" t="s">
@@ -13928,12 +13924,12 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="104">
+      <c r="F8" s="95">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="103">
+      <c r="A9" s="94">
         <v>7</v>
       </c>
       <c r="B9" s="45" t="s">
@@ -13948,12 +13944,12 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="104">
+      <c r="F9" s="95">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="103">
+      <c r="A10" s="94">
         <v>8</v>
       </c>
       <c r="B10" s="45" t="s">
@@ -13966,13 +13962,13 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="104">
+      <c r="F10" s="95">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.8541666666666668E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="103">
+      <c r="A11" s="94">
         <v>9</v>
       </c>
       <c r="B11" s="45" t="s">
@@ -13987,12 +13983,12 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="104">
+      <c r="F11" s="95">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="103">
+      <c r="A12" s="94">
         <v>10</v>
       </c>
       <c r="B12" s="45" t="s">
@@ -14007,12 +14003,12 @@
       <c r="E12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="104">
+      <c r="F12" s="95">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="103">
+      <c r="A13" s="94">
         <v>11</v>
       </c>
       <c r="B13" s="45" t="s">
@@ -14027,12 +14023,12 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="104">
+      <c r="F13" s="95">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="103">
+      <c r="A14" s="94">
         <v>12</v>
       </c>
       <c r="B14" s="45" t="s">
@@ -14047,12 +14043,12 @@
       <c r="E14" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="104">
+      <c r="F14" s="95">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="103">
+      <c r="A15" s="94">
         <v>13</v>
       </c>
       <c r="B15" s="45" t="s">
@@ -14067,12 +14063,12 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="104">
+      <c r="F15" s="95">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="103">
+      <c r="A16" s="94">
         <v>14</v>
       </c>
       <c r="B16" s="45" t="s">
@@ -14087,12 +14083,12 @@
       <c r="E16" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="104">
+      <c r="F16" s="95">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="103">
+      <c r="A17" s="94">
         <v>15</v>
       </c>
       <c r="B17" s="45" t="s">
@@ -14107,12 +14103,12 @@
       <c r="E17" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="104">
+      <c r="F17" s="95">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="103">
+      <c r="A18" s="94">
         <v>16</v>
       </c>
       <c r="B18" s="45" t="s">
@@ -14127,27 +14123,27 @@
       <c r="E18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="104">
+      <c r="F18" s="95">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="105"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="44"/>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="44"/>
-      <c r="F19" s="106"/>
+      <c r="F19" s="97"/>
     </row>
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="107"/>
-      <c r="B20" s="108" t="s">
+      <c r="A20" s="98"/>
+      <c r="B20" s="99" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="110">
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="101">
         <f>SUM(F3:F19)</f>
         <v>4.5983796296296293E-2</v>
       </c>

--- a/docs/music/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/music/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/docs/music/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99876235-2DCE-0A49-B4F1-3C34EB239718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51BF7C7C-E55D-934A-8122-5E6358AB329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40040" yWindow="1840" windowWidth="34560" windowHeight="19220" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="2620" windowWidth="30360" windowHeight="18200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="275">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -669,9 +669,6 @@
     <t>Jenny.Sprenzel@rushortho.com</t>
   </si>
   <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
     <t>Ridgeville Parks</t>
   </si>
   <si>
@@ -679,9 +676,6 @@
   </si>
   <si>
     <t>programs@ridgeville.org</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
   </si>
   <si>
     <t>KINGS OF EWING — POTENTIAL SONGS</t>
@@ -1606,7 +1600,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1779,9 +1773,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1888,6 +1879,13 @@
     <xf numFmtId="165" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="18" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1922,6 +1920,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2355,7 +2357,7 @@
       <c r="E3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="89">
+      <c r="F3" s="88">
         <v>2.7662037037037039E-3</v>
       </c>
       <c r="G3" s="13" t="s">
@@ -2406,7 +2408,7 @@
       <c r="E4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="89">
+      <c r="F4" s="88">
         <v>3.9583333333333337E-3</v>
       </c>
       <c r="G4" s="14" t="s">
@@ -2443,19 +2445,21 @@
     </row>
     <row r="5" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="70"/>
+      <c r="C5" s="112" t="s">
+        <v>3</v>
+      </c>
       <c r="D5" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="88">
         <v>2.5810185185185185E-3</v>
       </c>
       <c r="G5" s="14" t="s">
@@ -2518,7 +2522,7 @@
       <c r="E6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="88">
         <v>2.7199074074074074E-3</v>
       </c>
       <c r="G6" s="14" t="s">
@@ -2571,7 +2575,7 @@
       <c r="E7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="88">
         <v>3.414351851851852E-3</v>
       </c>
       <c r="G7" s="14" t="s">
@@ -2626,7 +2630,7 @@
       <c r="E8" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="88">
         <v>1.7476851851851852E-3</v>
       </c>
       <c r="G8" s="14" t="s">
@@ -2693,7 +2697,7 @@
       <c r="E9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="88">
         <v>2.1875000000000002E-3</v>
       </c>
       <c r="G9" s="14" t="s">
@@ -2772,7 +2776,7 @@
       <c r="E10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="88">
         <v>3.3449074074074076E-3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -2821,7 +2825,7 @@
       <c r="E11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="88">
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -2884,7 +2888,7 @@
       <c r="E12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="88">
         <v>2.7430555555555554E-3</v>
       </c>
       <c r="G12" s="14" t="s">
@@ -2941,7 +2945,7 @@
       <c r="E13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="89">
+      <c r="F13" s="88">
         <v>2.3032407407407407E-3</v>
       </c>
       <c r="G13" s="14" t="s">
@@ -2992,7 +2996,7 @@
       <c r="E14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="88">
         <v>1.7708333333333332E-3</v>
       </c>
       <c r="G14" s="14" t="s">
@@ -3039,7 +3043,7 @@
       <c r="E15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="88">
         <v>2.7893518518518519E-3</v>
       </c>
       <c r="G15" s="14" t="s">
@@ -3110,7 +3114,7 @@
       <c r="E16" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="88">
         <v>2.488425925925926E-3</v>
       </c>
       <c r="G16" s="14" t="s">
@@ -3171,7 +3175,7 @@
       <c r="E17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="88">
         <v>1.9328703703703704E-3</v>
       </c>
       <c r="G17" s="14" t="s">
@@ -3220,7 +3224,7 @@
       <c r="E18" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="89">
+      <c r="F18" s="88">
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="G18" s="14" t="s">
@@ -3281,7 +3285,7 @@
       <c r="E19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="89">
+      <c r="F19" s="88">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G19" s="14" t="s">
@@ -3336,7 +3340,7 @@
       <c r="E20" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="88">
         <v>4.6874999999999998E-3</v>
       </c>
       <c r="G20" s="14" t="s">
@@ -3399,7 +3403,7 @@
       <c r="E21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="89">
+      <c r="F21" s="88">
         <v>2.5115740740740741E-3</v>
       </c>
       <c r="G21" s="14" t="s">
@@ -3446,7 +3450,7 @@
       <c r="E22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="89">
+      <c r="F22" s="88">
         <v>2.5810185185185185E-3</v>
       </c>
       <c r="G22" s="14" t="s">
@@ -3523,7 +3527,7 @@
       <c r="E23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="89">
+      <c r="F23" s="88">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G23" s="14" t="s">
@@ -3577,14 +3581,14 @@
       <c r="B24" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="70"/>
       <c r="D24" s="14" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="89">
+      <c r="F24" s="88">
         <v>3.8541666666666668E-3</v>
       </c>
       <c r="G24" s="14" t="s">
@@ -3647,7 +3651,7 @@
       <c r="E25" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="89">
+      <c r="F25" s="88">
         <v>1.9791666666666668E-3</v>
       </c>
       <c r="G25" s="14" t="s">
@@ -3714,7 +3718,7 @@
       <c r="E26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="89">
+      <c r="F26" s="88">
         <v>2.650462962962963E-3</v>
       </c>
       <c r="G26" s="14" t="s">
@@ -3727,9 +3731,7 @@
       <c r="J26" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="K26" s="14"/>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
@@ -3763,7 +3765,7 @@
       <c r="E27" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="89">
+      <c r="F27" s="88">
         <v>3.0439814814814813E-3</v>
       </c>
       <c r="G27" s="14" t="s">
@@ -3814,7 +3816,7 @@
       <c r="E28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="89">
+      <c r="F28" s="88">
         <v>2.8587962962962963E-3</v>
       </c>
       <c r="G28" s="14" t="s">
@@ -3869,7 +3871,7 @@
       <c r="E29" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="89">
+      <c r="F29" s="88">
         <v>2.0486111111111113E-3</v>
       </c>
       <c r="G29" s="14" t="s">
@@ -3938,7 +3940,7 @@
       <c r="E30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="89">
+      <c r="F30" s="88">
         <v>3.5995370370370369E-3</v>
       </c>
       <c r="G30" s="14" t="s">
@@ -4013,7 +4015,7 @@
       <c r="E31" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="89">
+      <c r="F31" s="88">
         <v>1.9675925925925924E-3</v>
       </c>
       <c r="G31" s="14" t="s">
@@ -4064,7 +4066,7 @@
       <c r="E32" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="89">
+      <c r="F32" s="88">
         <v>3.2291666666666666E-3</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -4123,7 +4125,7 @@
       <c r="E33" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="89">
+      <c r="F33" s="88">
         <v>2.9513888888888888E-3</v>
       </c>
       <c r="G33" s="14" t="s">
@@ -4192,7 +4194,7 @@
       <c r="E34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="89">
+      <c r="F34" s="88">
         <v>4.1319444444444442E-3</v>
       </c>
       <c r="G34" s="14" t="s">
@@ -4253,7 +4255,7 @@
       <c r="E35" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="89">
+      <c r="F35" s="88">
         <v>5.9606481481481481E-3</v>
       </c>
       <c r="G35" s="14" t="s">
@@ -4316,7 +4318,7 @@
       <c r="E36" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="89">
+      <c r="F36" s="88">
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="G36" s="14" t="s">
@@ -4369,7 +4371,7 @@
       <c r="E37" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="89">
+      <c r="F37" s="88">
         <v>3.3680555555555556E-3</v>
       </c>
       <c r="G37" s="14" t="s">
@@ -4432,7 +4434,7 @@
       <c r="E38" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="89">
+      <c r="F38" s="88">
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="G38" s="14" t="s">
@@ -4487,7 +4489,7 @@
       <c r="E39" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="89">
+      <c r="F39" s="88">
         <v>3.472222222222222E-3</v>
       </c>
       <c r="G39" s="14" t="s">
@@ -4536,7 +4538,7 @@
       <c r="E40" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="89">
+      <c r="F40" s="88">
         <v>2.0023148148148148E-3</v>
       </c>
       <c r="G40" s="14" t="s">
@@ -4583,7 +4585,7 @@
       <c r="E41" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="89">
+      <c r="F41" s="88">
         <v>3.460648148148148E-3</v>
       </c>
       <c r="G41" s="14" t="s">
@@ -4636,7 +4638,7 @@
       <c r="E42" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="89">
+      <c r="F42" s="88">
         <v>2.2569444444444442E-3</v>
       </c>
       <c r="G42" s="14" t="s">
@@ -4693,7 +4695,7 @@
       <c r="E43" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="89">
+      <c r="F43" s="88">
         <v>3.472222222222222E-3</v>
       </c>
       <c r="G43" s="14" t="s">
@@ -4742,7 +4744,7 @@
       <c r="E44" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="89">
+      <c r="F44" s="88">
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="G44" s="14" t="s">
@@ -4797,7 +4799,7 @@
       <c r="E45" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="89">
+      <c r="F45" s="88">
         <v>3.1250000000000002E-3</v>
       </c>
       <c r="G45" s="14" t="s">
@@ -4844,7 +4846,7 @@
       <c r="E46" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="89">
+      <c r="F46" s="88">
         <v>3.3217592592592591E-3</v>
       </c>
       <c r="G46" s="14" t="s">
@@ -4911,15 +4913,15 @@
       <c r="A47" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
       <c r="D47" s="14" t="s">
         <v>127</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="89"/>
+      <c r="F47" s="88"/>
       <c r="G47" s="14" t="s">
         <v>128</v>
       </c>
@@ -4964,7 +4966,7 @@
       <c r="E48" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="89">
+      <c r="F48" s="88">
         <v>2.0949074074074073E-3</v>
       </c>
       <c r="G48" s="14" t="s">
@@ -5019,8 +5021,8 @@
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
       <c r="F49" s="12"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
@@ -5150,6 +5152,7 @@
     <hyperlink ref="B48" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
     <hyperlink ref="C48" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
     <hyperlink ref="B5" r:id="rId88" xr:uid="{EA461231-8E8E-5746-9DF4-72454CC19E36}"/>
+    <hyperlink ref="C5" r:id="rId89" xr:uid="{C5ECF11B-005F-3145-827A-22E761430CCB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5170,7 +5173,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -5180,7 +5183,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -5192,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -5200,7 +5203,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B3" s="45" t="s">
         <v>106</v>
@@ -5214,7 +5217,7 @@
       <c r="E3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -5235,7 +5238,7 @@
       <c r="E4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5255,7 +5258,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -5275,7 +5278,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5295,7 +5298,7 @@
       <c r="E7" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5315,7 +5318,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -5335,7 +5338,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -5355,7 +5358,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -5365,7 +5368,7 @@
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>
       <c r="E11" s="45"/>
-      <c r="F11" s="90"/>
+      <c r="F11" s="89"/>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="60">
@@ -5383,7 +5386,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -5403,7 +5406,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -5423,7 +5426,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -5432,7 +5435,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>2</v>
@@ -5443,7 +5446,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5463,7 +5466,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5483,7 +5486,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -5503,7 +5506,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -5523,7 +5526,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -5533,12 +5536,12 @@
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="44"/>
-      <c r="F20" s="91"/>
+      <c r="F20" s="90"/>
     </row>
     <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54"/>
       <c r="B21" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
@@ -5602,7 +5605,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -5612,7 +5615,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -5624,7 +5627,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -5646,7 +5649,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5666,7 +5669,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -5686,7 +5689,7 @@
       <c r="E5" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5706,7 +5709,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -5726,7 +5729,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -5746,7 +5749,7 @@
       <c r="E8" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -5766,7 +5769,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -5786,7 +5789,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -5806,7 +5809,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -5826,7 +5829,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -5836,12 +5839,12 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="91"/>
+      <c r="F13" s="90"/>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54"/>
       <c r="B14" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -5893,7 +5896,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -5903,7 +5906,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -5915,7 +5918,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -5937,7 +5940,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -5957,7 +5960,7 @@
       <c r="E4" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -5977,7 +5980,7 @@
       <c r="E5" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -5997,7 +6000,7 @@
       <c r="E6" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -6017,7 +6020,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>3.0439814814814817E-3</v>
       </c>
     </row>
@@ -6037,7 +6040,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -6057,7 +6060,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -6077,7 +6080,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -6097,7 +6100,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>1.9328703703703704E-3</v>
       </c>
     </row>
@@ -6117,7 +6120,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -6137,7 +6140,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -6157,7 +6160,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -6177,7 +6180,7 @@
       <c r="E15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -6197,7 +6200,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
@@ -6217,7 +6220,7 @@
       <c r="E17" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -6237,7 +6240,7 @@
       <c r="E18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -6257,7 +6260,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -6277,7 +6280,7 @@
       <c r="E20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="89">
         <v>3.414351851851852E-3</v>
       </c>
     </row>
@@ -6297,7 +6300,7 @@
       <c r="E21" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -6306,7 +6309,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C22" s="58" t="s">
         <v>2</v>
@@ -6317,7 +6320,7 @@
       <c r="E22" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -6335,7 +6338,7 @@
       <c r="E23" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="90">
+      <c r="F23" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -6355,7 +6358,7 @@
       <c r="E24" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="90">
+      <c r="F24" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -6375,7 +6378,7 @@
       <c r="E25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="90">
+      <c r="F25" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -6395,7 +6398,7 @@
       <c r="E26" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="90">
+      <c r="F26" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -6415,7 +6418,7 @@
       <c r="E27" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -6435,7 +6438,7 @@
       <c r="E28" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="90">
+      <c r="F28" s="89">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -6455,7 +6458,7 @@
       <c r="E29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="90">
+      <c r="F29" s="89">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -6473,7 +6476,7 @@
       <c r="E30" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="90">
+      <c r="F30" s="89">
         <f>VLOOKUP(B30,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -6494,7 +6497,7 @@
       <c r="E31" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="90">
+      <c r="F31" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -6514,7 +6517,7 @@
       <c r="E32" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="90">
+      <c r="F32" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -6534,7 +6537,7 @@
       <c r="E33" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="90">
+      <c r="F33" s="89">
         <f>VLOOKUP(B33,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -6545,12 +6548,12 @@
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="91"/>
+      <c r="F34" s="90"/>
     </row>
     <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="54"/>
       <c r="B35" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
@@ -6642,7 +6645,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -6652,7 +6655,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -6664,7 +6667,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -6686,7 +6689,7 @@
       <c r="E3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
@@ -6706,7 +6709,7 @@
       <c r="E4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -6726,7 +6729,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -6746,7 +6749,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -6766,7 +6769,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0023148148148148E-3</v>
       </c>
@@ -6787,7 +6790,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -6807,7 +6810,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -6827,7 +6830,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -6847,7 +6850,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -6867,7 +6870,7 @@
       <c r="E12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -6888,7 +6891,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
@@ -6908,7 +6911,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -6928,7 +6931,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -6938,12 +6941,12 @@
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="91"/>
+      <c r="F16" s="90"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54"/>
       <c r="B17" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
@@ -7001,7 +7004,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -7023,7 +7026,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -7045,7 +7048,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -7065,7 +7068,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7085,7 +7088,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -7105,7 +7108,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -7121,7 +7124,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7662037037037039E-3</v>
       </c>
@@ -7142,7 +7145,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -7162,7 +7165,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -7182,7 +7185,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -7202,7 +7205,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -7220,7 +7223,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -7241,7 +7244,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -7261,7 +7264,7 @@
       <c r="E14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -7282,7 +7285,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -7298,7 +7301,7 @@
       <c r="E16" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="90"/>
+      <c r="F16" s="89"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
@@ -7306,12 +7309,12 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="44"/>
-      <c r="F17" s="91"/>
+      <c r="F17" s="90"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54"/>
       <c r="B18" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
@@ -7366,7 +7369,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -7388,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -7410,7 +7413,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -7430,7 +7433,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7450,7 +7453,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -7470,7 +7473,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -7491,7 +7494,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -7511,7 +7514,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -7531,7 +7534,7 @@
       <c r="E9" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -7547,7 +7550,7 @@
       <c r="E10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7662037037037039E-3</v>
       </c>
@@ -7568,7 +7571,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -7588,7 +7591,7 @@
       <c r="E12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.3032407407407407E-3</v>
       </c>
@@ -7609,7 +7612,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -7629,7 +7632,7 @@
       <c r="E14" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -7649,7 +7652,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -7669,7 +7672,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -7689,7 +7692,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -7709,7 +7712,7 @@
       <c r="E18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -7727,7 +7730,7 @@
       <c r="E19" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -7748,7 +7751,7 @@
       <c r="E20" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -7768,7 +7771,7 @@
       <c r="E21" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -7777,7 +7780,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C22" s="58" t="s">
         <v>2</v>
@@ -7788,7 +7791,7 @@
       <c r="E22" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -7808,7 +7811,7 @@
       <c r="E23" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="90">
+      <c r="F23" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -7826,7 +7829,7 @@
       <c r="E24" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="90">
+      <c r="F24" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -7846,7 +7849,7 @@
       <c r="E25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="90">
+      <c r="F25" s="89">
         <f>VLOOKUP(B25,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -7867,7 +7870,7 @@
       <c r="E26" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="90">
+      <c r="F26" s="89">
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
@@ -7887,7 +7890,7 @@
       <c r="E27" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="89">
         <f>VLOOKUP(B27,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -7908,7 +7911,7 @@
       <c r="E28" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="90">
+      <c r="F28" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -7928,7 +7931,7 @@
       <c r="E29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="90">
+      <c r="F29" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -7948,7 +7951,7 @@
       <c r="E30" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="90">
+      <c r="F30" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -7958,12 +7961,12 @@
       <c r="C31" s="51"/>
       <c r="D31" s="51"/>
       <c r="E31" s="44"/>
-      <c r="F31" s="91"/>
+      <c r="F31" s="90"/>
     </row>
     <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="54"/>
       <c r="B32" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
@@ -8047,7 +8050,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -8057,7 +8060,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -8069,7 +8072,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -8091,7 +8094,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -8111,7 +8114,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8131,7 +8134,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -8151,7 +8154,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -8172,7 +8175,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -8192,7 +8195,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
@@ -8212,7 +8215,7 @@
       <c r="E9" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.3032407407407407E-3</v>
       </c>
@@ -8233,7 +8236,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -8253,7 +8256,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
@@ -8273,7 +8276,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -8293,7 +8296,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -8313,7 +8316,7 @@
       <c r="E14" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -8331,7 +8334,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -8352,7 +8355,7 @@
       <c r="E16" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -8372,7 +8375,7 @@
       <c r="E17" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -8392,7 +8395,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -8410,7 +8413,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -8430,7 +8433,7 @@
       <c r="E20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -8450,13 +8453,13 @@
       <c r="E21" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="60" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B22" s="45" t="s">
         <v>105</v>
@@ -8470,7 +8473,7 @@
       <c r="E22" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -8480,12 +8483,12 @@
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="91"/>
+      <c r="F23" s="90"/>
     </row>
     <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="54"/>
       <c r="B24" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
@@ -8555,7 +8558,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -8565,7 +8568,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -8577,7 +8580,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -8599,7 +8602,7 @@
       <c r="E3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0833333333333333E-3</v>
       </c>
@@ -8620,7 +8623,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -8640,7 +8643,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8660,7 +8663,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -8680,7 +8683,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -8700,7 +8703,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
@@ -8720,7 +8723,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -8738,7 +8741,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -8759,7 +8762,7 @@
       <c r="E11" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -8779,7 +8782,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -8799,7 +8802,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
@@ -8808,7 +8811,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>2</v>
@@ -8819,7 +8822,7 @@
       <c r="E14" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -8839,13 +8842,13 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="60" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B16" s="45" t="s">
         <v>105</v>
@@ -8859,7 +8862,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -8869,12 +8872,12 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="44"/>
-      <c r="F17" s="91"/>
+      <c r="F17" s="90"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54"/>
       <c r="B18" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
@@ -8933,7 +8936,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -8955,7 +8958,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -8977,7 +8980,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -8997,7 +9000,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9017,7 +9020,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -9037,7 +9040,7 @@
       <c r="E6" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -9057,7 +9060,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -9078,7 +9081,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -9096,7 +9099,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -9116,7 +9119,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -9134,7 +9137,7 @@
       <c r="E11" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -9155,7 +9158,7 @@
       <c r="E12" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -9175,7 +9178,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -9185,12 +9188,12 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="91"/>
+      <c r="F14" s="90"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
       <c r="B15" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -9242,7 +9245,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -9252,7 +9255,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -9264,7 +9267,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -9286,7 +9289,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -9306,7 +9309,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -9326,7 +9329,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -9346,7 +9349,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -9366,7 +9369,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -9386,7 +9389,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -9395,7 +9398,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>2</v>
@@ -9406,7 +9409,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9426,7 +9429,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -9447,7 +9450,7 @@
       <c r="E11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9675925925925924E-3</v>
       </c>
@@ -9468,7 +9471,7 @@
       <c r="E12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -9487,7 +9490,7 @@
       <c r="E13" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -9507,7 +9510,7 @@
       <c r="E14" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -9527,7 +9530,7 @@
       <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -9547,7 +9550,7 @@
       <c r="E16" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -9566,7 +9569,7 @@
       <c r="E17" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -9587,7 +9590,7 @@
       <c r="E18" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5115740740740741E-3</v>
       </c>
@@ -9608,7 +9611,7 @@
       <c r="E19" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3449074074074076E-3</v>
       </c>
@@ -9629,7 +9632,7 @@
       <c r="E20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -9649,7 +9652,7 @@
       <c r="E21" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="89">
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
@@ -9669,7 +9672,7 @@
       <c r="E22" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="89">
         <f>VLOOKUP(B22,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -9690,7 +9693,7 @@
       <c r="E23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="90">
+      <c r="F23" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -9710,7 +9713,7 @@
       <c r="E24" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="90">
+      <c r="F24" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -9730,7 +9733,7 @@
       <c r="E25" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="90">
+      <c r="F25" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -9750,7 +9753,7 @@
       <c r="E26" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="90">
+      <c r="F26" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -9770,7 +9773,7 @@
       <c r="E27" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -9790,7 +9793,7 @@
       <c r="E28" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="90">
+      <c r="F28" s="89">
         <f>VLOOKUP(B28,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -9801,12 +9804,12 @@
       <c r="C29" s="51"/>
       <c r="D29" s="51"/>
       <c r="E29" s="44"/>
-      <c r="F29" s="91"/>
+      <c r="F29" s="90"/>
     </row>
     <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="54"/>
       <c r="B30" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
@@ -9893,7 +9896,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>131</v>
       </c>
       <c r="B1" s="63"/>
@@ -9905,49 +9908,49 @@
       <c r="H1" s="63"/>
       <c r="I1" s="63"/>
       <c r="J1" s="63"/>
-      <c r="K1" s="79"/>
+      <c r="K1" s="78"/>
       <c r="L1" s="63"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="79" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="80" t="s">
+      <c r="J2" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="80" t="s">
+      <c r="L2" s="79" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="82" t="s">
         <v>144</v>
       </c>
       <c r="B3" s="18" t="s">
@@ -9967,11 +9970,11 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
-      <c r="K3" s="84"/>
+      <c r="K3" s="83"/>
       <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="82" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -9991,11 +9994,11 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
-      <c r="K4" s="85"/>
+      <c r="K4" s="84"/>
       <c r="L4" s="14"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="82" t="s">
         <v>152</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -10017,11 +10020,11 @@
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="85"/>
+      <c r="K5" s="84"/>
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="82" t="s">
         <v>155</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -10045,13 +10048,13 @@
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
-      <c r="K6" s="85">
+      <c r="K6" s="84">
         <v>100</v>
       </c>
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="82" t="s">
         <v>160</v>
       </c>
       <c r="B7" s="19" t="s">
@@ -10073,11 +10076,11 @@
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
-      <c r="K7" s="85"/>
+      <c r="K7" s="84"/>
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="82" t="s">
         <v>161</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -10097,11 +10100,11 @@
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
-      <c r="K8" s="85"/>
+      <c r="K8" s="84"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="82" t="s">
         <v>162</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -10125,11 +10128,11 @@
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="85"/>
+      <c r="K9" s="84"/>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="82" t="s">
         <v>164</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -10149,11 +10152,11 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="85"/>
+      <c r="K10" s="84"/>
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="82" t="s">
         <v>165</v>
       </c>
       <c r="B11" s="19" t="s">
@@ -10175,11 +10178,11 @@
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="85"/>
+      <c r="K11" s="84"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="82" t="s">
         <v>166</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -10197,11 +10200,11 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="85"/>
+      <c r="K12" s="84"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="82" t="s">
         <v>168</v>
       </c>
       <c r="B13" s="19" t="s">
@@ -10221,7 +10224,7 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="85"/>
+      <c r="K13" s="84"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -10243,13 +10246,13 @@
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-      <c r="K14" s="85"/>
+      <c r="K14" s="84"/>
       <c r="L14" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="82" t="s">
         <v>174</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -10279,11 +10282,11 @@
       <c r="J15" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="K15" s="85"/>
+      <c r="K15" s="84"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="82" t="s">
         <v>182</v>
       </c>
       <c r="B16" s="19" t="s">
@@ -10305,11 +10308,11 @@
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
-      <c r="K16" s="85"/>
+      <c r="K16" s="84"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="82" t="s">
         <v>185</v>
       </c>
       <c r="B17" s="19" t="s">
@@ -10331,11 +10334,11 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="85"/>
+      <c r="K17" s="84"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="82" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="19" t="s">
@@ -10357,11 +10360,11 @@
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="85"/>
+      <c r="K18" s="84"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="82" t="s">
         <v>188</v>
       </c>
       <c r="B19" s="19" t="s">
@@ -10373,7 +10376,9 @@
       <c r="D19" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="14">
+        <v>16</v>
+      </c>
       <c r="F19" s="19">
         <v>75</v>
       </c>
@@ -10389,11 +10394,11 @@
       <c r="J19" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="K19" s="85"/>
+      <c r="K19" s="84"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="82" t="s">
         <v>192</v>
       </c>
       <c r="B20" s="19" t="s">
@@ -10421,59 +10426,59 @@
       <c r="J20" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="K20" s="85">
+      <c r="K20" s="84">
         <v>150</v>
       </c>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>149</v>
+      <c r="A21" s="110">
+        <v>46194</v>
+      </c>
+      <c r="B21" s="111">
+        <v>0.70833333333333337</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="14"/>
+        <v>156</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="E21" s="14"/>
       <c r="F21" s="19"/>
       <c r="G21" s="14" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="85"/>
+      <c r="K21" s="84"/>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
-        <v>200</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>145</v>
+      <c r="A22" s="110">
+        <v>46197</v>
+      </c>
+      <c r="B22" s="111">
+        <v>0.75</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>157</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="19"/>
       <c r="G22" s="14" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="85"/>
+      <c r="K22" s="84"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10518,7 +10523,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -10528,7 +10533,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -10540,7 +10545,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -10562,7 +10567,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -10582,7 +10587,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -10602,7 +10607,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -10622,7 +10627,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -10642,7 +10647,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -10662,7 +10667,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -10671,7 +10676,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>2</v>
@@ -10682,7 +10687,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -10702,7 +10707,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.9583333333333337E-3</v>
       </c>
@@ -10723,7 +10728,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -10742,7 +10747,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -10762,7 +10767,7 @@
       <c r="E13" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -10782,7 +10787,7 @@
       <c r="E14" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.472222222222222E-3</v>
       </c>
@@ -10801,7 +10806,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -10822,7 +10827,7 @@
       <c r="E16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -10842,7 +10847,7 @@
       <c r="E17" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -10863,7 +10868,7 @@
       <c r="E18" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -10883,7 +10888,7 @@
       <c r="E19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -10903,7 +10908,7 @@
       <c r="E20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -10923,7 +10928,7 @@
       <c r="E21" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -10943,7 +10948,7 @@
       <c r="E22" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -10963,7 +10968,7 @@
       <c r="E23" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="90">
+      <c r="F23" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -10973,12 +10978,12 @@
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="44"/>
-      <c r="F24" s="91"/>
+      <c r="F24" s="90"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54"/>
       <c r="B25" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
@@ -11050,7 +11055,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -11060,7 +11065,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -11072,7 +11077,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -11094,7 +11099,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11114,7 +11119,7 @@
       <c r="E4" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11134,7 +11139,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -11154,7 +11159,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -11174,7 +11179,7 @@
       <c r="E7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -11194,7 +11199,7 @@
       <c r="E8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -11214,7 +11219,7 @@
       <c r="E9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -11234,7 +11239,7 @@
       <c r="E10" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -11254,7 +11259,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11275,7 +11280,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11295,7 +11300,7 @@
       <c r="E13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -11305,12 +11310,12 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="91"/>
+      <c r="F14" s="90"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
       <c r="B15" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -11364,7 +11369,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -11374,7 +11379,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -11386,7 +11391,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -11408,7 +11413,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11428,7 +11433,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -11448,7 +11453,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
@@ -11468,7 +11473,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -11488,7 +11493,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
@@ -11508,7 +11513,7 @@
       <c r="E8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -11517,7 +11522,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>2</v>
@@ -11528,7 +11533,7 @@
       <c r="E9" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11548,7 +11553,7 @@
       <c r="E10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -11568,7 +11573,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11587,7 +11592,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
@@ -11607,7 +11612,7 @@
       <c r="E13" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -11627,7 +11632,7 @@
       <c r="E14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -11647,7 +11652,7 @@
       <c r="E15" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11667,7 +11672,7 @@
       <c r="E16" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11687,7 +11692,7 @@
       <c r="E17" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="89">
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
@@ -11707,7 +11712,7 @@
       <c r="E18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -11717,12 +11722,12 @@
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="44"/>
-      <c r="F19" s="91"/>
+      <c r="F19" s="90"/>
     </row>
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54"/>
       <c r="B20" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
@@ -11785,7 +11790,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -11795,7 +11800,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -11807,7 +11812,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -11829,7 +11834,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -11849,7 +11854,7 @@
       <c r="E4" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -11869,7 +11874,7 @@
       <c r="E5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -11889,7 +11894,7 @@
       <c r="E6" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -11909,7 +11914,7 @@
       <c r="E7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -11930,7 +11935,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
@@ -11951,7 +11956,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
@@ -11971,7 +11976,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -11991,7 +11996,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
@@ -12011,7 +12016,7 @@
       <c r="E12" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
@@ -12031,7 +12036,7 @@
       <c r="E13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="89">
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
@@ -12041,12 +12046,12 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="44"/>
-      <c r="F14" s="91"/>
+      <c r="F14" s="90"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54"/>
       <c r="B15" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -12100,7 +12105,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -12110,7 +12115,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -12122,7 +12127,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>6</v>
@@ -12144,7 +12149,7 @@
       <c r="E3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="89">
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
@@ -12164,7 +12169,7 @@
       <c r="E4" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="89">
         <v>2.488425925925926E-3</v>
       </c>
     </row>
@@ -12184,7 +12189,7 @@
       <c r="E5" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="89">
         <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9675925925925924E-3</v>
       </c>
@@ -12205,7 +12210,7 @@
       <c r="E6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="89">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>5.5555555555555558E-3</v>
       </c>
@@ -12226,7 +12231,7 @@
       <c r="E7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
@@ -12246,7 +12251,7 @@
       <c r="E8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="89">
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
@@ -12264,7 +12269,7 @@
       <c r="E9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.7708333333333332E-3</v>
       </c>
@@ -12285,7 +12290,7 @@
       <c r="E10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="89">
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
@@ -12305,7 +12310,7 @@
       <c r="E11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="89">
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
@@ -12325,7 +12330,7 @@
       <c r="E12" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="89">
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
@@ -12335,12 +12340,12 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="91"/>
+      <c r="F13" s="90"/>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54"/>
       <c r="B14" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -12391,89 +12396,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+    </row>
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="72" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-    </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="C2" s="74" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="D2" s="74" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="E2" s="74" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="F2" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="E2" s="75" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>212</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>214</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>36</v>
@@ -12483,17 +12488,17 @@
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>36</v>
@@ -12502,26 +12507,26 @@
         <v>40</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
@@ -12567,81 +12572,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="77" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-    </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="78" t="s">
+      <c r="D2" s="77" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="E2" s="77" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="F2" s="77" t="s">
         <v>230</v>
       </c>
-      <c r="E2" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>232</v>
-      </c>
-      <c r="G2" s="78" t="s">
+      <c r="G2" s="77" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>236</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>240</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>242</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>168</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -12664,7 +12669,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B1" s="63"/>
       <c r="C1" s="63"/>
@@ -12675,19 +12680,19 @@
       <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="86" t="s">
-        <v>246</v>
-      </c>
-      <c r="D2" s="86" t="s">
-        <v>247</v>
-      </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>143</v>
       </c>
       <c r="F2" s="63"/>
@@ -12695,20 +12700,20 @@
       <c r="H2" s="63"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87">
+      <c r="A3" s="86">
         <v>46154</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="88">
+      <c r="D3" s="87">
         <v>86.99</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
@@ -12977,7 +12982,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="50"/>
@@ -12987,7 +12992,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>1</v>
@@ -12999,7 +13004,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r